--- a/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
@@ -1700,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2126,7 +2126,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2625,7 +2625,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>HANBAITEN_NOT_FOUND</t>
+          <t>NOT_FOUND</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -2678,7 +2678,7 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="19" t="inlineStr">
         <is>
-          <t>HAS_RELATED_DATA</t>
+          <t>CONFLICT</t>
         </is>
       </c>
       <c r="K14" s="10" t="n"/>
@@ -2941,7 +2941,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3376,7 +3376,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3730,7 +3730,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK91"/>
+  <dimension ref="A1:AK90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7305,7 +7305,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/16</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -7659,7 +7659,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="19" t="inlineStr">
         <is>
-          <t>Content-Type: application/json&lt;br&gt;※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
+          <t>Content-Type: application/json  ※ 認証情報はHTTP-only Cookieにより自動的に送信される</t>
         </is>
       </c>
       <c r="K13" s="10" t="n"/>
@@ -8471,7 +8471,7 @@
       <c r="C47" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "HANBAITEN_NOT_FOUND",
+  "error_code": "NOT_FOUND",
   "message": "指定された販売店が見つかりません"
 }</t>
         </is>
@@ -8522,7 +8522,7 @@
       <c r="C50" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "HAS_RELATED_DATA",
+  "error_code": "CONFLICT",
   "message": "関連データが存在するため削除できません"
 }</t>
         </is>
@@ -8621,59 +8621,96 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
-      <c r="B57" s="27" t="inlineStr">
+    <row r="57" ht="54" customHeight="1">
+      <c r="B57" s="42" t="inlineStr">
+        <is>
+          <t>※ 以下の処理は単一トランザクション内で実行する（本処理 + 操作ログ記録）。
+いずれかが失敗した場合は全てロールバックすること。
+例外処理中のエラーログ（log_type=3）はトランザクション外で別途記録する。</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="10" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="10" t="n"/>
+      <c r="M57" s="10" t="n"/>
+      <c r="N57" s="10" t="n"/>
+      <c r="O57" s="10" t="n"/>
+      <c r="P57" s="10" t="n"/>
+      <c r="Q57" s="10" t="n"/>
+      <c r="R57" s="10" t="n"/>
+      <c r="S57" s="10" t="n"/>
+      <c r="T57" s="10" t="n"/>
+      <c r="U57" s="10" t="n"/>
+      <c r="V57" s="10" t="n"/>
+      <c r="W57" s="10" t="n"/>
+      <c r="X57" s="10" t="n"/>
+      <c r="Y57" s="10" t="n"/>
+      <c r="Z57" s="10" t="n"/>
+      <c r="AA57" s="10" t="n"/>
+      <c r="AB57" s="10" t="n"/>
+      <c r="AC57" s="10" t="n"/>
+      <c r="AD57" s="10" t="n"/>
+      <c r="AE57" s="10" t="n"/>
+      <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="11" t="n"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
-      <c r="C58" s="41" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="C59" s="41" t="inlineStr">
         <is>
           <t>パスパラメータの検証：</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="D59" s="41" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="D60" s="41" t="inlineStr">
         <is>
           <t>hanbaiten_id：数値型チェック、必須チェック</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="C60" s="41" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="41" t="inlineStr">
         <is>
           <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="D61" s="41" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="D62" s="41" t="inlineStr">
         <is>
           <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="27" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（JWT / Cookie）。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
       <c r="C64" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
@@ -8699,35 +8736,28 @@
       </c>
     </row>
     <row r="68" ht="18" customHeight="1">
-      <c r="C68" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
     <row r="69" ht="18" customHeight="1">
-      <c r="B69" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="C69" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="C70" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープを取得する（ja_id）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="C71" s="41" t="inlineStr">
-        <is>
           <t>対象レコードの存在確認とスコープチェックを行う。</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="198" customHeight="1">
-      <c r="C72" s="42" t="inlineStr">
+    <row r="71" ht="198" customHeight="1">
+      <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
        hanbaiten_name_kana, torihikisaki_no,
@@ -8742,76 +8772,119 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n"/>
-      <c r="M72" s="10" t="n"/>
-      <c r="N72" s="10" t="n"/>
-      <c r="O72" s="10" t="n"/>
-      <c r="P72" s="10" t="n"/>
-      <c r="Q72" s="10" t="n"/>
-      <c r="R72" s="10" t="n"/>
-      <c r="S72" s="10" t="n"/>
-      <c r="T72" s="10" t="n"/>
-      <c r="U72" s="10" t="n"/>
-      <c r="V72" s="10" t="n"/>
-      <c r="W72" s="10" t="n"/>
-      <c r="X72" s="10" t="n"/>
-      <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="10" t="n"/>
-      <c r="AA72" s="10" t="n"/>
-      <c r="AB72" s="10" t="n"/>
-      <c r="AC72" s="10" t="n"/>
-      <c r="AD72" s="10" t="n"/>
-      <c r="AE72" s="10" t="n"/>
-      <c r="AF72" s="10" t="n"/>
-      <c r="AG72" s="10" t="n"/>
-      <c r="AH72" s="10" t="n"/>
-      <c r="AI72" s="10" t="n"/>
-      <c r="AJ72" s="10" t="n"/>
-      <c r="AK72" s="11" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="10" t="n"/>
+      <c r="M71" s="10" t="n"/>
+      <c r="N71" s="10" t="n"/>
+      <c r="O71" s="10" t="n"/>
+      <c r="P71" s="10" t="n"/>
+      <c r="Q71" s="10" t="n"/>
+      <c r="R71" s="10" t="n"/>
+      <c r="S71" s="10" t="n"/>
+      <c r="T71" s="10" t="n"/>
+      <c r="U71" s="10" t="n"/>
+      <c r="V71" s="10" t="n"/>
+      <c r="W71" s="10" t="n"/>
+      <c r="X71" s="10" t="n"/>
+      <c r="Y71" s="10" t="n"/>
+      <c r="Z71" s="10" t="n"/>
+      <c r="AA71" s="10" t="n"/>
+      <c r="AB71" s="10" t="n"/>
+      <c r="AC71" s="10" t="n"/>
+      <c r="AD71" s="10" t="n"/>
+      <c r="AE71" s="10" t="n"/>
+      <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="11" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="C72" s="41" t="inlineStr">
+        <is>
+          <t>レコードが存在しない場合：HTTP 404 (`NOT_FOUND`)</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="18" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>レコードが存在しない場合：HTTP 404 (`HANBAITEN_NOT_FOUND`)</t>
+          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
     <row r="74" ht="18" customHeight="1">
-      <c r="C74" s="41" t="inlineStr">
-        <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>4.4 関連データの存在チェック</t>
         </is>
       </c>
     </row>
     <row r="75" ht="18" customHeight="1">
-      <c r="B75" s="27" t="inlineStr">
-        <is>
-          <t>4.4 関連データの存在チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="C76" s="41" t="inlineStr">
+      <c r="C75" s="41" t="inlineStr">
         <is>
           <t>以下のテーブルで対象販売店が参照されているか確認する。</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="72" customHeight="1">
-      <c r="C77" s="42" t="inlineStr">
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS cnt
 FROM t_dokusya
 WHERE hanbaiten_id = :hanbaiten_id
   AND deleted_at IS NULL</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="54" customHeight="1">
+      <c r="C77" s="42" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) AS cnt
+FROM t_dokusya_rireki
+WHERE hanbaiten_id = :hanbaiten_id</t>
         </is>
       </c>
       <c r="D77" s="10" t="n"/>
@@ -8849,65 +8922,22 @@
       <c r="AJ77" s="10" t="n"/>
       <c r="AK77" s="11" t="n"/>
     </row>
-    <row r="78" ht="54" customHeight="1">
-      <c r="C78" s="42" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) AS cnt
-FROM t_dokusya_rireki
-WHERE hanbaiten_id = :hanbaiten_id</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="n"/>
-      <c r="E78" s="10" t="n"/>
-      <c r="F78" s="10" t="n"/>
-      <c r="G78" s="10" t="n"/>
-      <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="10" t="n"/>
-      <c r="M78" s="10" t="n"/>
-      <c r="N78" s="10" t="n"/>
-      <c r="O78" s="10" t="n"/>
-      <c r="P78" s="10" t="n"/>
-      <c r="Q78" s="10" t="n"/>
-      <c r="R78" s="10" t="n"/>
-      <c r="S78" s="10" t="n"/>
-      <c r="T78" s="10" t="n"/>
-      <c r="U78" s="10" t="n"/>
-      <c r="V78" s="10" t="n"/>
-      <c r="W78" s="10" t="n"/>
-      <c r="X78" s="10" t="n"/>
-      <c r="Y78" s="10" t="n"/>
-      <c r="Z78" s="10" t="n"/>
-      <c r="AA78" s="10" t="n"/>
-      <c r="AB78" s="10" t="n"/>
-      <c r="AC78" s="10" t="n"/>
-      <c r="AD78" s="10" t="n"/>
-      <c r="AE78" s="10" t="n"/>
-      <c r="AF78" s="10" t="n"/>
-      <c r="AG78" s="10" t="n"/>
-      <c r="AH78" s="10" t="n"/>
-      <c r="AI78" s="10" t="n"/>
-      <c r="AJ78" s="10" t="n"/>
-      <c r="AK78" s="11" t="n"/>
-    </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="C79" s="41" t="inlineStr">
-        <is>
-          <t>いずれかのテーブルで関連データが存在する場合（cnt &gt; 0）：HTTP 409 (`HAS_RELATED_DATA`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
+    <row r="78" ht="36" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>いずれかのテーブルで関連データが存在する場合（cnt &gt; 0）：HTTP 409 (`CONFLICT`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="126" customHeight="1">
-      <c r="C81" s="42" t="inlineStr">
+    <row r="80" ht="126" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_hanbaiten
 SET deleted_at = NOW(),
@@ -8918,57 +8948,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
-      <c r="U81" s="10" t="n"/>
-      <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
-      <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
-      <c r="AG81" s="10" t="n"/>
-      <c r="AH81" s="10" t="n"/>
-      <c r="AI81" s="10" t="n"/>
-      <c r="AJ81" s="10" t="n"/>
-      <c r="AK81" s="11" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>4.6 操作ログ記録</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
-        <is>
-          <t>4.6 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="216" customHeight="1">
-      <c r="C84" s="42" t="inlineStr">
+    <row r="83" ht="216" customHeight="1">
+      <c r="C83" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -8982,6 +9012,63 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="324" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "山田新聞販売店",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区千代田1-1",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_shiharai_cycle": 1,
+  "tesuryo_kubun": 1,
+  "tesuryo_amount": 500
+}</t>
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
@@ -9019,100 +9106,43 @@
       <c r="AJ84" s="10" t="n"/>
       <c r="AK84" s="11" t="n"/>
     </row>
-    <row r="85" ht="324" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "山田新聞販売店",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区千代田1-1",
-  "tel": "0312345678",
-  "fax": "0312345679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_shiharai_cycle": 1,
-  "tesuryo_kubun": 1,
-  "tesuryo_amount": 500
-}</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>4.7 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="B86" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>削除成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>削除成功メッセージを返却する。HTTP 200。</t>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="B88" s="27" t="inlineStr">
-        <is>
-          <t>4.8 例外処理</t>
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="216" customHeight="1">
-      <c r="C91" s="42" t="inlineStr">
+    <row r="90" ht="216" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9128,43 +9158,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="121">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
@@ -9178,40 +9208,40 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C68:AK68"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="C58:AK58"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="C65:AK65"/>
     <mergeCell ref="C44:AK44"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="C70:AK70"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="D61:AK61"/>
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C74:AK74"/>
-    <mergeCell ref="B69:AK69"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
@@ -9220,36 +9250,37 @@
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="B49:I49"/>
     <mergeCell ref="Y29:AE29"/>
+    <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="D66:AK66"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
-    <mergeCell ref="C81:AK81"/>
+    <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
-    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="C64:AK64"/>
-    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="C41:AK41"/>
     <mergeCell ref="C50:AK50"/>
     <mergeCell ref="J10:AK10"/>
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
@@ -9261,16 +9292,17 @@
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="B14:I19"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="C69:AK69"/>
     <mergeCell ref="C83:AK83"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B52:I52"/>
-    <mergeCell ref="B88:AK88"/>
-    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
-    <mergeCell ref="D59:AK59"/>
     <mergeCell ref="C47:AK47"/>
+    <mergeCell ref="D60:AK60"/>
+    <mergeCell ref="B74:AK74"/>
+    <mergeCell ref="B68:AK68"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
@@ -9278,13 +9310,10 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="C60:AK60"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="B75:AK75"/>
-    <mergeCell ref="B62:AK62"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>

--- a/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1512,22 +1512,88 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Dao Van Thang</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>画面設計書 v1.2 対応：検索条件「廃店フラグ」追加（デフォルトは廃店=false のレコードのみ表示）、一覧レスポンスに「都道府県」（m_todofuken JOIN による todofuken_name）追加、列ラベルを「手数料区分」→「振込手数料負担区分」、「支払区分」→「配達手数料支払サイクル」に変更</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="21">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="R2:V2"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,7 +1605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1700,7 +1766,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1923,8 +1989,52 @@
       <c r="AF20" s="10" t="n"/>
       <c r="AG20" s="11" t="n"/>
     </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="C21" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>ACSMS-API-COMMON-001</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="19" t="inlineStr">
+        <is>
+          <t>Get Prefecture List（都道府県プルダウン取得）</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
+    <mergeCell ref="O21:AG21"/>
     <mergeCell ref="D20:N20"/>
     <mergeCell ref="D19:N19"/>
     <mergeCell ref="Z1:AC1"/>
@@ -1932,6 +2042,7 @@
     <mergeCell ref="C15:AK15"/>
     <mergeCell ref="B14:AK14"/>
     <mergeCell ref="B17:AK17"/>
+    <mergeCell ref="D21:N21"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AG3"/>
@@ -2126,7 +2237,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2694,7 +2805,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>この販売店は関連オブジェクトに紐づいているため削除できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -2941,7 +3052,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3215,7 +3326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK130"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3376,7 +3487,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4380,13 +4491,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="54" customHeight="1">
       <c r="B28" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4400,7 +4511,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -4431,7 +4542,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（1始まり）。デフォルト: 1</t>
+          <t>廃店フラグ（true:廃店も含む, false:廃店を除外）。**省略時は false（廃店フラグが立っているレコードは一覧に表示しない）**。画面設計書 v1.2 §1.1 / §2.1 参照</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4446,7 +4557,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -4491,7 +4602,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
+          <t>ページ番号（1始まり）。デフォルト: 1</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -4500,13 +4611,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="18" customHeight="1">
       <c r="B30" s="31" t="n">
         <v>9</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -4520,7 +4631,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -4551,7 +4662,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name）。デフォルト: created_at</t>
+          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -4560,13 +4671,13 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1">
+    <row r="31" ht="54" customHeight="1">
       <c r="B31" s="31" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -4611,7 +4722,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc, desc）。デフォルト: desc</t>
+          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name, updated_at）。デフォルト: updated_at（最終更新が新しい順）。updated_at は画面のソートヘッダではなく既定の並び順（新規作成・取込・更新直後の行を先頭に表示）</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4620,88 +4731,84 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="17" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc, desc）。デフォルト: desc（最終更新が新しい順）</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="19.5" customHeight="1"/>
+    <row r="34" ht="19.5" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -4713,29 +4820,33 @@
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
       <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
+      <c r="Q36" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
+      <c r="T36" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y36" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -4744,9 +4855,9 @@
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>販売店データの配列</t>
+      <c r="AF36" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4757,14 +4868,14 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>hanbaiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -4775,7 +4886,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4783,7 +4894,7 @@
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R37" s="10" t="n"/>
@@ -4806,7 +4917,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店データの配列</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4817,12 +4928,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C38" s="37" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4866,7 +4977,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4877,12 +4988,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4895,7 +5006,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -4926,7 +5037,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>販売店コード</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4937,12 +5048,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4986,7 +5097,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>販売店コード</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -4997,12 +5108,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5046,7 +5157,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5055,14 +5166,14 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5106,7 +5217,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>都道府県コード（m_hanbaiten.todofuken_code、2桁）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5115,14 +5226,14 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="36" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5166,7 +5277,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>都道府県名（m_todofuken JOIN による表示用。一覧では本項目を「都道府県」列に表示する）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5177,12 +5288,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5226,7 +5337,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5237,12 +5348,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5286,7 +5397,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5297,12 +5408,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5315,7 +5426,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -5335,7 +5446,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -5346,7 +5457,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5357,12 +5468,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun_label</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5395,7 +5506,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -5406,7 +5517,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>委託区分のラベル</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5417,12 +5528,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5435,7 +5546,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5455,7 +5566,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -5466,7 +5577,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5475,14 +5586,14 @@
       <c r="AJ48" s="10" t="n"/>
       <c r="AK48" s="11" t="n"/>
     </row>
-    <row r="49" ht="18" customHeight="1">
+    <row r="49" ht="54" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5526,7 +5637,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分（1:JA, 2:販売店）</t>
+          <t>委託区分（※m_code.code_category='ITAKU_KUBUN'を参照、1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5535,14 +5646,14 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="36" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun_label</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -5555,7 +5666,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5586,7 +5697,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分のラベル</t>
+          <t>配達手数料支払サイクル（月数）。一覧では「配達手数料支払サイクル」列に表示する</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5595,14 +5706,14 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="54" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_amount</t>
+          <t>furikomi_tesuryo_futan_kubun</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5646,7 +5757,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>手数料金額</t>
+          <t>振込手数料負担区分（※m_code.code_category='TESURYO_KUBUN'を参照、1:JA, 2:販売店）。一覧では「振込手数料負担区分」列に表示する</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5657,12 +5768,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>furikomi_tesuryo</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -5675,7 +5786,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5688,18 +5799,14 @@
       </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="11" t="n"/>
-      <c r="T52" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T52" s="17" t="inlineStr"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
       <c r="W52" s="10" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z52" s="10" t="n"/>
@@ -5710,7 +5817,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>振込手数料</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5721,12 +5828,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C53" s="39" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5739,7 +5846,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -5752,18 +5859,14 @@
       </c>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="11" t="n"/>
-      <c r="T53" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T53" s="17" t="inlineStr"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z53" s="10" t="n"/>
@@ -5774,7 +5877,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5785,14 +5888,14 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
@@ -5803,7 +5906,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -5816,7 +5919,11 @@
       </c>
       <c r="R54" s="10" t="n"/>
       <c r="S54" s="11" t="n"/>
-      <c r="T54" s="17" t="inlineStr"/>
+      <c r="T54" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
@@ -5834,7 +5941,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -5845,12 +5952,12 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C55" s="37" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C55" s="39" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -5863,7 +5970,7 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
@@ -5876,7 +5983,11 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
@@ -5894,7 +6005,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -5905,14 +6016,14 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C56" s="38" t="n"/>
-      <c r="D56" s="19" t="inlineStr">
-        <is>
-          <t>page</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C56" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
@@ -5923,7 +6034,7 @@
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
@@ -5954,7 +6065,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -5965,12 +6076,12 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="C57" s="38" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C57" s="37" t="n"/>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E57" s="10" t="n"/>
@@ -6014,7 +6125,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6025,12 +6136,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="C58" s="39" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="C58" s="38" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>page</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -6074,7 +6185,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>現在のページ番号</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6083,64 +6194,184 @@
       <c r="AJ58" s="10" t="n"/>
       <c r="AK58" s="11" t="n"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1"/>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="17" t="inlineStr"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="11" t="n"/>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="C60" s="39" t="n"/>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="11" t="n"/>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="17" t="inlineStr"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="11" t="n"/>
+      <c r="Y60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
+    </row>
+    <row r="61" ht="19.5" customHeight="1"/>
+    <row r="62" ht="19.5" customHeight="1">
+      <c r="B62" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
-      <c r="N61" s="10" t="n"/>
-      <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
-      <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
-      <c r="U61" s="10" t="n"/>
-      <c r="V61" s="10" t="n"/>
-      <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
-      <c r="Z61" s="10" t="n"/>
-      <c r="AA61" s="10" t="n"/>
-      <c r="AB61" s="10" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="10" t="n"/>
-      <c r="AK61" s="11" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="C63" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;haiten_flg=false&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="10" t="n"/>
+      <c r="M63" s="10" t="n"/>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="10" t="n"/>
+      <c r="Q63" s="10" t="n"/>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="10" t="n"/>
+      <c r="T63" s="10" t="n"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="10" t="n"/>
+      <c r="Y63" s="10" t="n"/>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="10" t="n"/>
+      <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
+    </row>
+    <row r="65" ht="19.5" customHeight="1">
+      <c r="B65" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="409" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
+    <row r="66" ht="409" customHeight="1">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -6149,17 +6380,18 @@
       "ja_id": 1,
       "hanbaiten_code": "H001",
       "hanbaiten_name": "山田新聞販売店",
+      "todofuken_code": "13",
+      "todofuken_name": "東京都",
       "yubin_no": "1000001",
       "address": "東京都千代田区千代田1-1",
       "tel": "0312345678",
       "fax": "0312345679",
       "shocho_name": "山田太郎",
       "itaku_kubun": 1,
-      "itaku_kubun_label": "振込",
       "haitatsuryo_shiharai_cycle": 1,
-      "tesuryo_kubun": 1,
-      "tesuryo_kubun_label": "JA",
-      "tesuryo_amount": 500,
+      "furikomi_tesuryo_futan_kubun": 1,
+      "furikomi_tesuryo": 500,
+      "haiten_flg": false,
       "created_at": "2026-01-15T10:00:00Z",
       "updated_at": "2026-03-10T14:30:00Z"
     },
@@ -6168,17 +6400,18 @@
       "ja_id": 1,
       "hanbaiten_code": "H002",
       "hanbaiten_name": "山田書店",
+      "todofuken_code": "14",
+      "todofuken_name": "神奈川県",
       "yubin_no": "1500001",
-      "address": "東京都渋谷区神宮前1-2-3",
+      "address": "神奈川県横浜市西区1-2-3",
       "tel": "0398765432",
       "fax": "0398765433",
       "shocho_name": "山田花子",
       "itaku_kubun": 2,
-      "itaku_kubun_label": "日農委託",
       "haitatsuryo_shiharai_cycle": 3,
-      "tesuryo_kubun": 2,
-      "tesuryo_kubun_label": "販売店",
-      "tesuryo_amount": 300,
+      "furikomi_tesuryo_futan_kubun": 2,
+      "furikomi_tesuryo": 300,
+      "haiten_flg": false,
       "created_at": "2026-02-01T09:00:00Z",
       "updated_at": null
     }
@@ -6192,50 +6425,50 @@
 }</t>
         </is>
       </c>
-      <c r="D64" s="10" t="n"/>
-      <c r="E64" s="10" t="n"/>
-      <c r="F64" s="10" t="n"/>
-      <c r="G64" s="10" t="n"/>
-      <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
-      <c r="N64" s="10" t="n"/>
-      <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
-      <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
-      <c r="U64" s="10" t="n"/>
-      <c r="V64" s="10" t="n"/>
-      <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
-      <c r="Z64" s="10" t="n"/>
-      <c r="AA64" s="10" t="n"/>
-      <c r="AB64" s="10" t="n"/>
-      <c r="AC64" s="10" t="n"/>
-      <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
-      <c r="AG64" s="10" t="n"/>
-      <c r="AH64" s="10" t="n"/>
-      <c r="AI64" s="10" t="n"/>
-      <c r="AJ64" s="10" t="n"/>
-      <c r="AK64" s="11" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="B66" s="40" t="inlineStr">
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="10" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="10" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="10" t="n"/>
+      <c r="R66" s="10" t="n"/>
+      <c r="S66" s="10" t="n"/>
+      <c r="T66" s="10" t="n"/>
+      <c r="U66" s="10" t="n"/>
+      <c r="V66" s="10" t="n"/>
+      <c r="W66" s="10" t="n"/>
+      <c r="X66" s="10" t="n"/>
+      <c r="Y66" s="10" t="n"/>
+      <c r="Z66" s="10" t="n"/>
+      <c r="AA66" s="10" t="n"/>
+      <c r="AB66" s="10" t="n"/>
+      <c r="AC66" s="10" t="n"/>
+      <c r="AD66" s="10" t="n"/>
+      <c r="AE66" s="10" t="n"/>
+      <c r="AF66" s="10" t="n"/>
+      <c r="AG66" s="10" t="n"/>
+      <c r="AH66" s="10" t="n"/>
+      <c r="AI66" s="10" t="n"/>
+      <c r="AJ66" s="10" t="n"/>
+      <c r="AK66" s="11" t="n"/>
+    </row>
+    <row r="68" ht="19.5" customHeight="1">
+      <c r="B68" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="72" customHeight="1">
-      <c r="C67" s="19" t="inlineStr">
+    <row r="69" ht="72" customHeight="1">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -6243,50 +6476,50 @@
 }</t>
         </is>
       </c>
-      <c r="D67" s="10" t="n"/>
-      <c r="E67" s="10" t="n"/>
-      <c r="F67" s="10" t="n"/>
-      <c r="G67" s="10" t="n"/>
-      <c r="H67" s="10" t="n"/>
-      <c r="I67" s="10" t="n"/>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="10" t="n"/>
-      <c r="M67" s="10" t="n"/>
-      <c r="N67" s="10" t="n"/>
-      <c r="O67" s="10" t="n"/>
-      <c r="P67" s="10" t="n"/>
-      <c r="Q67" s="10" t="n"/>
-      <c r="R67" s="10" t="n"/>
-      <c r="S67" s="10" t="n"/>
-      <c r="T67" s="10" t="n"/>
-      <c r="U67" s="10" t="n"/>
-      <c r="V67" s="10" t="n"/>
-      <c r="W67" s="10" t="n"/>
-      <c r="X67" s="10" t="n"/>
-      <c r="Y67" s="10" t="n"/>
-      <c r="Z67" s="10" t="n"/>
-      <c r="AA67" s="10" t="n"/>
-      <c r="AB67" s="10" t="n"/>
-      <c r="AC67" s="10" t="n"/>
-      <c r="AD67" s="10" t="n"/>
-      <c r="AE67" s="10" t="n"/>
-      <c r="AF67" s="10" t="n"/>
-      <c r="AG67" s="10" t="n"/>
-      <c r="AH67" s="10" t="n"/>
-      <c r="AI67" s="10" t="n"/>
-      <c r="AJ67" s="10" t="n"/>
-      <c r="AK67" s="11" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1">
-      <c r="B69" s="40" t="inlineStr">
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="10" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="10" t="n"/>
+      <c r="M69" s="10" t="n"/>
+      <c r="N69" s="10" t="n"/>
+      <c r="O69" s="10" t="n"/>
+      <c r="P69" s="10" t="n"/>
+      <c r="Q69" s="10" t="n"/>
+      <c r="R69" s="10" t="n"/>
+      <c r="S69" s="10" t="n"/>
+      <c r="T69" s="10" t="n"/>
+      <c r="U69" s="10" t="n"/>
+      <c r="V69" s="10" t="n"/>
+      <c r="W69" s="10" t="n"/>
+      <c r="X69" s="10" t="n"/>
+      <c r="Y69" s="10" t="n"/>
+      <c r="Z69" s="10" t="n"/>
+      <c r="AA69" s="10" t="n"/>
+      <c r="AB69" s="10" t="n"/>
+      <c r="AC69" s="10" t="n"/>
+      <c r="AD69" s="10" t="n"/>
+      <c r="AE69" s="10" t="n"/>
+      <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="19.5" customHeight="1">
+      <c r="B71" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="72" customHeight="1">
-      <c r="C70" s="19" t="inlineStr">
+    <row r="72" ht="72" customHeight="1">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -6294,50 +6527,50 @@
 }</t>
         </is>
       </c>
-      <c r="D70" s="10" t="n"/>
-      <c r="E70" s="10" t="n"/>
-      <c r="F70" s="10" t="n"/>
-      <c r="G70" s="10" t="n"/>
-      <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="10" t="n"/>
-      <c r="M70" s="10" t="n"/>
-      <c r="N70" s="10" t="n"/>
-      <c r="O70" s="10" t="n"/>
-      <c r="P70" s="10" t="n"/>
-      <c r="Q70" s="10" t="n"/>
-      <c r="R70" s="10" t="n"/>
-      <c r="S70" s="10" t="n"/>
-      <c r="T70" s="10" t="n"/>
-      <c r="U70" s="10" t="n"/>
-      <c r="V70" s="10" t="n"/>
-      <c r="W70" s="10" t="n"/>
-      <c r="X70" s="10" t="n"/>
-      <c r="Y70" s="10" t="n"/>
-      <c r="Z70" s="10" t="n"/>
-      <c r="AA70" s="10" t="n"/>
-      <c r="AB70" s="10" t="n"/>
-      <c r="AC70" s="10" t="n"/>
-      <c r="AD70" s="10" t="n"/>
-      <c r="AE70" s="10" t="n"/>
-      <c r="AF70" s="10" t="n"/>
-      <c r="AG70" s="10" t="n"/>
-      <c r="AH70" s="10" t="n"/>
-      <c r="AI70" s="10" t="n"/>
-      <c r="AJ70" s="10" t="n"/>
-      <c r="AK70" s="11" t="n"/>
-    </row>
-    <row r="72" ht="19.5" customHeight="1">
-      <c r="B72" s="40" t="inlineStr">
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="10" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="10" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="10" t="n"/>
+      <c r="R72" s="10" t="n"/>
+      <c r="S72" s="10" t="n"/>
+      <c r="T72" s="10" t="n"/>
+      <c r="U72" s="10" t="n"/>
+      <c r="V72" s="10" t="n"/>
+      <c r="W72" s="10" t="n"/>
+      <c r="X72" s="10" t="n"/>
+      <c r="Y72" s="10" t="n"/>
+      <c r="Z72" s="10" t="n"/>
+      <c r="AA72" s="10" t="n"/>
+      <c r="AB72" s="10" t="n"/>
+      <c r="AC72" s="10" t="n"/>
+      <c r="AD72" s="10" t="n"/>
+      <c r="AE72" s="10" t="n"/>
+      <c r="AF72" s="10" t="n"/>
+      <c r="AG72" s="10" t="n"/>
+      <c r="AH72" s="10" t="n"/>
+      <c r="AI72" s="10" t="n"/>
+      <c r="AJ72" s="10" t="n"/>
+      <c r="AK72" s="11" t="n"/>
+    </row>
+    <row r="74" ht="19.5" customHeight="1">
+      <c r="B74" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="72" customHeight="1">
-      <c r="C73" s="19" t="inlineStr">
+    <row r="75" ht="72" customHeight="1">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6345,515 +6578,555 @@
 }</t>
         </is>
       </c>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-      <c r="H73" s="10" t="n"/>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="10" t="n"/>
-      <c r="M73" s="10" t="n"/>
-      <c r="N73" s="10" t="n"/>
-      <c r="O73" s="10" t="n"/>
-      <c r="P73" s="10" t="n"/>
-      <c r="Q73" s="10" t="n"/>
-      <c r="R73" s="10" t="n"/>
-      <c r="S73" s="10" t="n"/>
-      <c r="T73" s="10" t="n"/>
-      <c r="U73" s="10" t="n"/>
-      <c r="V73" s="10" t="n"/>
-      <c r="W73" s="10" t="n"/>
-      <c r="X73" s="10" t="n"/>
-      <c r="Y73" s="10" t="n"/>
-      <c r="Z73" s="10" t="n"/>
-      <c r="AA73" s="10" t="n"/>
-      <c r="AB73" s="10" t="n"/>
-      <c r="AC73" s="10" t="n"/>
-      <c r="AD73" s="10" t="n"/>
-      <c r="AE73" s="10" t="n"/>
-      <c r="AF73" s="10" t="n"/>
-      <c r="AG73" s="10" t="n"/>
-      <c r="AH73" s="10" t="n"/>
-      <c r="AI73" s="10" t="n"/>
-      <c r="AJ73" s="10" t="n"/>
-      <c r="AK73" s="11" t="n"/>
-    </row>
-    <row r="75" ht="19.5" customHeight="1"/>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="10" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="10" t="n"/>
+      <c r="M75" s="10" t="n"/>
+      <c r="N75" s="10" t="n"/>
+      <c r="O75" s="10" t="n"/>
+      <c r="P75" s="10" t="n"/>
+      <c r="Q75" s="10" t="n"/>
+      <c r="R75" s="10" t="n"/>
+      <c r="S75" s="10" t="n"/>
+      <c r="T75" s="10" t="n"/>
+      <c r="U75" s="10" t="n"/>
+      <c r="V75" s="10" t="n"/>
+      <c r="W75" s="10" t="n"/>
+      <c r="X75" s="10" t="n"/>
+      <c r="Y75" s="10" t="n"/>
+      <c r="Z75" s="10" t="n"/>
+      <c r="AA75" s="10" t="n"/>
+      <c r="AB75" s="10" t="n"/>
+      <c r="AC75" s="10" t="n"/>
+      <c r="AD75" s="10" t="n"/>
+      <c r="AE75" s="10" t="n"/>
+      <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="11" t="n"/>
+    </row>
+    <row r="77" ht="19.5" customHeight="1"/>
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="C80" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_code：最大10桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
-          <t>tel：最大15桁</t>
+          <t>hanbaiten_code：最大10桁</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>hanbaiten_name：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
+          <t>fax：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数。デフォルト: 1</t>
+          <t>address：最大200桁</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数。デフォルト: 20</t>
+          <t>shocho_name：最大50桁</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, created_at）のみ。デフォルト: created_at</t>
+          <t>haiten_flg：Boolean型チェック。省略時は false（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>sort_order：asc または desc のみ。デフォルト: desc</t>
+          <t>page：正の整数。デフォルト: 1</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
+      <c r="D89" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100の整数。デフォルト: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="108" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, updated_at）のみ。画面のソートヘッダは hanbaiten_code / hanbaiten_name（画面設計書 v1.2 §8.1）、updated_at は既定の並び順専用。デフォルト: updated_at（最終更新が新しい順）。updated_at は新規作成・更新・取込のいずれの書き込みでも更新されるため、直近に操作した行が先頭に並ぶ。並び順には常に二次キー hanbaiten_id DESC を付与し、同一 updated_at（取込バッチ等）でも安定した順序となる</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：asc または desc のみ。デフォルト: desc（最終更新が新しい順）</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="C95" s="41" t="inlineStr">
+        <is>
           <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="D95" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="18" customHeight="1">
-      <c r="C98" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="D98" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>DataScope条件を構築する：</t>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="D100" s="41" t="inlineStr">
-        <is>
-          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="D101" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
+          <t>DataScope条件を構築する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="D103" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能。販売店代行入力時は明示的に対象 ja_id を指定する）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="D104" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
           <t>基本条件：</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="18" customHeight="1">
-      <c r="D103" s="41" t="inlineStr">
+    <row r="106" ht="18" customHeight="1">
+      <c r="D106" s="41" t="inlineStr">
         <is>
           <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
+    <row r="107" ht="36" customHeight="1">
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>**`haiten_flg = false`（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）**</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
         <is>
           <t>検索条件（指定時のみ追加）：</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="36" customHeight="1">
-      <c r="D105" s="41" t="inlineStr">
+    <row r="109" ht="36" customHeight="1">
+      <c r="D109" s="41" t="inlineStr">
         <is>
           <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="36" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
-        <is>
-          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
+          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="D114" s="41" t="inlineStr">
+        <is>
           <t>shocho_name 指定時：`shocho_name ILIKE '%' || :shocho_name || '%'`</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="115" ht="54" customHeight="1">
+      <c r="C115" s="41" t="inlineStr">
+        <is>
+          <t>都道府県表示：`m_todofuken` を `LEFT JOIN`（`m_hanbaiten.todofuken_code = m_todofuken.todofuken_code`）し、`todofuken_name` を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="180" customHeight="1">
-      <c r="C112" s="42" t="inlineStr">
+    <row r="117" ht="198" customHeight="1">
+      <c r="C117" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
-FROM m_hanbaiten
-WHERE deleted_at IS NULL
-  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="B113" s="27" t="inlineStr">
+FROM m_hanbaiten h
+WHERE h.deleted_at IS NULL
+  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="B118" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="306" customHeight="1">
-      <c r="C114" s="42" t="inlineStr">
-        <is>
-          <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
-       yubin_no, address, tel, fax, shocho_name,
-       itaku_kubun, haitatsuryo_shiharai_cycle,
-       tesuryo_kubun, tesuryo_amount,
-       created_at, updated_at
-FROM m_hanbaiten
-WHERE deleted_at IS NULL
-  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')
-ORDER BY :sort_by :sort_order
+    <row r="119" ht="360" customHeight="1">
+      <c r="C119" s="42" t="inlineStr">
+        <is>
+          <t>SELECT h.hanbaiten_id, h.ja_id, h.hanbaiten_code, h.hanbaiten_name,
+       h.todofuken_code, t.todofuken_name,
+       h.yubin_no, h.address, h.tel, h.fax, h.shocho_name,
+       h.itaku_kubun, h.haitatsuryo_shiharai_cycle,
+       h.furikomi_tesuryo_futan_kubun, h.furikomi_tesuryo, h.haiten_flg,
+       h.created_at, h.updated_at
+FROM m_hanbaiten h
+LEFT JOIN m_todofuken t ON h.todofuken_code = t.todofuken_code
+WHERE h.deleted_at IS NULL
+  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')
+ORDER BY :sort_by :sort_order, h.hanbaiten_id DESC
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="n"/>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="n"/>
-      <c r="O114" s="10" t="n"/>
-      <c r="P114" s="10" t="n"/>
-      <c r="Q114" s="10" t="n"/>
-      <c r="R114" s="10" t="n"/>
-      <c r="S114" s="10" t="n"/>
-      <c r="T114" s="10" t="n"/>
-      <c r="U114" s="10" t="n"/>
-      <c r="V114" s="10" t="n"/>
-      <c r="W114" s="10" t="n"/>
-      <c r="X114" s="10" t="n"/>
-      <c r="Y114" s="10" t="n"/>
-      <c r="Z114" s="10" t="n"/>
-      <c r="AA114" s="10" t="n"/>
-      <c r="AB114" s="10" t="n"/>
-      <c r="AC114" s="10" t="n"/>
-      <c r="AD114" s="10" t="n"/>
-      <c r="AE114" s="10" t="n"/>
-      <c r="AF114" s="10" t="n"/>
-      <c r="AG114" s="10" t="n"/>
-      <c r="AH114" s="10" t="n"/>
-      <c r="AI114" s="10" t="n"/>
-      <c r="AJ114" s="10" t="n"/>
-      <c r="AK114" s="11" t="n"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="10" t="n"/>
+      <c r="K119" s="10" t="n"/>
+      <c r="L119" s="10" t="n"/>
+      <c r="M119" s="10" t="n"/>
+      <c r="N119" s="10" t="n"/>
+      <c r="O119" s="10" t="n"/>
+      <c r="P119" s="10" t="n"/>
+      <c r="Q119" s="10" t="n"/>
+      <c r="R119" s="10" t="n"/>
+      <c r="S119" s="10" t="n"/>
+      <c r="T119" s="10" t="n"/>
+      <c r="U119" s="10" t="n"/>
+      <c r="V119" s="10" t="n"/>
+      <c r="W119" s="10" t="n"/>
+      <c r="X119" s="10" t="n"/>
+      <c r="Y119" s="10" t="n"/>
+      <c r="Z119" s="10" t="n"/>
+      <c r="AA119" s="10" t="n"/>
+      <c r="AB119" s="10" t="n"/>
+      <c r="AC119" s="10" t="n"/>
+      <c r="AD119" s="10" t="n"/>
+      <c r="AE119" s="10" t="n"/>
+      <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="10" t="n"/>
+      <c r="AK119" s="11" t="n"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="B120" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="C116" s="41" t="inlineStr">
-        <is>
-          <t>コード値をラベルにマッピングする：</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="D117" s="41" t="inlineStr">
-        <is>
-          <t>itaku_kubun：1 → 振込, 2 → 日農委託, 9 → その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="D118" s="41" t="inlineStr">
-        <is>
-          <t>tesuryo_kubun：1 → JA, 2 → 販売店</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="C120" s="41" t="inlineStr">
-        <is>
-          <t>total_pages = CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="C121" s="41" t="inlineStr">
         <is>
+          <t>列ラベルとデータの対応（画面設計書 v1.2 §6 検索結果テーブル）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="D122" s="41" t="inlineStr">
+        <is>
+          <t>「都道府県」列 → `todofuken_name`（m_todofuken JOIN）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="D123" s="41" t="inlineStr">
+        <is>
+          <t>「委託区分」列 → `itaku_kubun`（FE は `useCodesStore().label('ITAKU_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="D124" s="41" t="inlineStr">
+        <is>
+          <t>「配達手数料支払サイクル」列（旧「支払区分」）→ `haitatsuryo_shiharai_cycle`</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="54" customHeight="1">
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>「振込手数料負担区分」列（旧「手数料区分」）→ `furikomi_tesuryo_futan_kubun`（FE は `useCodesStore().label('TESURYO_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="C126" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="C127" s="41" t="inlineStr">
+        <is>
+          <t>total_pages = CEIL(total / per_page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="C128" s="41" t="inlineStr">
+        <is>
           <t>検索結果が0件の場合も空配列 `[]` を返却する（HTTP 200）。</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="B122" s="27" t="inlineStr">
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="C123" s="41" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="321">
+  <mergeCells count="339">
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D48:L48"/>
-    <mergeCell ref="A76:AK76"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
+    <mergeCell ref="M59:P59"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="B74:I74"/>
+    <mergeCell ref="C95:AK95"/>
+    <mergeCell ref="B68:I68"/>
+    <mergeCell ref="D124:AK124"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="B115:AK115"/>
-    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="D39:L39"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D81:AK81"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="B97:AK97"/>
+    <mergeCell ref="C115:AK115"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
@@ -6864,38 +7137,34 @@
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="AF31:AK31"/>
+    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D105:AK105"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="C119:AK119"/>
+    <mergeCell ref="C56:L56"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="M24:P24"/>
-    <mergeCell ref="B111:AK111"/>
-    <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
-    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
@@ -6904,11 +7173,13 @@
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
+    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
@@ -6919,10 +7190,13 @@
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="D103:AK103"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="D118:AK118"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="C38:C55"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
@@ -6930,46 +7204,38 @@
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF53:AK53"/>
-    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="C96:AK96"/>
-    <mergeCell ref="B66:I66"/>
-    <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="C116:AK116"/>
-    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C93:AK93"/>
-    <mergeCell ref="B69:I69"/>
     <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="T56:X56"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="D57:L57"/>
-    <mergeCell ref="A33:AK33"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
-    <mergeCell ref="D117:AK117"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="D45:L45"/>
-    <mergeCell ref="C37:C53"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
@@ -6977,31 +7243,36 @@
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="B62:I62"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="D122:AK122"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="C112:AK112"/>
+    <mergeCell ref="A34:AK34"/>
+    <mergeCell ref="C127:AK127"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="A78:AK78"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="D47:L47"/>
+    <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
+    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -7011,42 +7282,50 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="D90:AK90"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="T60:X60"/>
+    <mergeCell ref="C130:AK130"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="C72:AK72"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="C37:L37"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="C55:C58"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="D80:AK80"/>
+    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="B94:AK94"/>
     <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="C69:AK69"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
+    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
@@ -7058,10 +7337,14 @@
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="B100:AK100"/>
+    <mergeCell ref="D104:AK104"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M57:P57"/>
+    <mergeCell ref="M32:P32"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="N17:AK17"/>
@@ -7069,39 +7352,43 @@
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
+    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="D101:AK101"/>
-    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="M45:P45"/>
+    <mergeCell ref="D125:AK125"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="B116:AK116"/>
     <mergeCell ref="M44:P44"/>
+    <mergeCell ref="B118:AK118"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D38:L38"/>
+    <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="D107:AK107"/>
-    <mergeCell ref="B63:I63"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="T32:X32"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="M50:P50"/>
-    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="C121:AK121"/>
     <mergeCell ref="T21:X21"/>
@@ -7120,17 +7407,20 @@
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
+    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="D123:AK123"/>
+    <mergeCell ref="AF60:AK60"/>
+    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="D110:AK110"/>
-    <mergeCell ref="D85:AK85"/>
+    <mergeCell ref="D59:L59"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -7144,7 +7434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK90"/>
+  <dimension ref="A1:AK91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7305,7 +7595,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/06/22</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8268,7 +8558,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -8523,7 +8813,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "関連データが存在するため削除できません"
+  "message": "この販売店は関連オブジェクトに紐づいているため削除できません。"
 }</t>
         </is>
       </c>
@@ -8756,19 +9046,20 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="198" customHeight="1">
+    <row r="71" ht="216" customHeight="1">
       <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
-       hanbaiten_name_kana, torihikisaki_no,
+       hanbaiten_name_kana, torihikisaki_no, todofuken_code,
        yubin_no, address, tel, fax, shocho_name,
        itaku_kubun, haitatsuryo_tanka_id, haitatsuryo_shiharai_cycle,
-       tesuryo_kubun, tesuryo_amount,
+       furikomi_tesuryo_futan_kubun, furikomi_tesuryo,
        bank_code, bank_name, bank_branch_code, bank_branch_name,
-       yokin_shubetsu, koza_no, koza_meigi, biko,
+       yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
        created_at, updated_at
 FROM m_hanbaiten
 WHERE hanbaiten_id = :hanbaiten_id
+  AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
@@ -8814,10 +9105,10 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="36" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>ja_id が一致しない場合：HTTP 404 (`NOT_FOUND`)（DataScope 違反を秘匿するため、存在しないものとして扱う）</t>
         </is>
       </c>
     </row>
@@ -8929,15 +9220,22 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>エラーメッセージ：「この販売店は関連オブジェクトに紐づいているため削除できません。」（ACSMS-MSG-018-004、画面設計書 v1.2 §7.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="126" customHeight="1">
-      <c r="C80" s="42" t="inlineStr">
+    <row r="81" ht="126" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_hanbaiten
 SET deleted_at = NOW(),
@@ -8948,57 +9246,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n"/>
-      <c r="M80" s="10" t="n"/>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="10" t="n"/>
-      <c r="T80" s="10" t="n"/>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="10" t="n"/>
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="10" t="n"/>
-      <c r="AF80" s="10" t="n"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="216" customHeight="1">
-      <c r="C83" s="42" t="inlineStr">
+    <row r="84" ht="216" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9012,63 +9310,6 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="324" customHeight="1">
-      <c r="C84" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "山田新聞販売店",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区千代田1-1",
-  "tel": "0312345678",
-  "fax": "0312345679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_shiharai_cycle": 1,
-  "tesuryo_kubun": 1,
-  "tesuryo_amount": 500
-}</t>
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
@@ -9106,43 +9347,102 @@
       <c r="AJ84" s="10" t="n"/>
       <c r="AK84" s="11" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
+    <row r="85" ht="360" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "山田新聞販売店",
+  "todofuken_code": "13",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区千代田1-1",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_shiharai_cycle": 1,
+  "furikomi_tesuryo_futan_kubun": 1,
+  "furikomi_tesuryo": 500,
+  "haiten_flg": false
+}</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>削除成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="216" customHeight="1">
-      <c r="C90" s="42" t="inlineStr">
+    <row r="91" ht="216" customHeight="1">
+      <c r="C91" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9158,43 +9458,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
@@ -9208,15 +9508,14 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
@@ -9226,7 +9525,6 @@
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
@@ -9235,16 +9533,17 @@
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="J13:AK13"/>
@@ -9252,22 +9551,21 @@
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="D66:AK66"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -9281,6 +9579,7 @@
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
@@ -9297,6 +9596,8 @@
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
@@ -9310,10 +9611,10 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>

--- a/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG3"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1512,88 +1512,22 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="n"/>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>2026/05/18</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="11" t="n"/>
-      <c r="K3" s="17" t="inlineStr">
-        <is>
-          <t>Dao Van Thang</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="19" t="inlineStr">
-        <is>
-          <t>画面設計書 v1.2 対応：検索条件「廃店フラグ」追加（デフォルトは廃店=false のレコードのみ表示）、一覧レスポンスに「都道府県」（m_todofuken JOIN による todofuken_name）追加、列ラベルを「手数料区分」→「振込手数料負担区分」、「支払区分」→「配達手数料支払サイクル」に変更</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="11" t="n"/>
-      <c r="W3" s="17" t="inlineStr">
-        <is>
-          <t>Nguyen Huy Dat</t>
-        </is>
-      </c>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="11" t="n"/>
-      <c r="AB3" s="17" t="inlineStr">
-        <is>
-          <t>Nguyen Huy Dat</t>
-        </is>
-      </c>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="10" t="n"/>
-      <c r="AE3" s="10" t="n"/>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="14">
+    <mergeCell ref="H1:J1"/>
     <mergeCell ref="R1:V1"/>
+    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="W3:AA3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="R3:V3"/>
-    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K2:Q2"/>
     <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="R2:V2"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1605,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1766,7 +1700,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1989,52 +1923,8 @@
       <c r="AF20" s="10" t="n"/>
       <c r="AG20" s="11" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="C21" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>ACSMS-API-COMMON-001</t>
-        </is>
-      </c>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="19" t="inlineStr">
-        <is>
-          <t>Get Prefecture List（都道府県プルダウン取得）</t>
-        </is>
-      </c>
-      <c r="P21" s="10" t="n"/>
-      <c r="Q21" s="10" t="n"/>
-      <c r="R21" s="10" t="n"/>
-      <c r="S21" s="10" t="n"/>
-      <c r="T21" s="10" t="n"/>
-      <c r="U21" s="10" t="n"/>
-      <c r="V21" s="10" t="n"/>
-      <c r="W21" s="10" t="n"/>
-      <c r="X21" s="10" t="n"/>
-      <c r="Y21" s="10" t="n"/>
-      <c r="Z21" s="10" t="n"/>
-      <c r="AA21" s="10" t="n"/>
-      <c r="AB21" s="10" t="n"/>
-      <c r="AC21" s="10" t="n"/>
-      <c r="AD21" s="10" t="n"/>
-      <c r="AE21" s="10" t="n"/>
-      <c r="AF21" s="10" t="n"/>
-      <c r="AG21" s="11" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="O21:AG21"/>
+  <mergeCells count="29">
     <mergeCell ref="D20:N20"/>
     <mergeCell ref="D19:N19"/>
     <mergeCell ref="Z1:AC1"/>
@@ -2042,7 +1932,6 @@
     <mergeCell ref="C15:AK15"/>
     <mergeCell ref="B14:AK14"/>
     <mergeCell ref="B17:AK17"/>
-    <mergeCell ref="D21:N21"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AG3"/>
@@ -2237,7 +2126,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2805,7 +2694,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>この販売店は関連オブジェクトに紐づいているため削除できません。</t>
+          <t>関連データが存在するため削除できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -3052,7 +2941,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3326,7 +3215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK130"/>
+  <dimension ref="A1:AK123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3487,7 +3376,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4491,13 +4380,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="54" customHeight="1">
+    <row r="28" ht="18" customHeight="1">
       <c r="B28" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>haiten_flg</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4511,7 +4400,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -4542,7 +4431,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>廃店フラグ（true:廃店も含む, false:廃店を除外）。**省略時は false（廃店フラグが立っているレコードは一覧に表示しない）**。画面設計書 v1.2 §1.1 / §2.1 参照</t>
+          <t>ページ番号（1始まり）。デフォルト: 1</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4557,7 +4446,7 @@
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -4602,7 +4491,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（1始まり）。デフォルト: 1</t>
+          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -4611,13 +4500,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="B30" s="31" t="n">
         <v>9</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -4631,7 +4520,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -4662,7 +4551,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
+          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name）。デフォルト: created_at</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -4671,13 +4560,13 @@
       <c r="AJ30" s="10" t="n"/>
       <c r="AK30" s="11" t="n"/>
     </row>
-    <row r="31" ht="54" customHeight="1">
+    <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
         <v>10</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -4722,7 +4611,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name, updated_at）。デフォルト: updated_at（最終更新が新しい順）。updated_at は画面のソートヘッダではなく既定の並び順（新規作成・取込・更新直後の行を先頭に表示）</t>
+          <t>ソート順（asc, desc）。デフォルト: desc</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4731,84 +4620,88 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>sort_order</t>
-        </is>
-      </c>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="11" t="n"/>
-      <c r="Q32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="11" t="n"/>
-      <c r="Y32" s="17" t="inlineStr"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="11" t="n"/>
-      <c r="AC32" s="17" t="inlineStr"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="11" t="n"/>
-      <c r="AF32" s="19" t="inlineStr">
-        <is>
-          <t>ソート順（asc, desc）。デフォルト: desc（最終更新が新しい順）</t>
-        </is>
-      </c>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="19.5" customHeight="1"/>
-    <row r="34" ht="19.5" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
+    <row r="32" ht="19.5" customHeight="1"/>
+    <row r="33" ht="19.5" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19.5" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="B36" s="30" t="inlineStr">
+    <row r="34" ht="19.5" customHeight="1"/>
+    <row r="35" ht="19.5" customHeight="1">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="10" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="11" t="n"/>
+      <c r="T35" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="n"/>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="11" t="n"/>
+      <c r="Y35" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
+        </is>
+      </c>
+      <c r="Z35" s="10" t="n"/>
+      <c r="AA35" s="10" t="n"/>
+      <c r="AB35" s="10" t="n"/>
+      <c r="AC35" s="10" t="n"/>
+      <c r="AD35" s="10" t="n"/>
+      <c r="AE35" s="11" t="n"/>
+      <c r="AF35" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -4820,33 +4713,29 @@
       <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="n"/>
       <c r="L36" s="11" t="n"/>
-      <c r="M36" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
+      <c r="M36" s="17" t="inlineStr">
+        <is>
+          <t>Array</t>
         </is>
       </c>
       <c r="N36" s="10" t="n"/>
       <c r="O36" s="10" t="n"/>
       <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
+      <c r="Q36" s="17" t="inlineStr">
+        <is>
+          <t>〇</t>
         </is>
       </c>
       <c r="R36" s="10" t="n"/>
       <c r="S36" s="11" t="n"/>
-      <c r="T36" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
+      <c r="T36" s="17" t="inlineStr"/>
       <c r="U36" s="10" t="n"/>
       <c r="V36" s="10" t="n"/>
       <c r="W36" s="10" t="n"/>
       <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
+      <c r="Y36" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="Z36" s="10" t="n"/>
@@ -4855,9 +4744,9 @@
       <c r="AC36" s="10" t="n"/>
       <c r="AD36" s="10" t="n"/>
       <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
+      <c r="AF36" s="19" t="inlineStr">
+        <is>
+          <t>販売店データの配列</t>
         </is>
       </c>
       <c r="AG36" s="10" t="n"/>
@@ -4868,14 +4757,14 @@
     </row>
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>hanbaiten_id</t>
+        </is>
+      </c>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -4886,7 +4775,7 @@
       <c r="L37" s="11" t="n"/>
       <c r="M37" s="17" t="inlineStr">
         <is>
-          <t>Array</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
@@ -4894,7 +4783,7 @@
       <c r="P37" s="11" t="n"/>
       <c r="Q37" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R37" s="10" t="n"/>
@@ -4917,7 +4806,7 @@
       <c r="AE37" s="11" t="n"/>
       <c r="AF37" s="19" t="inlineStr">
         <is>
-          <t>販売店データの配列</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4928,12 +4817,12 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C38" s="37" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="C38" s="38" t="n"/>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_id</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E38" s="10" t="n"/>
@@ -4977,7 +4866,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4988,12 +4877,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -5006,7 +4895,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -5037,7 +4926,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店コード</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5048,12 +4937,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -5097,7 +4986,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>販売店コード</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5108,12 +4997,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5157,7 +5046,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5166,14 +5055,14 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="36" customHeight="1">
+    <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5217,7 +5106,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（m_hanbaiten.todofuken_code、2桁）</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5226,14 +5115,14 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="36" customHeight="1">
+    <row r="43" ht="18" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5277,7 +5166,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>都道府県名（m_todofuken JOIN による表示用。一覧では本項目を「都道府県」列に表示する）</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5288,12 +5177,12 @@
     </row>
     <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5337,7 +5226,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5348,12 +5237,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5397,7 +5286,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5408,12 +5297,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5426,7 +5315,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -5446,7 +5335,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -5457,7 +5346,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5468,12 +5357,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>itaku_kubun_label</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5506,7 +5395,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -5517,7 +5406,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>委託区分のラベル</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5528,12 +5417,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5546,7 +5435,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5566,7 +5455,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -5577,7 +5466,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>配達手数料支払サイクル（月数）</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5586,14 +5475,14 @@
       <c r="AJ48" s="10" t="n"/>
       <c r="AK48" s="11" t="n"/>
     </row>
-    <row r="49" ht="54" customHeight="1">
+    <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>tesuryo_kubun</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5637,7 +5526,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>委託区分（※m_code.code_category='ITAKU_KUBUN'を参照、1:振込, 2:日農委託, 9:その他）</t>
+          <t>振込手数料負担区分（1:JA, 2:販売店）</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5646,14 +5535,14 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="36" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>tesuryo_kubun_label</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -5666,7 +5555,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5697,7 +5586,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）。一覧では「配達手数料支払サイクル」列に表示する</t>
+          <t>振込手数料負担区分のラベル</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5706,14 +5595,14 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="54" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>furikomi_tesuryo_futan_kubun</t>
+          <t>tesuryo_amount</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5757,7 +5646,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分（※m_code.code_category='TESURYO_KUBUN'を参照、1:JA, 2:販売店）。一覧では「振込手数料負担区分」列に表示する</t>
+          <t>手数料金額</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5768,12 +5657,12 @@
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>furikomi_tesuryo</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -5786,7 +5675,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5799,14 +5688,18 @@
       </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="11" t="n"/>
-      <c r="T52" s="17" t="inlineStr"/>
+      <c r="T52" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
       <c r="W52" s="10" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z52" s="10" t="n"/>
@@ -5817,7 +5710,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>振込手数料</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5828,12 +5721,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="C53" s="38" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C53" s="39" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>haiten_flg</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5846,7 +5739,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -5859,14 +5752,18 @@
       </c>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="11" t="n"/>
-      <c r="T53" s="17" t="inlineStr"/>
+      <c r="T53" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
       <c r="W53" s="10" t="n"/>
       <c r="X53" s="11" t="n"/>
       <c r="Y53" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z53" s="10" t="n"/>
@@ -5877,7 +5774,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>廃店フラグ（true:廃店, false:営業中）</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5888,14 +5785,14 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C54" s="38" t="n"/>
-      <c r="D54" s="19" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="n"/>
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
@@ -5906,7 +5803,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -5919,11 +5816,7 @@
       </c>
       <c r="R54" s="10" t="n"/>
       <c r="S54" s="11" t="n"/>
-      <c r="T54" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T54" s="17" t="inlineStr"/>
       <c r="U54" s="10" t="n"/>
       <c r="V54" s="10" t="n"/>
       <c r="W54" s="10" t="n"/>
@@ -5941,7 +5834,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -5952,12 +5845,12 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C55" s="39" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="C55" s="37" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -5970,7 +5863,7 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
@@ -5983,11 +5876,7 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="inlineStr"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
@@ -6005,7 +5894,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -6016,14 +5905,14 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C56" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
       <c r="E56" s="10" t="n"/>
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
@@ -6034,7 +5923,7 @@
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
@@ -6065,7 +5954,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>現在のページ番号</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -6076,12 +5965,12 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C57" s="37" t="n"/>
+        <v>22</v>
+      </c>
+      <c r="C57" s="38" t="n"/>
       <c r="D57" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="E57" s="10" t="n"/>
@@ -6125,7 +6014,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>1ページあたりの件数</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6136,12 +6025,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="C58" s="38" t="n"/>
+        <v>23</v>
+      </c>
+      <c r="C58" s="39" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>total_pages</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -6185,7 +6074,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>総ページ数</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6194,184 +6083,64 @@
       <c r="AJ58" s="10" t="n"/>
       <c r="AK58" s="11" t="n"/>
     </row>
-    <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="C59" s="38" t="n"/>
-      <c r="D59" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
-      <c r="E59" s="10" t="n"/>
-      <c r="F59" s="10" t="n"/>
-      <c r="G59" s="10" t="n"/>
-      <c r="H59" s="10" t="n"/>
-      <c r="I59" s="10" t="n"/>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N59" s="10" t="n"/>
-      <c r="O59" s="10" t="n"/>
-      <c r="P59" s="11" t="n"/>
-      <c r="Q59" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R59" s="10" t="n"/>
-      <c r="S59" s="11" t="n"/>
-      <c r="T59" s="17" t="inlineStr"/>
-      <c r="U59" s="10" t="n"/>
-      <c r="V59" s="10" t="n"/>
-      <c r="W59" s="10" t="n"/>
-      <c r="X59" s="11" t="n"/>
-      <c r="Y59" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z59" s="10" t="n"/>
-      <c r="AA59" s="10" t="n"/>
-      <c r="AB59" s="10" t="n"/>
-      <c r="AC59" s="10" t="n"/>
-      <c r="AD59" s="10" t="n"/>
-      <c r="AE59" s="11" t="n"/>
-      <c r="AF59" s="19" t="inlineStr">
-        <is>
-          <t>1ページあたりの件数</t>
-        </is>
-      </c>
-      <c r="AG59" s="10" t="n"/>
-      <c r="AH59" s="10" t="n"/>
-      <c r="AI59" s="10" t="n"/>
-      <c r="AJ59" s="10" t="n"/>
-      <c r="AK59" s="11" t="n"/>
-    </row>
-    <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="31" t="n">
-        <v>24</v>
-      </c>
-      <c r="C60" s="39" t="n"/>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>total_pages</t>
-        </is>
-      </c>
-      <c r="E60" s="10" t="n"/>
-      <c r="F60" s="10" t="n"/>
-      <c r="G60" s="10" t="n"/>
-      <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="11" t="n"/>
-      <c r="M60" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
-        </is>
-      </c>
-      <c r="N60" s="10" t="n"/>
-      <c r="O60" s="10" t="n"/>
-      <c r="P60" s="11" t="n"/>
-      <c r="Q60" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R60" s="10" t="n"/>
-      <c r="S60" s="11" t="n"/>
-      <c r="T60" s="17" t="inlineStr"/>
-      <c r="U60" s="10" t="n"/>
-      <c r="V60" s="10" t="n"/>
-      <c r="W60" s="10" t="n"/>
-      <c r="X60" s="11" t="n"/>
-      <c r="Y60" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z60" s="10" t="n"/>
-      <c r="AA60" s="10" t="n"/>
-      <c r="AB60" s="10" t="n"/>
-      <c r="AC60" s="10" t="n"/>
-      <c r="AD60" s="10" t="n"/>
-      <c r="AE60" s="11" t="n"/>
-      <c r="AF60" s="19" t="inlineStr">
-        <is>
-          <t>総ページ数</t>
-        </is>
-      </c>
-      <c r="AG60" s="10" t="n"/>
-      <c r="AH60" s="10" t="n"/>
-      <c r="AI60" s="10" t="n"/>
-      <c r="AJ60" s="10" t="n"/>
-      <c r="AK60" s="11" t="n"/>
-    </row>
-    <row r="61" ht="19.5" customHeight="1"/>
-    <row r="62" ht="19.5" customHeight="1">
-      <c r="B62" s="40" t="inlineStr">
+    <row r="59" ht="19.5" customHeight="1"/>
+    <row r="60" ht="19.5" customHeight="1">
+      <c r="B60" s="40" t="inlineStr">
         <is>
           <t>リクエスト</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="C63" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;haiten_flg=false&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D63" s="10" t="n"/>
-      <c r="E63" s="10" t="n"/>
-      <c r="F63" s="10" t="n"/>
-      <c r="G63" s="10" t="n"/>
-      <c r="H63" s="10" t="n"/>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="10" t="n"/>
-      <c r="M63" s="10" t="n"/>
-      <c r="N63" s="10" t="n"/>
-      <c r="O63" s="10" t="n"/>
-      <c r="P63" s="10" t="n"/>
-      <c r="Q63" s="10" t="n"/>
-      <c r="R63" s="10" t="n"/>
-      <c r="S63" s="10" t="n"/>
-      <c r="T63" s="10" t="n"/>
-      <c r="U63" s="10" t="n"/>
-      <c r="V63" s="10" t="n"/>
-      <c r="W63" s="10" t="n"/>
-      <c r="X63" s="10" t="n"/>
-      <c r="Y63" s="10" t="n"/>
-      <c r="Z63" s="10" t="n"/>
-      <c r="AA63" s="10" t="n"/>
-      <c r="AB63" s="10" t="n"/>
-      <c r="AC63" s="10" t="n"/>
-      <c r="AD63" s="10" t="n"/>
-      <c r="AE63" s="10" t="n"/>
-      <c r="AF63" s="10" t="n"/>
-      <c r="AG63" s="10" t="n"/>
-      <c r="AH63" s="10" t="n"/>
-      <c r="AI63" s="10" t="n"/>
-      <c r="AJ63" s="10" t="n"/>
-      <c r="AK63" s="11" t="n"/>
-    </row>
-    <row r="65" ht="19.5" customHeight="1">
-      <c r="B65" s="40" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="C61" s="19" t="inlineStr">
+        <is>
+          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="10" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="10" t="n"/>
+      <c r="M61" s="10" t="n"/>
+      <c r="N61" s="10" t="n"/>
+      <c r="O61" s="10" t="n"/>
+      <c r="P61" s="10" t="n"/>
+      <c r="Q61" s="10" t="n"/>
+      <c r="R61" s="10" t="n"/>
+      <c r="S61" s="10" t="n"/>
+      <c r="T61" s="10" t="n"/>
+      <c r="U61" s="10" t="n"/>
+      <c r="V61" s="10" t="n"/>
+      <c r="W61" s="10" t="n"/>
+      <c r="X61" s="10" t="n"/>
+      <c r="Y61" s="10" t="n"/>
+      <c r="Z61" s="10" t="n"/>
+      <c r="AA61" s="10" t="n"/>
+      <c r="AB61" s="10" t="n"/>
+      <c r="AC61" s="10" t="n"/>
+      <c r="AD61" s="10" t="n"/>
+      <c r="AE61" s="10" t="n"/>
+      <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="11" t="n"/>
+    </row>
+    <row r="63" ht="19.5" customHeight="1">
+      <c r="B63" s="40" t="inlineStr">
         <is>
           <t>レスポンス（成功）</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="409" customHeight="1">
-      <c r="C66" s="19" t="inlineStr">
+    <row r="64" ht="409" customHeight="1">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>{
   "data": [
@@ -6380,18 +6149,17 @@
       "ja_id": 1,
       "hanbaiten_code": "H001",
       "hanbaiten_name": "山田新聞販売店",
-      "todofuken_code": "13",
-      "todofuken_name": "東京都",
       "yubin_no": "1000001",
       "address": "東京都千代田区千代田1-1",
       "tel": "0312345678",
       "fax": "0312345679",
       "shocho_name": "山田太郎",
       "itaku_kubun": 1,
+      "itaku_kubun_label": "振込",
       "haitatsuryo_shiharai_cycle": 1,
-      "furikomi_tesuryo_futan_kubun": 1,
-      "furikomi_tesuryo": 500,
-      "haiten_flg": false,
+      "tesuryo_kubun": 1,
+      "tesuryo_kubun_label": "JA",
+      "tesuryo_amount": 500,
       "created_at": "2026-01-15T10:00:00Z",
       "updated_at": "2026-03-10T14:30:00Z"
     },
@@ -6400,18 +6168,17 @@
       "ja_id": 1,
       "hanbaiten_code": "H002",
       "hanbaiten_name": "山田書店",
-      "todofuken_code": "14",
-      "todofuken_name": "神奈川県",
       "yubin_no": "1500001",
-      "address": "神奈川県横浜市西区1-2-3",
+      "address": "東京都渋谷区神宮前1-2-3",
       "tel": "0398765432",
       "fax": "0398765433",
       "shocho_name": "山田花子",
       "itaku_kubun": 2,
+      "itaku_kubun_label": "日農委託",
       "haitatsuryo_shiharai_cycle": 3,
-      "furikomi_tesuryo_futan_kubun": 2,
-      "furikomi_tesuryo": 300,
-      "haiten_flg": false,
+      "tesuryo_kubun": 2,
+      "tesuryo_kubun_label": "販売店",
+      "tesuryo_amount": 300,
       "created_at": "2026-02-01T09:00:00Z",
       "updated_at": null
     }
@@ -6425,50 +6192,50 @@
 }</t>
         </is>
       </c>
-      <c r="D66" s="10" t="n"/>
-      <c r="E66" s="10" t="n"/>
-      <c r="F66" s="10" t="n"/>
-      <c r="G66" s="10" t="n"/>
-      <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="10" t="n"/>
-      <c r="M66" s="10" t="n"/>
-      <c r="N66" s="10" t="n"/>
-      <c r="O66" s="10" t="n"/>
-      <c r="P66" s="10" t="n"/>
-      <c r="Q66" s="10" t="n"/>
-      <c r="R66" s="10" t="n"/>
-      <c r="S66" s="10" t="n"/>
-      <c r="T66" s="10" t="n"/>
-      <c r="U66" s="10" t="n"/>
-      <c r="V66" s="10" t="n"/>
-      <c r="W66" s="10" t="n"/>
-      <c r="X66" s="10" t="n"/>
-      <c r="Y66" s="10" t="n"/>
-      <c r="Z66" s="10" t="n"/>
-      <c r="AA66" s="10" t="n"/>
-      <c r="AB66" s="10" t="n"/>
-      <c r="AC66" s="10" t="n"/>
-      <c r="AD66" s="10" t="n"/>
-      <c r="AE66" s="10" t="n"/>
-      <c r="AF66" s="10" t="n"/>
-      <c r="AG66" s="10" t="n"/>
-      <c r="AH66" s="10" t="n"/>
-      <c r="AI66" s="10" t="n"/>
-      <c r="AJ66" s="10" t="n"/>
-      <c r="AK66" s="11" t="n"/>
-    </row>
-    <row r="68" ht="19.5" customHeight="1">
-      <c r="B68" s="40" t="inlineStr">
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="10" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="10" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="10" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="10" t="n"/>
+      <c r="R64" s="10" t="n"/>
+      <c r="S64" s="10" t="n"/>
+      <c r="T64" s="10" t="n"/>
+      <c r="U64" s="10" t="n"/>
+      <c r="V64" s="10" t="n"/>
+      <c r="W64" s="10" t="n"/>
+      <c r="X64" s="10" t="n"/>
+      <c r="Y64" s="10" t="n"/>
+      <c r="Z64" s="10" t="n"/>
+      <c r="AA64" s="10" t="n"/>
+      <c r="AB64" s="10" t="n"/>
+      <c r="AC64" s="10" t="n"/>
+      <c r="AD64" s="10" t="n"/>
+      <c r="AE64" s="10" t="n"/>
+      <c r="AF64" s="10" t="n"/>
+      <c r="AG64" s="10" t="n"/>
+      <c r="AH64" s="10" t="n"/>
+      <c r="AI64" s="10" t="n"/>
+      <c r="AJ64" s="10" t="n"/>
+      <c r="AK64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="B66" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="72" customHeight="1">
-      <c r="C69" s="19" t="inlineStr">
+    <row r="67" ht="72" customHeight="1">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "UNAUTHORIZED",
@@ -6476,50 +6243,50 @@
 }</t>
         </is>
       </c>
-      <c r="D69" s="10" t="n"/>
-      <c r="E69" s="10" t="n"/>
-      <c r="F69" s="10" t="n"/>
-      <c r="G69" s="10" t="n"/>
-      <c r="H69" s="10" t="n"/>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="10" t="n"/>
-      <c r="M69" s="10" t="n"/>
-      <c r="N69" s="10" t="n"/>
-      <c r="O69" s="10" t="n"/>
-      <c r="P69" s="10" t="n"/>
-      <c r="Q69" s="10" t="n"/>
-      <c r="R69" s="10" t="n"/>
-      <c r="S69" s="10" t="n"/>
-      <c r="T69" s="10" t="n"/>
-      <c r="U69" s="10" t="n"/>
-      <c r="V69" s="10" t="n"/>
-      <c r="W69" s="10" t="n"/>
-      <c r="X69" s="10" t="n"/>
-      <c r="Y69" s="10" t="n"/>
-      <c r="Z69" s="10" t="n"/>
-      <c r="AA69" s="10" t="n"/>
-      <c r="AB69" s="10" t="n"/>
-      <c r="AC69" s="10" t="n"/>
-      <c r="AD69" s="10" t="n"/>
-      <c r="AE69" s="10" t="n"/>
-      <c r="AF69" s="10" t="n"/>
-      <c r="AG69" s="10" t="n"/>
-      <c r="AH69" s="10" t="n"/>
-      <c r="AI69" s="10" t="n"/>
-      <c r="AJ69" s="10" t="n"/>
-      <c r="AK69" s="11" t="n"/>
-    </row>
-    <row r="71" ht="19.5" customHeight="1">
-      <c r="B71" s="40" t="inlineStr">
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="10" t="n"/>
+      <c r="M67" s="10" t="n"/>
+      <c r="N67" s="10" t="n"/>
+      <c r="O67" s="10" t="n"/>
+      <c r="P67" s="10" t="n"/>
+      <c r="Q67" s="10" t="n"/>
+      <c r="R67" s="10" t="n"/>
+      <c r="S67" s="10" t="n"/>
+      <c r="T67" s="10" t="n"/>
+      <c r="U67" s="10" t="n"/>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" s="10" t="n"/>
+      <c r="X67" s="10" t="n"/>
+      <c r="Y67" s="10" t="n"/>
+      <c r="Z67" s="10" t="n"/>
+      <c r="AA67" s="10" t="n"/>
+      <c r="AB67" s="10" t="n"/>
+      <c r="AC67" s="10" t="n"/>
+      <c r="AD67" s="10" t="n"/>
+      <c r="AE67" s="10" t="n"/>
+      <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="11" t="n"/>
+    </row>
+    <row r="69" ht="19.5" customHeight="1">
+      <c r="B69" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="72" customHeight="1">
-      <c r="C72" s="19" t="inlineStr">
+    <row r="70" ht="72" customHeight="1">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "FORBIDDEN",
@@ -6527,50 +6294,50 @@
 }</t>
         </is>
       </c>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="10" t="n"/>
-      <c r="M72" s="10" t="n"/>
-      <c r="N72" s="10" t="n"/>
-      <c r="O72" s="10" t="n"/>
-      <c r="P72" s="10" t="n"/>
-      <c r="Q72" s="10" t="n"/>
-      <c r="R72" s="10" t="n"/>
-      <c r="S72" s="10" t="n"/>
-      <c r="T72" s="10" t="n"/>
-      <c r="U72" s="10" t="n"/>
-      <c r="V72" s="10" t="n"/>
-      <c r="W72" s="10" t="n"/>
-      <c r="X72" s="10" t="n"/>
-      <c r="Y72" s="10" t="n"/>
-      <c r="Z72" s="10" t="n"/>
-      <c r="AA72" s="10" t="n"/>
-      <c r="AB72" s="10" t="n"/>
-      <c r="AC72" s="10" t="n"/>
-      <c r="AD72" s="10" t="n"/>
-      <c r="AE72" s="10" t="n"/>
-      <c r="AF72" s="10" t="n"/>
-      <c r="AG72" s="10" t="n"/>
-      <c r="AH72" s="10" t="n"/>
-      <c r="AI72" s="10" t="n"/>
-      <c r="AJ72" s="10" t="n"/>
-      <c r="AK72" s="11" t="n"/>
-    </row>
-    <row r="74" ht="19.5" customHeight="1">
-      <c r="B74" s="40" t="inlineStr">
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="10" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="10" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="10" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="10" t="n"/>
+      <c r="R70" s="10" t="n"/>
+      <c r="S70" s="10" t="n"/>
+      <c r="T70" s="10" t="n"/>
+      <c r="U70" s="10" t="n"/>
+      <c r="V70" s="10" t="n"/>
+      <c r="W70" s="10" t="n"/>
+      <c r="X70" s="10" t="n"/>
+      <c r="Y70" s="10" t="n"/>
+      <c r="Z70" s="10" t="n"/>
+      <c r="AA70" s="10" t="n"/>
+      <c r="AB70" s="10" t="n"/>
+      <c r="AC70" s="10" t="n"/>
+      <c r="AD70" s="10" t="n"/>
+      <c r="AE70" s="10" t="n"/>
+      <c r="AF70" s="10" t="n"/>
+      <c r="AG70" s="10" t="n"/>
+      <c r="AH70" s="10" t="n"/>
+      <c r="AI70" s="10" t="n"/>
+      <c r="AJ70" s="10" t="n"/>
+      <c r="AK70" s="11" t="n"/>
+    </row>
+    <row r="72" ht="19.5" customHeight="1">
+      <c r="B72" s="40" t="inlineStr">
         <is>
           <t>レスポンス（失敗 500 Internal Server Error）</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="72" customHeight="1">
-      <c r="C75" s="19" t="inlineStr">
+    <row r="73" ht="72" customHeight="1">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
   "error_code": "INTERNAL_SERVER_ERROR",
@@ -6578,555 +6345,515 @@
 }</t>
         </is>
       </c>
-      <c r="D75" s="10" t="n"/>
-      <c r="E75" s="10" t="n"/>
-      <c r="F75" s="10" t="n"/>
-      <c r="G75" s="10" t="n"/>
-      <c r="H75" s="10" t="n"/>
-      <c r="I75" s="10" t="n"/>
-      <c r="J75" s="10" t="n"/>
-      <c r="K75" s="10" t="n"/>
-      <c r="L75" s="10" t="n"/>
-      <c r="M75" s="10" t="n"/>
-      <c r="N75" s="10" t="n"/>
-      <c r="O75" s="10" t="n"/>
-      <c r="P75" s="10" t="n"/>
-      <c r="Q75" s="10" t="n"/>
-      <c r="R75" s="10" t="n"/>
-      <c r="S75" s="10" t="n"/>
-      <c r="T75" s="10" t="n"/>
-      <c r="U75" s="10" t="n"/>
-      <c r="V75" s="10" t="n"/>
-      <c r="W75" s="10" t="n"/>
-      <c r="X75" s="10" t="n"/>
-      <c r="Y75" s="10" t="n"/>
-      <c r="Z75" s="10" t="n"/>
-      <c r="AA75" s="10" t="n"/>
-      <c r="AB75" s="10" t="n"/>
-      <c r="AC75" s="10" t="n"/>
-      <c r="AD75" s="10" t="n"/>
-      <c r="AE75" s="10" t="n"/>
-      <c r="AF75" s="10" t="n"/>
-      <c r="AG75" s="10" t="n"/>
-      <c r="AH75" s="10" t="n"/>
-      <c r="AI75" s="10" t="n"/>
-      <c r="AJ75" s="10" t="n"/>
-      <c r="AK75" s="11" t="n"/>
-    </row>
-    <row r="77" ht="19.5" customHeight="1"/>
-    <row r="78" ht="19.5" customHeight="1">
-      <c r="A78" s="27" t="inlineStr">
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="10" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="10" t="n"/>
+      <c r="M73" s="10" t="n"/>
+      <c r="N73" s="10" t="n"/>
+      <c r="O73" s="10" t="n"/>
+      <c r="P73" s="10" t="n"/>
+      <c r="Q73" s="10" t="n"/>
+      <c r="R73" s="10" t="n"/>
+      <c r="S73" s="10" t="n"/>
+      <c r="T73" s="10" t="n"/>
+      <c r="U73" s="10" t="n"/>
+      <c r="V73" s="10" t="n"/>
+      <c r="W73" s="10" t="n"/>
+      <c r="X73" s="10" t="n"/>
+      <c r="Y73" s="10" t="n"/>
+      <c r="Z73" s="10" t="n"/>
+      <c r="AA73" s="10" t="n"/>
+      <c r="AB73" s="10" t="n"/>
+      <c r="AC73" s="10" t="n"/>
+      <c r="AD73" s="10" t="n"/>
+      <c r="AE73" s="10" t="n"/>
+      <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="11" t="n"/>
+    </row>
+    <row r="75" ht="19.5" customHeight="1"/>
+    <row r="76" ht="19.5" customHeight="1">
+      <c r="A76" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>4.1 リクエストのバリデーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="C78" s="41" t="inlineStr">
+        <is>
+          <t>クエリパラメータの検証：</t>
+        </is>
+      </c>
+    </row>
     <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
-        <is>
-          <t>4.1 リクエストのバリデーション</t>
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_code：最大10桁</t>
         </is>
       </c>
     </row>
     <row r="80" ht="18" customHeight="1">
-      <c r="C80" s="41" t="inlineStr">
-        <is>
-          <t>クエリパラメータの検証：</t>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_name：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="81" ht="18" customHeight="1">
       <c r="D81" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_code：最大10桁</t>
+          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_name：最大100桁</t>
+          <t>fax：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>tel：最大15桁</t>
+          <t>address：最大200桁</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>shocho_name：最大50桁</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>page：正の整数。デフォルト: 1</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
+          <t>per_page：1〜100の整数。デフォルト: 20</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>haiten_flg：Boolean型チェック。省略時は false（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）</t>
+          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, created_at）のみ。デフォルト: created_at</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数。デフォルト: 1</t>
+          <t>sort_order：asc または desc のみ。デフォルト: desc</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="D89" s="41" t="inlineStr">
-        <is>
-          <t>per_page：1〜100の整数。デフォルト: 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="108" customHeight="1">
+      <c r="C89" s="41" t="inlineStr">
+        <is>
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, updated_at）のみ。画面のソートヘッダは hanbaiten_code / hanbaiten_name（画面設計書 v1.2 §8.1）、updated_at は既定の並び順専用。デフォルト: updated_at（最終更新が新しい順）。updated_at は新規作成・更新・取込のいずれの書き込みでも更新されるため、直近に操作した行が先頭に並ぶ。並び順には常に二次キー hanbaiten_id DESC を付与し、同一 updated_at（取込バッチ等）でも安定した順序となる</t>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="18" customHeight="1">
-      <c r="D91" s="41" t="inlineStr">
-        <is>
-          <t>sort_order：asc または desc のみ。デフォルト: desc（最終更新が新しい順）</t>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
       <c r="C92" s="41" t="inlineStr">
         <is>
-          <t>不正なパラメータが存在する場合：</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="D93" s="41" t="inlineStr">
-        <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+      <c r="C93" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="B94" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="C95" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+      <c r="C94" s="41" t="inlineStr">
+        <is>
+          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="36" customHeight="1">
-      <c r="D98" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="C98" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="99" ht="18" customHeight="1">
       <c r="C99" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+          <t>DataScope条件を構築する：</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="B100" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="18" customHeight="1">
-      <c r="C101" s="41" t="inlineStr">
-        <is>
-          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
+      <c r="D100" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="D101" s="41" t="inlineStr">
+        <is>
+          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>DataScope条件を構築する：</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="36" customHeight="1">
+          <t>基本条件：</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
       <c r="D103" s="41" t="inlineStr">
         <is>
-          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能。販売店代行入力時は明示的に対象 ja_id を指定する）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="36" customHeight="1">
-      <c r="D104" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="18" customHeight="1">
-      <c r="C105" s="41" t="inlineStr">
-        <is>
-          <t>基本条件：</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="18" customHeight="1">
+          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="C104" s="41" t="inlineStr">
+        <is>
+          <t>検索条件（指定時のみ追加）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="D105" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
       <c r="D106" s="41" t="inlineStr">
         <is>
-          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="36" customHeight="1">
+          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
       <c r="D107" s="41" t="inlineStr">
         <is>
-          <t>**`haiten_flg = false`（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）**</t>
+          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
         </is>
       </c>
     </row>
     <row r="108" ht="18" customHeight="1">
-      <c r="C108" s="41" t="inlineStr">
-        <is>
-          <t>検索条件（指定時のみ追加）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="36" customHeight="1">
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
       <c r="D109" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
+          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+          <t>shocho_name 指定時：`shocho_name ILIKE '%' || :shocho_name || '%'`</t>
         </is>
       </c>
     </row>
     <row r="111" ht="18" customHeight="1">
-      <c r="D111" s="41" t="inlineStr">
-        <is>
-          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="18" customHeight="1">
-      <c r="D112" s="41" t="inlineStr">
-        <is>
-          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
-        </is>
-      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>4.4 データ件数の取得</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="180" customHeight="1">
+      <c r="C112" s="42" t="inlineStr">
+        <is>
+          <t>SELECT COUNT(*) AS total
+FROM m_hanbaiten
+WHERE deleted_at IS NULL
+  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="10" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="10" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="10" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="10" t="n"/>
+      <c r="R112" s="10" t="n"/>
+      <c r="S112" s="10" t="n"/>
+      <c r="T112" s="10" t="n"/>
+      <c r="U112" s="10" t="n"/>
+      <c r="V112" s="10" t="n"/>
+      <c r="W112" s="10" t="n"/>
+      <c r="X112" s="10" t="n"/>
+      <c r="Y112" s="10" t="n"/>
+      <c r="Z112" s="10" t="n"/>
+      <c r="AA112" s="10" t="n"/>
+      <c r="AB112" s="10" t="n"/>
+      <c r="AC112" s="10" t="n"/>
+      <c r="AD112" s="10" t="n"/>
+      <c r="AE112" s="10" t="n"/>
+      <c r="AF112" s="10" t="n"/>
+      <c r="AG112" s="10" t="n"/>
+      <c r="AH112" s="10" t="n"/>
+      <c r="AI112" s="10" t="n"/>
+      <c r="AJ112" s="10" t="n"/>
+      <c r="AK112" s="11" t="n"/>
     </row>
     <row r="113" ht="18" customHeight="1">
-      <c r="D113" s="41" t="inlineStr">
-        <is>
-          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="36" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
-        <is>
-          <t>shocho_name 指定時：`shocho_name ILIKE '%' || :shocho_name || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="54" customHeight="1">
-      <c r="C115" s="41" t="inlineStr">
-        <is>
-          <t>都道府県表示：`m_todofuken` を `LEFT JOIN`（`m_hanbaiten.todofuken_code = m_todofuken.todofuken_code`）し、`todofuken_name` を取得する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="B116" s="27" t="inlineStr">
-        <is>
-          <t>4.4 データ件数の取得</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="198" customHeight="1">
-      <c r="C117" s="42" t="inlineStr">
-        <is>
-          <t>SELECT COUNT(*) AS total
-FROM m_hanbaiten h
-WHERE h.deleted_at IS NULL
-  AND (:include_haiten = true OR h.haiten_flg = false)
-  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')</t>
-        </is>
-      </c>
-      <c r="D117" s="10" t="n"/>
-      <c r="E117" s="10" t="n"/>
-      <c r="F117" s="10" t="n"/>
-      <c r="G117" s="10" t="n"/>
-      <c r="H117" s="10" t="n"/>
-      <c r="I117" s="10" t="n"/>
-      <c r="J117" s="10" t="n"/>
-      <c r="K117" s="10" t="n"/>
-      <c r="L117" s="10" t="n"/>
-      <c r="M117" s="10" t="n"/>
-      <c r="N117" s="10" t="n"/>
-      <c r="O117" s="10" t="n"/>
-      <c r="P117" s="10" t="n"/>
-      <c r="Q117" s="10" t="n"/>
-      <c r="R117" s="10" t="n"/>
-      <c r="S117" s="10" t="n"/>
-      <c r="T117" s="10" t="n"/>
-      <c r="U117" s="10" t="n"/>
-      <c r="V117" s="10" t="n"/>
-      <c r="W117" s="10" t="n"/>
-      <c r="X117" s="10" t="n"/>
-      <c r="Y117" s="10" t="n"/>
-      <c r="Z117" s="10" t="n"/>
-      <c r="AA117" s="10" t="n"/>
-      <c r="AB117" s="10" t="n"/>
-      <c r="AC117" s="10" t="n"/>
-      <c r="AD117" s="10" t="n"/>
-      <c r="AE117" s="10" t="n"/>
-      <c r="AF117" s="10" t="n"/>
-      <c r="AG117" s="10" t="n"/>
-      <c r="AH117" s="10" t="n"/>
-      <c r="AI117" s="10" t="n"/>
-      <c r="AJ117" s="10" t="n"/>
-      <c r="AK117" s="11" t="n"/>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="B118" s="27" t="inlineStr">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="360" customHeight="1">
-      <c r="C119" s="42" t="inlineStr">
-        <is>
-          <t>SELECT h.hanbaiten_id, h.ja_id, h.hanbaiten_code, h.hanbaiten_name,
-       h.todofuken_code, t.todofuken_name,
-       h.yubin_no, h.address, h.tel, h.fax, h.shocho_name,
-       h.itaku_kubun, h.haitatsuryo_shiharai_cycle,
-       h.furikomi_tesuryo_futan_kubun, h.furikomi_tesuryo, h.haiten_flg,
-       h.created_at, h.updated_at
-FROM m_hanbaiten h
-LEFT JOIN m_todofuken t ON h.todofuken_code = t.todofuken_code
-WHERE h.deleted_at IS NULL
-  AND (:include_haiten = true OR h.haiten_flg = false)
-  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')
-ORDER BY :sort_by :sort_order, h.hanbaiten_id DESC
+    <row r="114" ht="306" customHeight="1">
+      <c r="C114" s="42" t="inlineStr">
+        <is>
+          <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
+       yubin_no, address, tel, fax, shocho_name,
+       itaku_kubun, haitatsuryo_shiharai_cycle,
+       tesuryo_kubun, tesuryo_amount,
+       created_at, updated_at
+FROM m_hanbaiten
+WHERE deleted_at IS NULL
+  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')
+ORDER BY :sort_by :sort_order
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D119" s="10" t="n"/>
-      <c r="E119" s="10" t="n"/>
-      <c r="F119" s="10" t="n"/>
-      <c r="G119" s="10" t="n"/>
-      <c r="H119" s="10" t="n"/>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="10" t="n"/>
-      <c r="K119" s="10" t="n"/>
-      <c r="L119" s="10" t="n"/>
-      <c r="M119" s="10" t="n"/>
-      <c r="N119" s="10" t="n"/>
-      <c r="O119" s="10" t="n"/>
-      <c r="P119" s="10" t="n"/>
-      <c r="Q119" s="10" t="n"/>
-      <c r="R119" s="10" t="n"/>
-      <c r="S119" s="10" t="n"/>
-      <c r="T119" s="10" t="n"/>
-      <c r="U119" s="10" t="n"/>
-      <c r="V119" s="10" t="n"/>
-      <c r="W119" s="10" t="n"/>
-      <c r="X119" s="10" t="n"/>
-      <c r="Y119" s="10" t="n"/>
-      <c r="Z119" s="10" t="n"/>
-      <c r="AA119" s="10" t="n"/>
-      <c r="AB119" s="10" t="n"/>
-      <c r="AC119" s="10" t="n"/>
-      <c r="AD119" s="10" t="n"/>
-      <c r="AE119" s="10" t="n"/>
-      <c r="AF119" s="10" t="n"/>
-      <c r="AG119" s="10" t="n"/>
-      <c r="AH119" s="10" t="n"/>
-      <c r="AI119" s="10" t="n"/>
-      <c r="AJ119" s="10" t="n"/>
-      <c r="AK119" s="11" t="n"/>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="10" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="10" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="10" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="10" t="n"/>
+      <c r="R114" s="10" t="n"/>
+      <c r="S114" s="10" t="n"/>
+      <c r="T114" s="10" t="n"/>
+      <c r="U114" s="10" t="n"/>
+      <c r="V114" s="10" t="n"/>
+      <c r="W114" s="10" t="n"/>
+      <c r="X114" s="10" t="n"/>
+      <c r="Y114" s="10" t="n"/>
+      <c r="Z114" s="10" t="n"/>
+      <c r="AA114" s="10" t="n"/>
+      <c r="AB114" s="10" t="n"/>
+      <c r="AC114" s="10" t="n"/>
+      <c r="AD114" s="10" t="n"/>
+      <c r="AE114" s="10" t="n"/>
+      <c r="AF114" s="10" t="n"/>
+      <c r="AG114" s="10" t="n"/>
+      <c r="AH114" s="10" t="n"/>
+      <c r="AI114" s="10" t="n"/>
+      <c r="AJ114" s="10" t="n"/>
+      <c r="AK114" s="11" t="n"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>4.6 レスポンス生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>コード値をラベルにマッピングする：</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="D117" s="41" t="inlineStr">
+        <is>
+          <t>itaku_kubun：1 → 振込, 2 → 日農委託, 9 → その他</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="D118" s="41" t="inlineStr">
+        <is>
+          <t>tesuryo_kubun：1 → JA, 2 → 販売店</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="C119" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1">
-      <c r="B120" s="27" t="inlineStr">
-        <is>
-          <t>4.6 レスポンス生成</t>
+      <c r="C120" s="41" t="inlineStr">
+        <is>
+          <t>total_pages = CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
     <row r="121" ht="18" customHeight="1">
       <c r="C121" s="41" t="inlineStr">
         <is>
-          <t>列ラベルとデータの対応（画面設計書 v1.2 §6 検索結果テーブル）：</t>
+          <t>検索結果が0件の場合も空配列 `[]` を返却する（HTTP 200）。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="18" customHeight="1">
-      <c r="D122" s="41" t="inlineStr">
-        <is>
-          <t>「都道府県」列 → `todofuken_name`（m_todofuken JOIN）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="36" customHeight="1">
-      <c r="D123" s="41" t="inlineStr">
-        <is>
-          <t>「委託区分」列 → `itaku_kubun`（FE は `useCodesStore().label('ITAKU_KUBUN', value)` でラベル解決）</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="36" customHeight="1">
-      <c r="D124" s="41" t="inlineStr">
-        <is>
-          <t>「配達手数料支払サイクル」列（旧「支払区分」）→ `haitatsuryo_shiharai_cycle`</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="54" customHeight="1">
-      <c r="D125" s="41" t="inlineStr">
-        <is>
-          <t>「振込手数料負担区分」列（旧「手数料区分」）→ `furikomi_tesuryo_futan_kubun`（FE は `useCodesStore().label('TESURYO_KUBUN', value)` でラベル解決）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="18" customHeight="1">
-      <c r="C126" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="C127" s="41" t="inlineStr">
-        <is>
-          <t>total_pages = CEIL(total / per_page)</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="18" customHeight="1">
-      <c r="C128" s="41" t="inlineStr">
-        <is>
-          <t>検索結果が0件の場合も空配列 `[]` を返却する（HTTP 200）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="B129" s="27" t="inlineStr">
+      <c r="B122" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="18" customHeight="1">
-      <c r="C130" s="41" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="C123" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="339">
+  <mergeCells count="321">
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D48:L48"/>
+    <mergeCell ref="A76:AK76"/>
     <mergeCell ref="T53:X53"/>
-    <mergeCell ref="C128:AK128"/>
+    <mergeCell ref="D56:L56"/>
     <mergeCell ref="T55:X55"/>
-    <mergeCell ref="M59:P59"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="AF22:AK22"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="B74:I74"/>
-    <mergeCell ref="C95:AK95"/>
-    <mergeCell ref="B68:I68"/>
-    <mergeCell ref="D124:AK124"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Y40:AE40"/>
+    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
+    <mergeCell ref="B115:AK115"/>
+    <mergeCell ref="B77:AK77"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
-    <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
-    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="D39:L39"/>
+    <mergeCell ref="AF35:AK35"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
     <mergeCell ref="D81:AK81"/>
-    <mergeCell ref="C115:AK115"/>
+    <mergeCell ref="C35:L35"/>
+    <mergeCell ref="B97:AK97"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
     <mergeCell ref="AF25:AK25"/>
+    <mergeCell ref="Q35:S35"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="AF30:AK30"/>
@@ -7137,34 +6864,38 @@
     <mergeCell ref="Q49:S49"/>
     <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
-    <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="Y43:AE43"/>
     <mergeCell ref="AF31:AK31"/>
-    <mergeCell ref="C63:AK63"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="AF56:AK56"/>
+    <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="D105:AK105"/>
     <mergeCell ref="M40:P40"/>
     <mergeCell ref="C119:AK119"/>
-    <mergeCell ref="C56:L56"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="M24:P24"/>
+    <mergeCell ref="B111:AK111"/>
+    <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
+    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AF39:AK39"/>
+    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
@@ -7173,13 +6904,11 @@
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
-    <mergeCell ref="C66:AK66"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="AF21:AK21"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
-    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
@@ -7190,13 +6919,10 @@
     <mergeCell ref="Q58:S58"/>
     <mergeCell ref="D103:AK103"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="Q60:S60"/>
-    <mergeCell ref="C32:L32"/>
+    <mergeCell ref="D118:AK118"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="D98:AK98"/>
     <mergeCell ref="AC31:AE31"/>
-    <mergeCell ref="C38:C55"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
@@ -7204,38 +6930,46 @@
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="C96:AK96"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="C98:AK98"/>
+    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="AF42:AK42"/>
+    <mergeCell ref="C116:AK116"/>
+    <mergeCell ref="C64:AK64"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
+    <mergeCell ref="C93:AK93"/>
+    <mergeCell ref="B69:I69"/>
     <mergeCell ref="Y30:AB30"/>
-    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="T56:X56"/>
-    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
     <mergeCell ref="D57:L57"/>
+    <mergeCell ref="A33:AK33"/>
     <mergeCell ref="Y48:AE48"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
+    <mergeCell ref="D117:AK117"/>
     <mergeCell ref="AC27:AE27"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
-    <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M22:P22"/>
-    <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="D45:L45"/>
+    <mergeCell ref="C37:C53"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
@@ -7243,36 +6977,31 @@
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="B62:I62"/>
     <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="D87:AK87"/>
-    <mergeCell ref="D122:AK122"/>
+    <mergeCell ref="B72:I72"/>
     <mergeCell ref="Q31:S31"/>
-    <mergeCell ref="Y32:AB32"/>
-    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="A34:AK34"/>
-    <mergeCell ref="C127:AK127"/>
+    <mergeCell ref="C112:AK112"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
-    <mergeCell ref="B65:I65"/>
-    <mergeCell ref="A78:AK78"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T28:X28"/>
+    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="D47:L47"/>
-    <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
     <mergeCell ref="Q44:S44"/>
+    <mergeCell ref="C104:AK104"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
-    <mergeCell ref="D89:AK89"/>
-    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -7282,50 +7011,42 @@
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
     <mergeCell ref="C99:AK99"/>
-    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="D90:AK90"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
-    <mergeCell ref="T60:X60"/>
-    <mergeCell ref="C130:AK130"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C72:AK72"/>
+    <mergeCell ref="C61:AK61"/>
     <mergeCell ref="M36:P36"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C37:L37"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="J8:AK8"/>
+    <mergeCell ref="C55:C58"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="C105:AK105"/>
-    <mergeCell ref="B94:AK94"/>
+    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="M31:P31"/>
-    <mergeCell ref="Y60:AE60"/>
+    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
-    <mergeCell ref="D91:AK91"/>
+    <mergeCell ref="C67:AK67"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Q40:S40"/>
-    <mergeCell ref="C69:AK69"/>
-    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
-    <mergeCell ref="B120:AK120"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
@@ -7337,14 +7058,10 @@
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
-    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="D86:AK86"/>
-    <mergeCell ref="B100:AK100"/>
-    <mergeCell ref="D104:AK104"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M57:P57"/>
-    <mergeCell ref="M32:P32"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="N17:AK17"/>
@@ -7352,43 +7069,39 @@
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
-    <mergeCell ref="C75:AK75"/>
     <mergeCell ref="Q1:U1"/>
     <mergeCell ref="AF36:AK36"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
+    <mergeCell ref="D101:AK101"/>
+    <mergeCell ref="C70:AK70"/>
     <mergeCell ref="M45:P45"/>
-    <mergeCell ref="D125:AK125"/>
-    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
-    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D114:AK114"/>
+    <mergeCell ref="D37:L37"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
-    <mergeCell ref="B116:AK116"/>
     <mergeCell ref="M44:P44"/>
-    <mergeCell ref="B118:AK118"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="D38:L38"/>
-    <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="D107:AK107"/>
+    <mergeCell ref="B63:I63"/>
     <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="T32:X32"/>
+    <mergeCell ref="C78:AK78"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C73:AK73"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="C121:AK121"/>
     <mergeCell ref="T21:X21"/>
@@ -7407,20 +7120,17 @@
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="B71:I71"/>
     <mergeCell ref="C92:AK92"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="D123:AK123"/>
-    <mergeCell ref="AF60:AK60"/>
+    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D85:AK85"/>
-    <mergeCell ref="D110:AK110"/>
-    <mergeCell ref="D59:L59"/>
     <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -7434,7 +7144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK91"/>
+  <dimension ref="A1:AK90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7595,7 +7305,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/06/22</t>
+          <t>2026/04/24</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8558,7 +8268,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "削除しました。"
+  "message": "正常に削除しました"
 }</t>
         </is>
       </c>
@@ -8813,7 +8523,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "この販売店は関連オブジェクトに紐づいているため削除できません。"
+  "message": "関連データが存在するため削除できません"
 }</t>
         </is>
       </c>
@@ -9046,20 +8756,19 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="216" customHeight="1">
+    <row r="71" ht="198" customHeight="1">
       <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
-       hanbaiten_name_kana, torihikisaki_no, todofuken_code,
+       hanbaiten_name_kana, torihikisaki_no,
        yubin_no, address, tel, fax, shocho_name,
        itaku_kubun, haitatsuryo_tanka_id, haitatsuryo_shiharai_cycle,
-       furikomi_tesuryo_futan_kubun, furikomi_tesuryo,
+       tesuryo_kubun, tesuryo_amount,
        bank_code, bank_name, bank_branch_code, bank_branch_name,
-       yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
+       yokin_shubetsu, koza_no, koza_meigi, biko,
        created_at, updated_at
 FROM m_hanbaiten
 WHERE hanbaiten_id = :hanbaiten_id
-  AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
@@ -9105,10 +8814,10 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="36" customHeight="1">
+    <row r="73" ht="18" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 404 (`NOT_FOUND`)（DataScope 違反を秘匿するため、存在しないものとして扱う）</t>
+          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
         </is>
       </c>
     </row>
@@ -9220,22 +8929,15 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="36" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>エラーメッセージ：「この販売店は関連オブジェクトに紐づいているため削除できません。」（ACSMS-MSG-018-004、画面設計書 v1.2 §7.2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="B79" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="126" customHeight="1">
-      <c r="C81" s="42" t="inlineStr">
+    <row r="80" ht="126" customHeight="1">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_hanbaiten
 SET deleted_at = NOW(),
@@ -9246,57 +8948,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="10" t="n"/>
-      <c r="M81" s="10" t="n"/>
-      <c r="N81" s="10" t="n"/>
-      <c r="O81" s="10" t="n"/>
-      <c r="P81" s="10" t="n"/>
-      <c r="Q81" s="10" t="n"/>
-      <c r="R81" s="10" t="n"/>
-      <c r="S81" s="10" t="n"/>
-      <c r="T81" s="10" t="n"/>
-      <c r="U81" s="10" t="n"/>
-      <c r="V81" s="10" t="n"/>
-      <c r="W81" s="10" t="n"/>
-      <c r="X81" s="10" t="n"/>
-      <c r="Y81" s="10" t="n"/>
-      <c r="Z81" s="10" t="n"/>
-      <c r="AA81" s="10" t="n"/>
-      <c r="AB81" s="10" t="n"/>
-      <c r="AC81" s="10" t="n"/>
-      <c r="AD81" s="10" t="n"/>
-      <c r="AE81" s="10" t="n"/>
-      <c r="AF81" s="10" t="n"/>
-      <c r="AG81" s="10" t="n"/>
-      <c r="AH81" s="10" t="n"/>
-      <c r="AI81" s="10" t="n"/>
-      <c r="AJ81" s="10" t="n"/>
-      <c r="AK81" s="11" t="n"/>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="10" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="10" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="10" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="10" t="n"/>
+      <c r="R80" s="10" t="n"/>
+      <c r="S80" s="10" t="n"/>
+      <c r="T80" s="10" t="n"/>
+      <c r="U80" s="10" t="n"/>
+      <c r="V80" s="10" t="n"/>
+      <c r="W80" s="10" t="n"/>
+      <c r="X80" s="10" t="n"/>
+      <c r="Y80" s="10" t="n"/>
+      <c r="Z80" s="10" t="n"/>
+      <c r="AA80" s="10" t="n"/>
+      <c r="AB80" s="10" t="n"/>
+      <c r="AC80" s="10" t="n"/>
+      <c r="AD80" s="10" t="n"/>
+      <c r="AE80" s="10" t="n"/>
+      <c r="AF80" s="10" t="n"/>
+      <c r="AG80" s="10" t="n"/>
+      <c r="AH80" s="10" t="n"/>
+      <c r="AI80" s="10" t="n"/>
+      <c r="AJ80" s="10" t="n"/>
+      <c r="AK80" s="11" t="n"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>4.6 操作ログ記録</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="B82" s="27" t="inlineStr">
-        <is>
-          <t>4.6 操作ログ記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="C83" s="41" t="inlineStr">
+      <c r="C82" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="216" customHeight="1">
-      <c r="C84" s="42" t="inlineStr">
+    <row r="83" ht="216" customHeight="1">
+      <c r="C83" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9310,6 +9012,63 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="10" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="10" t="n"/>
+      <c r="M83" s="10" t="n"/>
+      <c r="N83" s="10" t="n"/>
+      <c r="O83" s="10" t="n"/>
+      <c r="P83" s="10" t="n"/>
+      <c r="Q83" s="10" t="n"/>
+      <c r="R83" s="10" t="n"/>
+      <c r="S83" s="10" t="n"/>
+      <c r="T83" s="10" t="n"/>
+      <c r="U83" s="10" t="n"/>
+      <c r="V83" s="10" t="n"/>
+      <c r="W83" s="10" t="n"/>
+      <c r="X83" s="10" t="n"/>
+      <c r="Y83" s="10" t="n"/>
+      <c r="Z83" s="10" t="n"/>
+      <c r="AA83" s="10" t="n"/>
+      <c r="AB83" s="10" t="n"/>
+      <c r="AC83" s="10" t="n"/>
+      <c r="AD83" s="10" t="n"/>
+      <c r="AE83" s="10" t="n"/>
+      <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="11" t="n"/>
+    </row>
+    <row r="84" ht="324" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "山田新聞販売店",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区千代田1-1",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_shiharai_cycle": 1,
+  "tesuryo_kubun": 1,
+  "tesuryo_amount": 500
+}</t>
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
@@ -9347,102 +9106,43 @@
       <c r="AJ84" s="10" t="n"/>
       <c r="AK84" s="11" t="n"/>
     </row>
-    <row r="85" ht="360" customHeight="1">
-      <c r="C85" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "山田新聞販売店",
-  "todofuken_code": "13",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区千代田1-1",
-  "tel": "0312345678",
-  "fax": "0312345679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_shiharai_cycle": 1,
-  "furikomi_tesuryo_futan_kubun": 1,
-  "furikomi_tesuryo": 500,
-  "haiten_flg": false
-}</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="n"/>
-      <c r="E85" s="10" t="n"/>
-      <c r="F85" s="10" t="n"/>
-      <c r="G85" s="10" t="n"/>
-      <c r="H85" s="10" t="n"/>
-      <c r="I85" s="10" t="n"/>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="10" t="n"/>
-      <c r="M85" s="10" t="n"/>
-      <c r="N85" s="10" t="n"/>
-      <c r="O85" s="10" t="n"/>
-      <c r="P85" s="10" t="n"/>
-      <c r="Q85" s="10" t="n"/>
-      <c r="R85" s="10" t="n"/>
-      <c r="S85" s="10" t="n"/>
-      <c r="T85" s="10" t="n"/>
-      <c r="U85" s="10" t="n"/>
-      <c r="V85" s="10" t="n"/>
-      <c r="W85" s="10" t="n"/>
-      <c r="X85" s="10" t="n"/>
-      <c r="Y85" s="10" t="n"/>
-      <c r="Z85" s="10" t="n"/>
-      <c r="AA85" s="10" t="n"/>
-      <c r="AB85" s="10" t="n"/>
-      <c r="AC85" s="10" t="n"/>
-      <c r="AD85" s="10" t="n"/>
-      <c r="AE85" s="10" t="n"/>
-      <c r="AF85" s="10" t="n"/>
-      <c r="AG85" s="10" t="n"/>
-      <c r="AH85" s="10" t="n"/>
-      <c r="AI85" s="10" t="n"/>
-      <c r="AJ85" s="10" t="n"/>
-      <c r="AK85" s="11" t="n"/>
+    <row r="85" ht="18" customHeight="1">
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>4.7 レスポンス生成</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="B86" s="27" t="inlineStr">
-        <is>
-          <t>4.7 レスポンス生成</t>
+      <c r="C86" s="41" t="inlineStr">
+        <is>
+          <t>削除成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="C87" s="41" t="inlineStr">
-        <is>
-          <t>削除成功メッセージを返却する。HTTP 200。</t>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>4.8 例外処理</t>
         </is>
       </c>
     </row>
     <row r="88" ht="18" customHeight="1">
-      <c r="B88" s="27" t="inlineStr">
-        <is>
-          <t>4.8 例外処理</t>
+      <c r="C88" s="41" t="inlineStr">
+        <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="18" customHeight="1">
-      <c r="C90" s="41" t="inlineStr">
-        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="216" customHeight="1">
-      <c r="C91" s="42" t="inlineStr">
+    <row r="90" ht="216" customHeight="1">
+      <c r="C90" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9458,43 +9158,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D91" s="10" t="n"/>
-      <c r="E91" s="10" t="n"/>
-      <c r="F91" s="10" t="n"/>
-      <c r="G91" s="10" t="n"/>
-      <c r="H91" s="10" t="n"/>
-      <c r="I91" s="10" t="n"/>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="10" t="n"/>
-      <c r="M91" s="10" t="n"/>
-      <c r="N91" s="10" t="n"/>
-      <c r="O91" s="10" t="n"/>
-      <c r="P91" s="10" t="n"/>
-      <c r="Q91" s="10" t="n"/>
-      <c r="R91" s="10" t="n"/>
-      <c r="S91" s="10" t="n"/>
-      <c r="T91" s="10" t="n"/>
-      <c r="U91" s="10" t="n"/>
-      <c r="V91" s="10" t="n"/>
-      <c r="W91" s="10" t="n"/>
-      <c r="X91" s="10" t="n"/>
-      <c r="Y91" s="10" t="n"/>
-      <c r="Z91" s="10" t="n"/>
-      <c r="AA91" s="10" t="n"/>
-      <c r="AB91" s="10" t="n"/>
-      <c r="AC91" s="10" t="n"/>
-      <c r="AD91" s="10" t="n"/>
-      <c r="AE91" s="10" t="n"/>
-      <c r="AF91" s="10" t="n"/>
-      <c r="AG91" s="10" t="n"/>
-      <c r="AH91" s="10" t="n"/>
-      <c r="AI91" s="10" t="n"/>
-      <c r="AJ91" s="10" t="n"/>
-      <c r="AK91" s="11" t="n"/>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="10" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="10" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="10" t="n"/>
+      <c r="S90" s="10" t="n"/>
+      <c r="T90" s="10" t="n"/>
+      <c r="U90" s="10" t="n"/>
+      <c r="V90" s="10" t="n"/>
+      <c r="W90" s="10" t="n"/>
+      <c r="X90" s="10" t="n"/>
+      <c r="Y90" s="10" t="n"/>
+      <c r="Z90" s="10" t="n"/>
+      <c r="AA90" s="10" t="n"/>
+      <c r="AB90" s="10" t="n"/>
+      <c r="AC90" s="10" t="n"/>
+      <c r="AD90" s="10" t="n"/>
+      <c r="AE90" s="10" t="n"/>
+      <c r="AF90" s="10" t="n"/>
+      <c r="AG90" s="10" t="n"/>
+      <c r="AH90" s="10" t="n"/>
+      <c r="AI90" s="10" t="n"/>
+      <c r="AJ90" s="10" t="n"/>
+      <c r="AK90" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="121">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
@@ -9508,14 +9208,15 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
+    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
+    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
-    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
@@ -9525,6 +9226,7 @@
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
+    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
@@ -9533,17 +9235,16 @@
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
-    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
-    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="J13:AK13"/>
@@ -9551,21 +9252,22 @@
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
+    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="D66:AK66"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
-    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C28:L28"/>
+    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -9579,7 +9281,6 @@
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
-    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
@@ -9596,8 +9297,6 @@
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B52:I52"/>
-    <mergeCell ref="B88:AK88"/>
-    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
@@ -9611,10 +9310,10 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
+    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
-    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>

--- a/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
@@ -1352,7 +1352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AG4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1512,22 +1512,154 @@
       <c r="AF2" s="10" t="n"/>
       <c r="AG2" s="11" t="n"/>
     </row>
+    <row r="3" ht="19.5" customHeight="1">
+      <c r="A3" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>2026/05/18</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="11" t="n"/>
+      <c r="H3" s="17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="11" t="n"/>
+      <c r="K3" s="17" t="inlineStr">
+        <is>
+          <t>Dao Van Thang</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="11" t="n"/>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>画面設計書 v1.2 対応：検索条件「廃店フラグ」追加（デフォルトは廃店=false のレコードのみ表示）、一覧レスポンスに「都道府県」（m_todofuken JOIN による todofuken_name）追加、列ラベルを「手数料区分」→「振込手数料負担区分」、「支払区分」→「配達手数料支払サイクル」に変更</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="11" t="n"/>
+      <c r="W3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="11" t="n"/>
+      <c r="AB3" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="10" t="n"/>
+      <c r="AE3" s="10" t="n"/>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="19.5" customHeight="1">
+      <c r="A4" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>2026/07/17</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="17" t="inlineStr">
+        <is>
+          <t>Tran Duc Tuyen</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="19" t="inlineStr">
+        <is>
+          <t>顧客要件 2026-07 改訂：失効単価参照フィルタ `inactive_tanka_flg`（真偽・失効のみ）を **有効単価フラグ `active_tanka_flg`（トライステート：true=有効単価参照のみ / false=失効単価参照のみ / 省略=両方）** へ変更。UI を単価一覧(SCR-006)と同一のラジオ（有効/無効）に統一。SCR-021 の失効単価エラーからの導線(`?inactive_tanka=1`)は「無効(false)」で初期選択。非相関サブクエリの active_flg はパラメータバインド。</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="W4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="17" t="inlineStr">
+        <is>
+          <t>Nguyen Huy Dat</t>
+        </is>
+      </c>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="10" t="n"/>
+      <c r="AE4" s="10" t="n"/>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="28">
     <mergeCell ref="R1:V1"/>
-    <mergeCell ref="AB2:AG2"/>
     <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="W2:AA2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="R2:V2"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="H2:J2"/>
+    <mergeCell ref="R4:V4"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="K4:Q4"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="K3:Q3"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="W3:AA3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="R3:V3"/>
+    <mergeCell ref="AB3:AG3"/>
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W2:AA2"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="R2:V2"/>
+    <mergeCell ref="AB4:AG4"/>
     <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="C3:G3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1539,7 +1671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -1700,7 +1832,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -1923,8 +2055,52 @@
       <c r="AF20" s="10" t="n"/>
       <c r="AG20" s="11" t="n"/>
     </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="C21" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>ACSMS-API-COMMON-001</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="10" t="n"/>
+      <c r="M21" s="10" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="19" t="inlineStr">
+        <is>
+          <t>Get Prefecture List（都道府県プルダウン取得）</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="n"/>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="n"/>
+      <c r="Y21" s="10" t="n"/>
+      <c r="Z21" s="10" t="n"/>
+      <c r="AA21" s="10" t="n"/>
+      <c r="AB21" s="10" t="n"/>
+      <c r="AC21" s="10" t="n"/>
+      <c r="AD21" s="10" t="n"/>
+      <c r="AE21" s="10" t="n"/>
+      <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="11" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="31">
+    <mergeCell ref="O21:AG21"/>
     <mergeCell ref="D20:N20"/>
     <mergeCell ref="D19:N19"/>
     <mergeCell ref="Z1:AC1"/>
@@ -1932,6 +2108,7 @@
     <mergeCell ref="C15:AK15"/>
     <mergeCell ref="B14:AK14"/>
     <mergeCell ref="B17:AK17"/>
+    <mergeCell ref="D21:N21"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AD2:AG3"/>
@@ -2126,7 +2303,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2694,7 +2871,7 @@
       <c r="U14" s="11" t="n"/>
       <c r="V14" s="19" t="inlineStr">
         <is>
-          <t>関連データが存在するため削除できません。</t>
+          <t>この販売店は関連オブジェクトに紐づいているため削除できません。</t>
         </is>
       </c>
       <c r="W14" s="10" t="n"/>
@@ -2941,7 +3118,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3215,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3376,7 +3553,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4380,13 +4557,13 @@
       <c r="AJ27" s="10" t="n"/>
       <c r="AK27" s="11" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1">
+    <row r="28" ht="54" customHeight="1">
       <c r="B28" s="31" t="n">
         <v>7</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4400,7 +4577,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -4431,7 +4608,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（1始まり）。デフォルト: 1</t>
+          <t>廃店フラグ（true:廃店も含む, false:廃店を除外）。**省略時は false（廃店フラグが立っているレコードは一覧に表示しない）**。画面設計書 v1.2 §1.1 / §2.1 参照</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4440,13 +4617,13 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1">
+    <row r="29" ht="126" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>active_tanka_flg</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -4460,7 +4637,7 @@
       <c r="L29" s="11" t="n"/>
       <c r="M29" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N29" s="10" t="n"/>
@@ -4491,7 +4668,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
+          <t>有効単価フラグ（SCR-021 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する販売店のみ、`false`=失効単価(active_flg=FALSE)を参照する販売店のみ、省略=両方。参照する配達手数料単価は m_hanbaiten.haitatsuryo_tanka_id → m_tanka.tanka_type=2。配達手数料出力(SCR-021)の失効単価エラーからは `false`(無効)で初期選択される</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -4500,13 +4677,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="36" customHeight="1">
+    <row r="30" ht="18" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -4520,7 +4697,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -4551,7 +4728,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name）。デフォルト: created_at</t>
+          <t>ページ番号（1始まり）。デフォルト: 1</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -4562,11 +4739,11 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -4580,7 +4757,7 @@
       <c r="L31" s="11" t="n"/>
       <c r="M31" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N31" s="10" t="n"/>
@@ -4611,7 +4788,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc, desc）。デフォルト: desc</t>
+          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4620,151 +4797,147 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="19.5" customHeight="1"/>
-    <row r="33" ht="19.5" customHeight="1">
-      <c r="A33" s="27" t="inlineStr">
-        <is>
-          <t>3.レスポンスデータ</t>
-        </is>
-      </c>
+    <row r="32" ht="54" customHeight="1">
+      <c r="B32" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>sort_by</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="11" t="n"/>
+      <c r="Y32" s="17" t="inlineStr"/>
+      <c r="Z32" s="10" t="n"/>
+      <c r="AA32" s="10" t="n"/>
+      <c r="AB32" s="11" t="n"/>
+      <c r="AC32" s="17" t="inlineStr"/>
+      <c r="AD32" s="10" t="n"/>
+      <c r="AE32" s="11" t="n"/>
+      <c r="AF32" s="19" t="inlineStr">
+        <is>
+          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name, updated_at）。デフォルト: updated_at（最終更新が新しい順）。updated_at は画面のソートヘッダではなく既定の並び順（新規作成・取込・更新直後の行を先頭に表示）</t>
+        </is>
+      </c>
+      <c r="AG32" s="10" t="n"/>
+      <c r="AH32" s="10" t="n"/>
+      <c r="AI32" s="10" t="n"/>
+      <c r="AJ32" s="10" t="n"/>
+      <c r="AK32" s="11" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="n"/>
+      <c r="O33" s="10" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="11" t="n"/>
+      <c r="Y33" s="17" t="inlineStr"/>
+      <c r="Z33" s="10" t="n"/>
+      <c r="AA33" s="10" t="n"/>
+      <c r="AB33" s="11" t="n"/>
+      <c r="AC33" s="17" t="inlineStr"/>
+      <c r="AD33" s="10" t="n"/>
+      <c r="AE33" s="11" t="n"/>
+      <c r="AF33" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc, desc）。デフォルト: desc（最終更新が新しい順）</t>
+        </is>
+      </c>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="11" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1"/>
     <row r="35" ht="19.5" customHeight="1">
-      <c r="B35" s="30" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>3.レスポンスデータ</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19.5" customHeight="1"/>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C37" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="10" t="n"/>
-      <c r="H35" s="10" t="n"/>
-      <c r="I35" s="10" t="n"/>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N35" s="10" t="n"/>
-      <c r="O35" s="10" t="n"/>
-      <c r="P35" s="11" t="n"/>
-      <c r="Q35" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R35" s="10" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U35" s="10" t="n"/>
-      <c r="V35" s="10" t="n"/>
-      <c r="W35" s="10" t="n"/>
-      <c r="X35" s="11" t="n"/>
-      <c r="Y35" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z35" s="10" t="n"/>
-      <c r="AA35" s="10" t="n"/>
-      <c r="AB35" s="10" t="n"/>
-      <c r="AC35" s="10" t="n"/>
-      <c r="AD35" s="10" t="n"/>
-      <c r="AE35" s="11" t="n"/>
-      <c r="AF35" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG35" s="10" t="n"/>
-      <c r="AH35" s="10" t="n"/>
-      <c r="AI35" s="10" t="n"/>
-      <c r="AJ35" s="10" t="n"/>
-      <c r="AK35" s="11" t="n"/>
-    </row>
-    <row r="36" ht="18" customHeight="1">
-      <c r="B36" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="10" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="10" t="n"/>
-      <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="n"/>
-      <c r="O36" s="10" t="n"/>
-      <c r="P36" s="11" t="n"/>
-      <c r="Q36" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="R36" s="10" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="17" t="inlineStr"/>
-      <c r="U36" s="10" t="n"/>
-      <c r="V36" s="10" t="n"/>
-      <c r="W36" s="10" t="n"/>
-      <c r="X36" s="11" t="n"/>
-      <c r="Y36" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z36" s="10" t="n"/>
-      <c r="AA36" s="10" t="n"/>
-      <c r="AB36" s="10" t="n"/>
-      <c r="AC36" s="10" t="n"/>
-      <c r="AD36" s="10" t="n"/>
-      <c r="AE36" s="11" t="n"/>
-      <c r="AF36" s="19" t="inlineStr">
-        <is>
-          <t>販売店データの配列</t>
-        </is>
-      </c>
-      <c r="AG36" s="10" t="n"/>
-      <c r="AH36" s="10" t="n"/>
-      <c r="AI36" s="10" t="n"/>
-      <c r="AJ36" s="10" t="n"/>
-      <c r="AK36" s="11" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="B37" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" s="37" t="n"/>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>hanbaiten_id</t>
-        </is>
-      </c>
+      <c r="D37" s="10" t="n"/>
       <c r="E37" s="10" t="n"/>
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
@@ -4773,29 +4946,33 @@
       <c r="J37" s="10" t="n"/>
       <c r="K37" s="10" t="n"/>
       <c r="L37" s="11" t="n"/>
-      <c r="M37" s="17" t="inlineStr">
-        <is>
-          <t>Number</t>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N37" s="10" t="n"/>
       <c r="O37" s="10" t="n"/>
       <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Q37" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R37" s="10" t="n"/>
       <c r="S37" s="11" t="n"/>
-      <c r="T37" s="17" t="inlineStr"/>
+      <c r="T37" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U37" s="10" t="n"/>
       <c r="V37" s="10" t="n"/>
       <c r="W37" s="10" t="n"/>
       <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y37" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z37" s="10" t="n"/>
@@ -4804,9 +4981,9 @@
       <c r="AC37" s="10" t="n"/>
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="19" t="inlineStr">
-        <is>
-          <t>販売店ID</t>
+      <c r="AF37" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG37" s="10" t="n"/>
@@ -4817,14 +4994,14 @@
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="38" t="n"/>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>ja_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C38" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="n"/>
       <c r="E38" s="10" t="n"/>
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
@@ -4835,7 +5012,7 @@
       <c r="L38" s="11" t="n"/>
       <c r="M38" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
@@ -4843,7 +5020,7 @@
       <c r="P38" s="11" t="n"/>
       <c r="Q38" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R38" s="10" t="n"/>
@@ -4866,7 +5043,7 @@
       <c r="AE38" s="11" t="n"/>
       <c r="AF38" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店データの配列</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -4877,12 +5054,12 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C39" s="37" t="n"/>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E39" s="10" t="n"/>
@@ -4895,7 +5072,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -4926,7 +5103,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>販売店コード</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -4937,12 +5114,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -4955,7 +5132,7 @@
       <c r="L40" s="11" t="n"/>
       <c r="M40" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N40" s="10" t="n"/>
@@ -4986,7 +5163,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -4997,12 +5174,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5046,7 +5223,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>販売店コード</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5057,12 +5234,12 @@
     </row>
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5106,7 +5283,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5115,14 +5292,14 @@
       <c r="AJ42" s="10" t="n"/>
       <c r="AK42" s="11" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1">
+    <row r="43" ht="36" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5166,7 +5343,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>都道府県コード（m_hanbaiten.todofuken_code、2桁）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5175,14 +5352,14 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1">
+    <row r="44" ht="36" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5226,7 +5403,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>都道府県名（m_todofuken JOIN による表示用。一覧では本項目を「都道府県」列に表示する）</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5237,12 +5414,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5286,7 +5463,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5297,12 +5474,12 @@
     </row>
     <row r="46" ht="18" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5315,7 +5492,7 @@
       <c r="L46" s="11" t="n"/>
       <c r="M46" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N46" s="10" t="n"/>
@@ -5335,7 +5512,7 @@
       <c r="X46" s="11" t="n"/>
       <c r="Y46" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z46" s="10" t="n"/>
@@ -5346,7 +5523,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>委託区分（1:振込, 2:日農委託, 9:その他）</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5357,12 +5534,12 @@
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun_label</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5395,7 +5572,7 @@
       <c r="X47" s="11" t="n"/>
       <c r="Y47" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z47" s="10" t="n"/>
@@ -5406,7 +5583,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>委託区分のラベル</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5417,12 +5594,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5435,7 +5612,7 @@
       <c r="L48" s="11" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N48" s="10" t="n"/>
@@ -5455,7 +5632,7 @@
       <c r="X48" s="11" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z48" s="10" t="n"/>
@@ -5466,7 +5643,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5477,12 +5654,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5495,7 +5672,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N49" s="10" t="n"/>
@@ -5515,7 +5692,7 @@
       <c r="X49" s="11" t="n"/>
       <c r="Y49" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z49" s="10" t="n"/>
@@ -5526,7 +5703,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分（1:JA, 2:販売店）</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5535,14 +5712,14 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="18" customHeight="1">
+    <row r="50" ht="54" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_kubun_label</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -5555,7 +5732,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5586,7 +5763,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分のラベル</t>
+          <t>委託区分（※m_code.code_category='ITAKU_KUBUN'を参照、1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5595,14 +5772,14 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="36" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>tesuryo_amount</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5646,7 +5823,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>手数料金額</t>
+          <t>配達手数料支払サイクル（月数）。一覧では「配達手数料支払サイクル」列に表示する</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5655,14 +5832,14 @@
       <c r="AJ51" s="10" t="n"/>
       <c r="AK51" s="11" t="n"/>
     </row>
-    <row r="52" ht="18" customHeight="1">
+    <row r="52" ht="54" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>furikomi_tesuryo_futan_kubun</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -5675,7 +5852,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5688,18 +5865,14 @@
       </c>
       <c r="R52" s="10" t="n"/>
       <c r="S52" s="11" t="n"/>
-      <c r="T52" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T52" s="17" t="inlineStr"/>
       <c r="U52" s="10" t="n"/>
       <c r="V52" s="10" t="n"/>
       <c r="W52" s="10" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z52" s="10" t="n"/>
@@ -5710,7 +5883,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>振込手数料負担区分（※m_code.code_category='TESURYO_KUBUN'を参照、1:JA, 2:販売店）。一覧では「振込手数料負担区分」列に表示する</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5721,12 +5894,12 @@
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>18</v>
-      </c>
-      <c r="C53" s="39" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>furikomi_tesuryo</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5739,7 +5912,7 @@
       <c r="L53" s="11" t="n"/>
       <c r="M53" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N53" s="10" t="n"/>
@@ -5752,11 +5925,7 @@
       </c>
       <c r="R53" s="10" t="n"/>
       <c r="S53" s="11" t="n"/>
-      <c r="T53" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T53" s="17" t="inlineStr"/>
       <c r="U53" s="10" t="n"/>
       <c r="V53" s="10" t="n"/>
       <c r="W53" s="10" t="n"/>
@@ -5774,7 +5943,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>振込手数料</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5785,14 +5954,14 @@
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C54" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="19" t="inlineStr">
+        <is>
+          <t>haiten_flg</t>
+        </is>
+      </c>
       <c r="E54" s="10" t="n"/>
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
@@ -5803,7 +5972,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -5834,7 +6003,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -5845,12 +6014,12 @@
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C55" s="37" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -5863,7 +6032,7 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
@@ -5876,7 +6045,11 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr"/>
+      <c r="T55" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
@@ -5894,7 +6067,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -5905,12 +6078,12 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C56" s="38" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C56" s="39" t="n"/>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -5923,7 +6096,7 @@
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
@@ -5936,7 +6109,11 @@
       </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="11" t="n"/>
-      <c r="T56" s="17" t="inlineStr"/>
+      <c r="T56" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
       <c r="W56" s="10" t="n"/>
@@ -5954,7 +6131,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -5965,14 +6142,14 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="C57" s="38" t="n"/>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="n"/>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -5983,7 +6160,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N57" s="10" t="n"/>
@@ -6014,7 +6191,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6025,12 +6202,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="C58" s="39" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C58" s="37" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -6074,7 +6251,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6083,21 +6260,136 @@
       <c r="AJ58" s="10" t="n"/>
       <c r="AK58" s="11" t="n"/>
     </row>
-    <row r="59" ht="19.5" customHeight="1"/>
-    <row r="60" ht="19.5" customHeight="1">
-      <c r="B60" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="59" ht="18" customHeight="1">
+      <c r="B59" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N59" s="10" t="n"/>
+      <c r="O59" s="10" t="n"/>
+      <c r="P59" s="11" t="n"/>
+      <c r="Q59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="17" t="inlineStr"/>
+      <c r="U59" s="10" t="n"/>
+      <c r="V59" s="10" t="n"/>
+      <c r="W59" s="10" t="n"/>
+      <c r="X59" s="11" t="n"/>
+      <c r="Y59" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z59" s="10" t="n"/>
+      <c r="AA59" s="10" t="n"/>
+      <c r="AB59" s="10" t="n"/>
+      <c r="AC59" s="10" t="n"/>
+      <c r="AD59" s="10" t="n"/>
+      <c r="AE59" s="11" t="n"/>
+      <c r="AF59" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="11" t="n"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="11" t="n"/>
+      <c r="M60" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N60" s="10" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="11" t="n"/>
+      <c r="Q60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" s="10" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="17" t="inlineStr"/>
+      <c r="U60" s="10" t="n"/>
+      <c r="V60" s="10" t="n"/>
+      <c r="W60" s="10" t="n"/>
+      <c r="X60" s="11" t="n"/>
+      <c r="Y60" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z60" s="10" t="n"/>
+      <c r="AA60" s="10" t="n"/>
+      <c r="AB60" s="10" t="n"/>
+      <c r="AC60" s="10" t="n"/>
+      <c r="AD60" s="10" t="n"/>
+      <c r="AE60" s="11" t="n"/>
+      <c r="AF60" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG60" s="10" t="n"/>
+      <c r="AH60" s="10" t="n"/>
+      <c r="AI60" s="10" t="n"/>
+      <c r="AJ60" s="10" t="n"/>
+      <c r="AK60" s="11" t="n"/>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="C61" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="n"/>
+      <c r="B61" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="C61" s="39" t="n"/>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
       <c r="E61" s="10" t="n"/>
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
@@ -6105,91 +6397,61 @@
       <c r="I61" s="10" t="n"/>
       <c r="J61" s="10" t="n"/>
       <c r="K61" s="10" t="n"/>
-      <c r="L61" s="10" t="n"/>
-      <c r="M61" s="10" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N61" s="10" t="n"/>
       <c r="O61" s="10" t="n"/>
-      <c r="P61" s="10" t="n"/>
-      <c r="Q61" s="10" t="n"/>
+      <c r="P61" s="11" t="n"/>
+      <c r="Q61" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R61" s="10" t="n"/>
-      <c r="S61" s="10" t="n"/>
-      <c r="T61" s="10" t="n"/>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="17" t="inlineStr"/>
       <c r="U61" s="10" t="n"/>
       <c r="V61" s="10" t="n"/>
       <c r="W61" s="10" t="n"/>
-      <c r="X61" s="10" t="n"/>
-      <c r="Y61" s="10" t="n"/>
+      <c r="X61" s="11" t="n"/>
+      <c r="Y61" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z61" s="10" t="n"/>
       <c r="AA61" s="10" t="n"/>
       <c r="AB61" s="10" t="n"/>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="10" t="n"/>
-      <c r="AF61" s="10" t="n"/>
+      <c r="AE61" s="11" t="n"/>
+      <c r="AF61" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
       <c r="AG61" s="10" t="n"/>
       <c r="AH61" s="10" t="n"/>
       <c r="AI61" s="10" t="n"/>
       <c r="AJ61" s="10" t="n"/>
       <c r="AK61" s="11" t="n"/>
     </row>
+    <row r="62" ht="19.5" customHeight="1"/>
     <row r="63" ht="19.5" customHeight="1">
       <c r="B63" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="409" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
       <c r="C64" s="19" t="inlineStr">
         <is>
-          <t>{
-  "data": [
-    {
-      "hanbaiten_id": 1,
-      "ja_id": 1,
-      "hanbaiten_code": "H001",
-      "hanbaiten_name": "山田新聞販売店",
-      "yubin_no": "1000001",
-      "address": "東京都千代田区千代田1-1",
-      "tel": "0312345678",
-      "fax": "0312345679",
-      "shocho_name": "山田太郎",
-      "itaku_kubun": 1,
-      "itaku_kubun_label": "振込",
-      "haitatsuryo_shiharai_cycle": 1,
-      "tesuryo_kubun": 1,
-      "tesuryo_kubun_label": "JA",
-      "tesuryo_amount": 500,
-      "created_at": "2026-01-15T10:00:00Z",
-      "updated_at": "2026-03-10T14:30:00Z"
-    },
-    {
-      "hanbaiten_id": 2,
-      "ja_id": 1,
-      "hanbaiten_code": "H002",
-      "hanbaiten_name": "山田書店",
-      "yubin_no": "1500001",
-      "address": "東京都渋谷区神宮前1-2-3",
-      "tel": "0398765432",
-      "fax": "0398765433",
-      "shocho_name": "山田花子",
-      "itaku_kubun": 2,
-      "itaku_kubun_label": "日農委託",
-      "haitatsuryo_shiharai_cycle": 3,
-      "tesuryo_kubun": 2,
-      "tesuryo_kubun_label": "販売店",
-      "tesuryo_amount": 300,
-      "created_at": "2026-02-01T09:00:00Z",
-      "updated_at": null
-    }
-  ],
-  "meta": {
-    "total": 25,
-    "page": 1,
-    "per_page": 20,
-    "total_pages": 2
-  }
-}</t>
+          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;haiten_flg=false&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
         </is>
       </c>
       <c r="D64" s="10" t="n"/>
@@ -6230,16 +6492,62 @@
     <row r="66" ht="19.5" customHeight="1">
       <c r="B66" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="72" customHeight="1">
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="409" customHeight="1">
       <c r="C67" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "data": [
+    {
+      "hanbaiten_id": 1,
+      "ja_id": 1,
+      "hanbaiten_code": "H001",
+      "hanbaiten_name": "山田新聞販売店",
+      "todofuken_code": "13",
+      "todofuken_name": "東京都",
+      "yubin_no": "1000001",
+      "address": "東京都千代田区千代田1-1",
+      "tel": "0312345678",
+      "fax": "0312345679",
+      "shocho_name": "山田太郎",
+      "itaku_kubun": 1,
+      "haitatsuryo_shiharai_cycle": 1,
+      "furikomi_tesuryo_futan_kubun": 1,
+      "furikomi_tesuryo": 500,
+      "haiten_flg": false,
+      "created_at": "2026-01-15T10:00:00Z",
+      "updated_at": "2026-03-10T14:30:00Z"
+    },
+    {
+      "hanbaiten_id": 2,
+      "ja_id": 1,
+      "hanbaiten_code": "H002",
+      "hanbaiten_name": "山田書店",
+      "todofuken_code": "14",
+      "todofuken_name": "神奈川県",
+      "yubin_no": "1500001",
+      "address": "神奈川県横浜市西区1-2-3",
+      "tel": "0398765432",
+      "fax": "0398765433",
+      "shocho_name": "山田花子",
+      "itaku_kubun": 2,
+      "haitatsuryo_shiharai_cycle": 3,
+      "furikomi_tesuryo_futan_kubun": 2,
+      "furikomi_tesuryo": 300,
+      "haiten_flg": false,
+      "created_at": "2026-02-01T09:00:00Z",
+      "updated_at": null
+    }
+  ],
+  "meta": {
+    "total": 25,
+    "page": 1,
+    "per_page": 20,
+    "total_pages": 2
+  }
 }</t>
         </is>
       </c>
@@ -6281,7 +6589,7 @@
     <row r="69" ht="19.5" customHeight="1">
       <c r="B69" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -6289,8 +6597,8 @@
       <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
 }</t>
         </is>
       </c>
@@ -6332,7 +6640,7 @@
     <row r="72" ht="19.5" customHeight="1">
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -6340,8 +6648,8 @@
       <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
 }</t>
         </is>
       </c>
@@ -6380,522 +6688,668 @@
       <c r="AJ73" s="10" t="n"/>
       <c r="AK73" s="11" t="n"/>
     </row>
-    <row r="75" ht="19.5" customHeight="1"/>
-    <row r="76" ht="19.5" customHeight="1">
-      <c r="A76" s="27" t="inlineStr">
+    <row r="75" ht="19.5" customHeight="1">
+      <c r="B75" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="72" customHeight="1">
+      <c r="C76" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="10" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="10" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="10" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="10" t="n"/>
+      <c r="R76" s="10" t="n"/>
+      <c r="S76" s="10" t="n"/>
+      <c r="T76" s="10" t="n"/>
+      <c r="U76" s="10" t="n"/>
+      <c r="V76" s="10" t="n"/>
+      <c r="W76" s="10" t="n"/>
+      <c r="X76" s="10" t="n"/>
+      <c r="Y76" s="10" t="n"/>
+      <c r="Z76" s="10" t="n"/>
+      <c r="AA76" s="10" t="n"/>
+      <c r="AB76" s="10" t="n"/>
+      <c r="AC76" s="10" t="n"/>
+      <c r="AD76" s="10" t="n"/>
+      <c r="AE76" s="10" t="n"/>
+      <c r="AF76" s="10" t="n"/>
+      <c r="AG76" s="10" t="n"/>
+      <c r="AH76" s="10" t="n"/>
+      <c r="AI76" s="10" t="n"/>
+      <c r="AJ76" s="10" t="n"/>
+      <c r="AK76" s="11" t="n"/>
+    </row>
+    <row r="78" ht="19.5" customHeight="1"/>
+    <row r="79" ht="19.5" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="B77" s="27" t="inlineStr">
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="18" customHeight="1">
-      <c r="C78" s="41" t="inlineStr">
+    <row r="81" ht="18" customHeight="1">
+      <c r="C81" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="D79" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_code：最大10桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="D80" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name：最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="D81" s="41" t="inlineStr">
-        <is>
-          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="82" ht="18" customHeight="1">
       <c r="D82" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>hanbaiten_code：最大10桁</t>
         </is>
       </c>
     </row>
     <row r="83" ht="18" customHeight="1">
       <c r="D83" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>hanbaiten_name：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="84" ht="18" customHeight="1">
       <c r="D84" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
+          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数。デフォルト: 1</t>
+          <t>fax：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数。デフォルト: 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="36" customHeight="1">
+          <t>address：最大200桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, created_at）のみ。デフォルト: created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
+          <t>shocho_name：最大50桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>sort_order：asc または desc のみ。デフォルト: desc</t>
+          <t>haiten_flg：Boolean型チェック。省略時は false（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
-      <c r="C89" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D89" s="41" t="inlineStr">
+        <is>
+          <t>page：正の整数。デフォルト: 1</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="18" customHeight="1">
-      <c r="B91" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
+          <t>per_page：1〜100の整数。デフォルト: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="108" customHeight="1">
+      <c r="D91" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, updated_at）のみ。画面のソートヘッダは hanbaiten_code / hanbaiten_name（画面設計書 v1.2 §8.1）、updated_at は既定の並び順専用。デフォルト: updated_at（最終更新が新しい順）。updated_at は新規作成・更新・取込のいずれの書き込みでも更新されるため、直近に操作した行が先頭に並ぶ。並び順には常に二次キー hanbaiten_id DESC を付与し、同一 updated_at（取込バッチ等）でも安定した順序となる</t>
         </is>
       </c>
     </row>
     <row r="92" ht="18" customHeight="1">
-      <c r="C92" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+      <c r="D92" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：asc または desc のみ。デフォルト: desc（最終更新が新しい順）</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
       <c r="C93" s="41" t="inlineStr">
         <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+          <t>不正なパラメータが存在する場合：</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
-      <c r="C94" s="41" t="inlineStr">
-        <is>
-          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="36" customHeight="1">
-      <c r="D95" s="41" t="inlineStr">
-        <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+      <c r="D94" s="41" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request を返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="96" ht="18" customHeight="1">
       <c r="C96" s="41" t="inlineStr">
         <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="B97" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="C97" s="41" t="inlineStr">
+        <is>
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="18" customHeight="1">
-      <c r="C99" s="41" t="inlineStr">
-        <is>
-          <t>DataScope条件を構築する：</t>
+          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="D99" s="41" t="inlineStr">
+        <is>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="D100" s="41" t="inlineStr">
-        <is>
-          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="36" customHeight="1">
-      <c r="D101" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
+      <c r="C100" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>基本条件：</t>
+          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
         </is>
       </c>
     </row>
     <row r="103" ht="18" customHeight="1">
-      <c r="D103" s="41" t="inlineStr">
-        <is>
-          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="18" customHeight="1">
-      <c r="C104" s="41" t="inlineStr">
-        <is>
-          <t>検索条件（指定時のみ追加）：</t>
+      <c r="C103" s="41" t="inlineStr">
+        <is>
+          <t>DataScope条件を構築する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="D104" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能。販売店代行入力時は明示的に対象 ja_id を指定する）</t>
         </is>
       </c>
     </row>
     <row r="105" ht="36" customHeight="1">
       <c r="D105" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="36" customHeight="1">
-      <c r="D106" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="C106" s="41" t="inlineStr">
+        <is>
+          <t>基本条件：</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
       <c r="D107" s="41" t="inlineStr">
         <is>
-          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="18" customHeight="1">
+          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
       <c r="D108" s="41" t="inlineStr">
         <is>
-          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+          <t>**`haiten_flg = false`（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）**</t>
         </is>
       </c>
     </row>
     <row r="109" ht="18" customHeight="1">
-      <c r="D109" s="41" t="inlineStr">
-        <is>
-          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
+      <c r="C109" s="41" t="inlineStr">
+        <is>
+          <t>検索条件（指定時のみ追加）：</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
+          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="D111" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="D112" s="41" t="inlineStr">
+        <is>
+          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="D113" s="41" t="inlineStr">
+        <is>
+          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="D114" s="41" t="inlineStr">
+        <is>
+          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="36" customHeight="1">
+      <c r="D115" s="41" t="inlineStr">
+        <is>
           <t>shocho_name 指定時：`shocho_name ILIKE '%' || :shocho_name || '%'`</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="B111" s="27" t="inlineStr">
+    <row r="116" ht="108" customHeight="1">
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>active_tanka_flg 指定時：`true`=参照する配達手数料単価が有効(active_flg=TRUE)の販売店のみ、`false`=失効(active_flg=FALSE)の販売店のみ抽出（省略時は絞り込まない）。非相関サブクエリ IN で判定する（getManyAndCount のページング経路を壊さず、pg-mem でも動作）。active_flg はパラメータ（`:activeTankaFlg`）でバインドする。`haitatsuryo_tanka_id` が NULL の販売店は `NULL IN (...)` が真にならず除外される。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="108" customHeight="1">
+      <c r="C117" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    AND m.haitatsuryo_tanka_id IN (
+      SELECT mti.tanka_id FROM m_tanka mti
+       WHERE mti.tanka_type = 2
+         AND mti.deleted_at IS NULL
+         AND mti.active_flg = FALSE
+    )</t>
+        </is>
+      </c>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="10" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="10" t="n"/>
+      <c r="M117" s="10" t="n"/>
+      <c r="N117" s="10" t="n"/>
+      <c r="O117" s="10" t="n"/>
+      <c r="P117" s="10" t="n"/>
+      <c r="Q117" s="10" t="n"/>
+      <c r="R117" s="10" t="n"/>
+      <c r="S117" s="10" t="n"/>
+      <c r="T117" s="10" t="n"/>
+      <c r="U117" s="10" t="n"/>
+      <c r="V117" s="10" t="n"/>
+      <c r="W117" s="10" t="n"/>
+      <c r="X117" s="10" t="n"/>
+      <c r="Y117" s="10" t="n"/>
+      <c r="Z117" s="10" t="n"/>
+      <c r="AA117" s="10" t="n"/>
+      <c r="AB117" s="10" t="n"/>
+      <c r="AC117" s="10" t="n"/>
+      <c r="AD117" s="10" t="n"/>
+      <c r="AE117" s="10" t="n"/>
+      <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="11" t="n"/>
+    </row>
+    <row r="118" ht="54" customHeight="1">
+      <c r="C118" s="41" t="inlineStr">
+        <is>
+          <t>都道府県表示：`m_todofuken` を `LEFT JOIN`（`m_hanbaiten.todofuken_code = m_todofuken.todofuken_code`）し、`todofuken_name` を取得する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="B119" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="180" customHeight="1">
-      <c r="C112" s="42" t="inlineStr">
+    <row r="120" ht="198" customHeight="1">
+      <c r="C120" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
-FROM m_hanbaiten
-WHERE deleted_at IS NULL
-  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')</t>
-        </is>
-      </c>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="10" t="n"/>
-      <c r="K112" s="10" t="n"/>
-      <c r="L112" s="10" t="n"/>
-      <c r="M112" s="10" t="n"/>
-      <c r="N112" s="10" t="n"/>
-      <c r="O112" s="10" t="n"/>
-      <c r="P112" s="10" t="n"/>
-      <c r="Q112" s="10" t="n"/>
-      <c r="R112" s="10" t="n"/>
-      <c r="S112" s="10" t="n"/>
-      <c r="T112" s="10" t="n"/>
-      <c r="U112" s="10" t="n"/>
-      <c r="V112" s="10" t="n"/>
-      <c r="W112" s="10" t="n"/>
-      <c r="X112" s="10" t="n"/>
-      <c r="Y112" s="10" t="n"/>
-      <c r="Z112" s="10" t="n"/>
-      <c r="AA112" s="10" t="n"/>
-      <c r="AB112" s="10" t="n"/>
-      <c r="AC112" s="10" t="n"/>
-      <c r="AD112" s="10" t="n"/>
-      <c r="AE112" s="10" t="n"/>
-      <c r="AF112" s="10" t="n"/>
-      <c r="AG112" s="10" t="n"/>
-      <c r="AH112" s="10" t="n"/>
-      <c r="AI112" s="10" t="n"/>
-      <c r="AJ112" s="10" t="n"/>
-      <c r="AK112" s="11" t="n"/>
-    </row>
-    <row r="113" ht="18" customHeight="1">
-      <c r="B113" s="27" t="inlineStr">
+FROM m_hanbaiten h
+WHERE h.deleted_at IS NULL
+  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="10" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="10" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="10" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="10" t="n"/>
+      <c r="R120" s="10" t="n"/>
+      <c r="S120" s="10" t="n"/>
+      <c r="T120" s="10" t="n"/>
+      <c r="U120" s="10" t="n"/>
+      <c r="V120" s="10" t="n"/>
+      <c r="W120" s="10" t="n"/>
+      <c r="X120" s="10" t="n"/>
+      <c r="Y120" s="10" t="n"/>
+      <c r="Z120" s="10" t="n"/>
+      <c r="AA120" s="10" t="n"/>
+      <c r="AB120" s="10" t="n"/>
+      <c r="AC120" s="10" t="n"/>
+      <c r="AD120" s="10" t="n"/>
+      <c r="AE120" s="10" t="n"/>
+      <c r="AF120" s="10" t="n"/>
+      <c r="AG120" s="10" t="n"/>
+      <c r="AH120" s="10" t="n"/>
+      <c r="AI120" s="10" t="n"/>
+      <c r="AJ120" s="10" t="n"/>
+      <c r="AK120" s="11" t="n"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="B121" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="306" customHeight="1">
-      <c r="C114" s="42" t="inlineStr">
-        <is>
-          <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
-       yubin_no, address, tel, fax, shocho_name,
-       itaku_kubun, haitatsuryo_shiharai_cycle,
-       tesuryo_kubun, tesuryo_amount,
-       created_at, updated_at
-FROM m_hanbaiten
-WHERE deleted_at IS NULL
-  AND (:role_code = 'NICHINO_STAFF' OR ja_id = :ja_id)
-  AND (:hanbaiten_code IS NULL OR hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
-  AND (:hanbaiten_name IS NULL OR hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
-  AND (:tel IS NULL OR tel ILIKE '%' || :tel || '%')
-  AND (:fax IS NULL OR fax ILIKE '%' || :fax || '%')
-  AND (:address IS NULL OR address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR shocho_name ILIKE '%' || :shocho_name || '%')
-ORDER BY :sort_by :sort_order
+    <row r="122" ht="360" customHeight="1">
+      <c r="C122" s="42" t="inlineStr">
+        <is>
+          <t>SELECT h.hanbaiten_id, h.ja_id, h.hanbaiten_code, h.hanbaiten_name,
+       h.todofuken_code, t.todofuken_name,
+       h.yubin_no, h.address, h.tel, h.fax, h.shocho_name,
+       h.itaku_kubun, h.haitatsuryo_shiharai_cycle,
+       h.furikomi_tesuryo_futan_kubun, h.furikomi_tesuryo, h.haiten_flg,
+       h.created_at, h.updated_at
+FROM m_hanbaiten h
+LEFT JOIN m_todofuken t ON h.todofuken_code = t.todofuken_code
+WHERE h.deleted_at IS NULL
+  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
+  AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
+  AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
+  AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
+  AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
+  AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
+  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')
+ORDER BY :sort_by :sort_order, h.hanbaiten_id DESC
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D114" s="10" t="n"/>
-      <c r="E114" s="10" t="n"/>
-      <c r="F114" s="10" t="n"/>
-      <c r="G114" s="10" t="n"/>
-      <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="10" t="n"/>
-      <c r="K114" s="10" t="n"/>
-      <c r="L114" s="10" t="n"/>
-      <c r="M114" s="10" t="n"/>
-      <c r="N114" s="10" t="n"/>
-      <c r="O114" s="10" t="n"/>
-      <c r="P114" s="10" t="n"/>
-      <c r="Q114" s="10" t="n"/>
-      <c r="R114" s="10" t="n"/>
-      <c r="S114" s="10" t="n"/>
-      <c r="T114" s="10" t="n"/>
-      <c r="U114" s="10" t="n"/>
-      <c r="V114" s="10" t="n"/>
-      <c r="W114" s="10" t="n"/>
-      <c r="X114" s="10" t="n"/>
-      <c r="Y114" s="10" t="n"/>
-      <c r="Z114" s="10" t="n"/>
-      <c r="AA114" s="10" t="n"/>
-      <c r="AB114" s="10" t="n"/>
-      <c r="AC114" s="10" t="n"/>
-      <c r="AD114" s="10" t="n"/>
-      <c r="AE114" s="10" t="n"/>
-      <c r="AF114" s="10" t="n"/>
-      <c r="AG114" s="10" t="n"/>
-      <c r="AH114" s="10" t="n"/>
-      <c r="AI114" s="10" t="n"/>
-      <c r="AJ114" s="10" t="n"/>
-      <c r="AK114" s="11" t="n"/>
-    </row>
-    <row r="115" ht="18" customHeight="1">
-      <c r="B115" s="27" t="inlineStr">
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="n"/>
+      <c r="J122" s="10" t="n"/>
+      <c r="K122" s="10" t="n"/>
+      <c r="L122" s="10" t="n"/>
+      <c r="M122" s="10" t="n"/>
+      <c r="N122" s="10" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="10" t="n"/>
+      <c r="Q122" s="10" t="n"/>
+      <c r="R122" s="10" t="n"/>
+      <c r="S122" s="10" t="n"/>
+      <c r="T122" s="10" t="n"/>
+      <c r="U122" s="10" t="n"/>
+      <c r="V122" s="10" t="n"/>
+      <c r="W122" s="10" t="n"/>
+      <c r="X122" s="10" t="n"/>
+      <c r="Y122" s="10" t="n"/>
+      <c r="Z122" s="10" t="n"/>
+      <c r="AA122" s="10" t="n"/>
+      <c r="AB122" s="10" t="n"/>
+      <c r="AC122" s="10" t="n"/>
+      <c r="AD122" s="10" t="n"/>
+      <c r="AE122" s="10" t="n"/>
+      <c r="AF122" s="10" t="n"/>
+      <c r="AG122" s="10" t="n"/>
+      <c r="AH122" s="10" t="n"/>
+      <c r="AI122" s="10" t="n"/>
+      <c r="AJ122" s="10" t="n"/>
+      <c r="AK122" s="11" t="n"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="B123" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="18" customHeight="1">
-      <c r="C116" s="41" t="inlineStr">
-        <is>
-          <t>コード値をラベルにマッピングする：</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="18" customHeight="1">
-      <c r="D117" s="41" t="inlineStr">
-        <is>
-          <t>itaku_kubun：1 → 振込, 2 → 日農委託, 9 → その他</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="18" customHeight="1">
-      <c r="D118" s="41" t="inlineStr">
-        <is>
-          <t>tesuryo_kubun：1 → JA, 2 → 販売店</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="C119" s="41" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="C124" s="41" t="inlineStr">
+        <is>
+          <t>列ラベルとデータの対応（画面設計書 v1.2 §6 検索結果テーブル）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="D125" s="41" t="inlineStr">
+        <is>
+          <t>「都道府県」列 → `todofuken_name`（m_todofuken JOIN）</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="D126" s="41" t="inlineStr">
+        <is>
+          <t>「委託区分」列 → `itaku_kubun`（FE は `useCodesStore().label('ITAKU_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="D127" s="41" t="inlineStr">
+        <is>
+          <t>「配達手数料支払サイクル」列（旧「支払区分」）→ `haitatsuryo_shiharai_cycle`</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="54" customHeight="1">
+      <c r="D128" s="41" t="inlineStr">
+        <is>
+          <t>「振込手数料負担区分」列（旧「手数料区分」）→ `furikomi_tesuryo_futan_kubun`（FE は `useCodesStore().label('TESURYO_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="C129" s="41" t="inlineStr">
         <is>
           <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="18" customHeight="1">
-      <c r="C120" s="41" t="inlineStr">
+    <row r="130" ht="18" customHeight="1">
+      <c r="C130" s="41" t="inlineStr">
         <is>
           <t>total_pages = CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="C121" s="41" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="C131" s="41" t="inlineStr">
         <is>
           <t>検索結果が0件の場合も空配列 `[]` を返却する（HTTP 200）。</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="18" customHeight="1">
-      <c r="B122" s="27" t="inlineStr">
+    <row r="132" ht="18" customHeight="1">
+      <c r="B132" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="C123" s="41" t="inlineStr">
+    <row r="133" ht="18" customHeight="1">
+      <c r="C133" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="321">
+  <mergeCells count="348">
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
+    <mergeCell ref="D61:L61"/>
     <mergeCell ref="D48:L48"/>
-    <mergeCell ref="A76:AK76"/>
     <mergeCell ref="T53:X53"/>
     <mergeCell ref="D56:L56"/>
     <mergeCell ref="T55:X55"/>
+    <mergeCell ref="M59:P59"/>
     <mergeCell ref="B8:I8"/>
+    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
-    <mergeCell ref="C94:AK94"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF22:AK22"/>
+    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="C22:L22"/>
+    <mergeCell ref="Q33:S33"/>
     <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="B113:AK113"/>
     <mergeCell ref="T37:X37"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="B115:AK115"/>
-    <mergeCell ref="B77:AK77"/>
+    <mergeCell ref="D126:AK126"/>
+    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="C38:L38"/>
+    <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
+    <mergeCell ref="Q61:S61"/>
     <mergeCell ref="D39:L39"/>
-    <mergeCell ref="AF35:AK35"/>
-    <mergeCell ref="D79:AK79"/>
+    <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="Y55:AE55"/>
+    <mergeCell ref="C117:AK117"/>
     <mergeCell ref="T40:X40"/>
-    <mergeCell ref="D81:AK81"/>
-    <mergeCell ref="C35:L35"/>
-    <mergeCell ref="B97:AK97"/>
+    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="M27:P27"/>
     <mergeCell ref="Y37:AE37"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="Q35:S35"/>
+    <mergeCell ref="C58:C61"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
+    <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="Y41:AE41"/>
+    <mergeCell ref="D92:AK92"/>
     <mergeCell ref="AC25:AE25"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="Q49:S49"/>
-    <mergeCell ref="Q36:S36"/>
     <mergeCell ref="Y56:AE56"/>
+    <mergeCell ref="T59:X59"/>
     <mergeCell ref="C30:L30"/>
     <mergeCell ref="Q30:S30"/>
     <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="D94:AK94"/>
     <mergeCell ref="AF31:AK31"/>
     <mergeCell ref="T51:X51"/>
     <mergeCell ref="T26:X26"/>
     <mergeCell ref="AF56:AK56"/>
-    <mergeCell ref="C54:L54"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="D105:AK105"/>
     <mergeCell ref="M40:P40"/>
-    <mergeCell ref="C119:AK119"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
+    <mergeCell ref="B121:AK121"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="M24:P24"/>
-    <mergeCell ref="B111:AK111"/>
-    <mergeCell ref="T35:X35"/>
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="D58:L58"/>
     <mergeCell ref="Y38:AE38"/>
-    <mergeCell ref="D100:AK100"/>
     <mergeCell ref="Q57:S57"/>
     <mergeCell ref="AF28:AK28"/>
     <mergeCell ref="C29:L29"/>
+    <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AF39:AK39"/>
     <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
-    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
@@ -6904,72 +7358,81 @@
     <mergeCell ref="M46:P46"/>
     <mergeCell ref="M37:P37"/>
     <mergeCell ref="AC30:AE30"/>
+    <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="AF21:AK21"/>
+    <mergeCell ref="C57:L57"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
+    <mergeCell ref="D113:AK113"/>
     <mergeCell ref="M43:P43"/>
     <mergeCell ref="AF23:AK23"/>
     <mergeCell ref="AF50:AK50"/>
+    <mergeCell ref="D115:AK115"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="T22:X22"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
+    <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
-    <mergeCell ref="D103:AK103"/>
     <mergeCell ref="AF44:AK44"/>
-    <mergeCell ref="D118:AK118"/>
+    <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="C32:L32"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
+    <mergeCell ref="B132:AK132"/>
+    <mergeCell ref="B119:AK119"/>
     <mergeCell ref="AC31:AE31"/>
+    <mergeCell ref="C103:AK103"/>
+    <mergeCell ref="C118:AK118"/>
     <mergeCell ref="M51:P51"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="T46:X46"/>
+    <mergeCell ref="D116:AK116"/>
     <mergeCell ref="AF53:AK53"/>
-    <mergeCell ref="B122:AK122"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="C96:AK96"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="C98:AK98"/>
-    <mergeCell ref="C89:AK89"/>
     <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="C116:AK116"/>
     <mergeCell ref="C64:AK64"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
     <mergeCell ref="C93:AK93"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
-    <mergeCell ref="Y35:AE35"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="Y29:AB29"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="Q21:S21"/>
     <mergeCell ref="T56:X56"/>
+    <mergeCell ref="AC32:AE32"/>
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
-    <mergeCell ref="T36:X36"/>
     <mergeCell ref="Y46:AE46"/>
-    <mergeCell ref="D57:L57"/>
-    <mergeCell ref="A33:AK33"/>
+    <mergeCell ref="Y61:AE61"/>
     <mergeCell ref="Y48:AE48"/>
+    <mergeCell ref="A35:AK35"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
-    <mergeCell ref="D117:AK117"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
+    <mergeCell ref="D60:L60"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M22:P22"/>
+    <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="Y59:AE59"/>
     <mergeCell ref="C21:L21"/>
     <mergeCell ref="D45:L45"/>
-    <mergeCell ref="C37:C53"/>
     <mergeCell ref="M42:P42"/>
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Y28:AB28"/>
@@ -6977,31 +7440,34 @@
     <mergeCell ref="Y49:AE49"/>
     <mergeCell ref="C23:L23"/>
     <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="Y36:AE36"/>
     <mergeCell ref="D87:AK87"/>
+    <mergeCell ref="T33:X33"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="Q31:S31"/>
+    <mergeCell ref="Y32:AB32"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="C112:AK112"/>
+    <mergeCell ref="C109:AK109"/>
+    <mergeCell ref="C133:AK133"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="C114:AK114"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T28:X28"/>
-    <mergeCell ref="B91:AK91"/>
     <mergeCell ref="T30:X30"/>
     <mergeCell ref="T57:X57"/>
     <mergeCell ref="T29:X29"/>
     <mergeCell ref="D53:L53"/>
     <mergeCell ref="D47:L47"/>
+    <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
+    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C104:AK104"/>
+    <mergeCell ref="C39:C56"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
+    <mergeCell ref="D89:AK89"/>
+    <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="AF26:AK26"/>
     <mergeCell ref="C24:L24"/>
@@ -7010,41 +7476,42 @@
     <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
-    <mergeCell ref="C99:AK99"/>
+    <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
     <mergeCell ref="D90:AK90"/>
     <mergeCell ref="J13:AK13"/>
     <mergeCell ref="AF27:AK27"/>
     <mergeCell ref="Q47:S47"/>
+    <mergeCell ref="T60:X60"/>
+    <mergeCell ref="C130:AK130"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="C122:AK122"/>
     <mergeCell ref="Q50:S50"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
+    <mergeCell ref="C37:L37"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
     <mergeCell ref="T44:X44"/>
     <mergeCell ref="J8:AK8"/>
-    <mergeCell ref="C55:C58"/>
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="J10:AK10"/>
-    <mergeCell ref="D80:AK80"/>
     <mergeCell ref="M31:P31"/>
     <mergeCell ref="C120:AK120"/>
+    <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
     <mergeCell ref="Q38:S38"/>
     <mergeCell ref="C67:AK67"/>
+    <mergeCell ref="D91:AK91"/>
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
-    <mergeCell ref="D106:AK106"/>
     <mergeCell ref="Q40:S40"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="Y42:AE42"/>
@@ -7052,16 +7519,19 @@
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="Y58:AE58"/>
-    <mergeCell ref="D109:AK109"/>
     <mergeCell ref="AF46:AK46"/>
     <mergeCell ref="D84:AK84"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AF61:AK61"/>
+    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="D104:AK104"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M57:P57"/>
+    <mergeCell ref="M32:P32"/>
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="N17:AK17"/>
@@ -7070,45 +7540,52 @@
     <mergeCell ref="Q41:S41"/>
     <mergeCell ref="D42:L42"/>
     <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="AF36:AK36"/>
+    <mergeCell ref="D99:AK99"/>
     <mergeCell ref="Q56:S56"/>
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="D101:AK101"/>
+    <mergeCell ref="B123:AK123"/>
     <mergeCell ref="C70:AK70"/>
+    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="M45:P45"/>
+    <mergeCell ref="B75:I75"/>
+    <mergeCell ref="D125:AK125"/>
+    <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="D127:AK127"/>
+    <mergeCell ref="D114:AK114"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AF38:AK38"/>
-    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
     <mergeCell ref="Y26:AB26"/>
+    <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="D107:AK107"/>
     <mergeCell ref="B63:I63"/>
-    <mergeCell ref="C36:L36"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
+    <mergeCell ref="AC33:AE33"/>
     <mergeCell ref="T39:X39"/>
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
-    <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="T32:X32"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
     <mergeCell ref="M50:P50"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="M55:P55"/>
-    <mergeCell ref="C121:AK121"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="M48:P48"/>
     <mergeCell ref="N15:AK15"/>
+    <mergeCell ref="D128:AK128"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
@@ -7120,17 +7597,18 @@
     <mergeCell ref="D41:L41"/>
     <mergeCell ref="T49:X49"/>
     <mergeCell ref="M38:P38"/>
-    <mergeCell ref="C92:AK92"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
     <mergeCell ref="D83:AK83"/>
+    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
-    <mergeCell ref="B60:I60"/>
+    <mergeCell ref="AF60:AK60"/>
+    <mergeCell ref="D85:AK85"/>
     <mergeCell ref="D110:AK110"/>
-    <mergeCell ref="D85:AK85"/>
+    <mergeCell ref="D59:L59"/>
+    <mergeCell ref="A79:AK79"/>
     <mergeCell ref="Q37:S37"/>
-    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -7144,7 +7622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK90"/>
+  <dimension ref="A1:AK91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -7305,7 +7783,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/04/24</t>
+          <t>2026/07/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -8268,7 +8746,7 @@
       <c r="C35" s="19" t="inlineStr">
         <is>
           <t>{
-  "message": "正常に削除しました"
+  "message": "削除しました。"
 }</t>
         </is>
       </c>
@@ -8523,7 +9001,7 @@
         <is>
           <t>{
   "error_code": "CONFLICT",
-  "message": "関連データが存在するため削除できません"
+  "message": "この販売店は関連オブジェクトに紐づいているため削除できません。"
 }</t>
         </is>
       </c>
@@ -8756,19 +9234,20 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="198" customHeight="1">
+    <row r="71" ht="216" customHeight="1">
       <c r="C71" s="42" t="inlineStr">
         <is>
           <t>SELECT hanbaiten_id, ja_id, hanbaiten_code, hanbaiten_name,
-       hanbaiten_name_kana, torihikisaki_no,
+       hanbaiten_name_kana, torihikisaki_no, todofuken_code,
        yubin_no, address, tel, fax, shocho_name,
        itaku_kubun, haitatsuryo_tanka_id, haitatsuryo_shiharai_cycle,
-       tesuryo_kubun, tesuryo_amount,
+       furikomi_tesuryo_futan_kubun, furikomi_tesuryo,
        bank_code, bank_name, bank_branch_code, bank_branch_name,
-       yokin_shubetsu, koza_no, koza_meigi, biko,
+       yokin_shubetsu, koza_no, koza_meigi, haiten_flg, biko,
        created_at, updated_at
 FROM m_hanbaiten
 WHERE hanbaiten_id = :hanbaiten_id
+  AND ja_id = :ja_id
   AND deleted_at IS NULL</t>
         </is>
       </c>
@@ -8814,10 +9293,10 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="18" customHeight="1">
+    <row r="73" ht="36" customHeight="1">
       <c r="C73" s="41" t="inlineStr">
         <is>
-          <t>ja_id が一致しない場合：HTTP 403 (`DATA_SCOPE_VIOLATION`)</t>
+          <t>ja_id が一致しない場合：HTTP 404 (`NOT_FOUND`)（DataScope 違反を秘匿するため、存在しないものとして扱う）</t>
         </is>
       </c>
     </row>
@@ -8929,15 +9408,22 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="18" customHeight="1">
-      <c r="B79" s="27" t="inlineStr">
+    <row r="79" ht="36" customHeight="1">
+      <c r="D79" s="41" t="inlineStr">
+        <is>
+          <t>エラーメッセージ：「この販売店は関連オブジェクトに紐づいているため削除できません。」（ACSMS-MSG-018-004、画面設計書 v1.2 §7.2）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>4.5 論理削除の実行</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="126" customHeight="1">
-      <c r="C80" s="42" t="inlineStr">
+    <row r="81" ht="126" customHeight="1">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>UPDATE m_hanbaiten
 SET deleted_at = NOW(),
@@ -8948,57 +9434,57 @@
   AND deleted_at IS NULL</t>
         </is>
       </c>
-      <c r="D80" s="10" t="n"/>
-      <c r="E80" s="10" t="n"/>
-      <c r="F80" s="10" t="n"/>
-      <c r="G80" s="10" t="n"/>
-      <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="10" t="n"/>
-      <c r="M80" s="10" t="n"/>
-      <c r="N80" s="10" t="n"/>
-      <c r="O80" s="10" t="n"/>
-      <c r="P80" s="10" t="n"/>
-      <c r="Q80" s="10" t="n"/>
-      <c r="R80" s="10" t="n"/>
-      <c r="S80" s="10" t="n"/>
-      <c r="T80" s="10" t="n"/>
-      <c r="U80" s="10" t="n"/>
-      <c r="V80" s="10" t="n"/>
-      <c r="W80" s="10" t="n"/>
-      <c r="X80" s="10" t="n"/>
-      <c r="Y80" s="10" t="n"/>
-      <c r="Z80" s="10" t="n"/>
-      <c r="AA80" s="10" t="n"/>
-      <c r="AB80" s="10" t="n"/>
-      <c r="AC80" s="10" t="n"/>
-      <c r="AD80" s="10" t="n"/>
-      <c r="AE80" s="10" t="n"/>
-      <c r="AF80" s="10" t="n"/>
-      <c r="AG80" s="10" t="n"/>
-      <c r="AH80" s="10" t="n"/>
-      <c r="AI80" s="10" t="n"/>
-      <c r="AJ80" s="10" t="n"/>
-      <c r="AK80" s="11" t="n"/>
-    </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="B81" s="27" t="inlineStr">
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="10" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="10" t="n"/>
+      <c r="M81" s="10" t="n"/>
+      <c r="N81" s="10" t="n"/>
+      <c r="O81" s="10" t="n"/>
+      <c r="P81" s="10" t="n"/>
+      <c r="Q81" s="10" t="n"/>
+      <c r="R81" s="10" t="n"/>
+      <c r="S81" s="10" t="n"/>
+      <c r="T81" s="10" t="n"/>
+      <c r="U81" s="10" t="n"/>
+      <c r="V81" s="10" t="n"/>
+      <c r="W81" s="10" t="n"/>
+      <c r="X81" s="10" t="n"/>
+      <c r="Y81" s="10" t="n"/>
+      <c r="Z81" s="10" t="n"/>
+      <c r="AA81" s="10" t="n"/>
+      <c r="AB81" s="10" t="n"/>
+      <c r="AC81" s="10" t="n"/>
+      <c r="AD81" s="10" t="n"/>
+      <c r="AE81" s="10" t="n"/>
+      <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="11" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>4.6 操作ログ記録</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="C82" s="41" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="C83" s="41" t="inlineStr">
         <is>
           <t>以下のSQLを実行して操作ログを記録する。</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="216" customHeight="1">
-      <c r="C83" s="42" t="inlineStr">
+    <row r="84" ht="216" customHeight="1">
+      <c r="C84" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9012,63 +9498,6 @@
         :before_value_json, '',
         '', '',
         :ip_address, :user_agent)</t>
-        </is>
-      </c>
-      <c r="D83" s="10" t="n"/>
-      <c r="E83" s="10" t="n"/>
-      <c r="F83" s="10" t="n"/>
-      <c r="G83" s="10" t="n"/>
-      <c r="H83" s="10" t="n"/>
-      <c r="I83" s="10" t="n"/>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="10" t="n"/>
-      <c r="M83" s="10" t="n"/>
-      <c r="N83" s="10" t="n"/>
-      <c r="O83" s="10" t="n"/>
-      <c r="P83" s="10" t="n"/>
-      <c r="Q83" s="10" t="n"/>
-      <c r="R83" s="10" t="n"/>
-      <c r="S83" s="10" t="n"/>
-      <c r="T83" s="10" t="n"/>
-      <c r="U83" s="10" t="n"/>
-      <c r="V83" s="10" t="n"/>
-      <c r="W83" s="10" t="n"/>
-      <c r="X83" s="10" t="n"/>
-      <c r="Y83" s="10" t="n"/>
-      <c r="Z83" s="10" t="n"/>
-      <c r="AA83" s="10" t="n"/>
-      <c r="AB83" s="10" t="n"/>
-      <c r="AC83" s="10" t="n"/>
-      <c r="AD83" s="10" t="n"/>
-      <c r="AE83" s="10" t="n"/>
-      <c r="AF83" s="10" t="n"/>
-      <c r="AG83" s="10" t="n"/>
-      <c r="AH83" s="10" t="n"/>
-      <c r="AI83" s="10" t="n"/>
-      <c r="AJ83" s="10" t="n"/>
-      <c r="AK83" s="11" t="n"/>
-    </row>
-    <row r="84" ht="324" customHeight="1">
-      <c r="C84" s="42" t="inlineStr">
-        <is>
-          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
-`after_value`：DELETE のため空文字列を設定する。
-{
-  "hanbaiten_id": 1,
-  "ja_id": 1,
-  "hanbaiten_code": "H001",
-  "hanbaiten_name": "山田新聞販売店",
-  "yubin_no": "1000001",
-  "address": "東京都千代田区千代田1-1",
-  "tel": "0312345678",
-  "fax": "0312345679",
-  "shocho_name": "山田太郎",
-  "itaku_kubun": 1,
-  "haitatsuryo_shiharai_cycle": 1,
-  "tesuryo_kubun": 1,
-  "tesuryo_amount": 500
-}</t>
         </is>
       </c>
       <c r="D84" s="10" t="n"/>
@@ -9106,43 +9535,102 @@
       <c r="AJ84" s="10" t="n"/>
       <c r="AK84" s="11" t="n"/>
     </row>
-    <row r="85" ht="18" customHeight="1">
-      <c r="B85" s="27" t="inlineStr">
+    <row r="85" ht="360" customHeight="1">
+      <c r="C85" s="42" t="inlineStr">
+        <is>
+          <t>`before_value`：削除前のデータをJSON形式で格納する。パスワード等の機密情報は含めないこと。
+`after_value`：DELETE のため空文字列を設定する。
+{
+  "hanbaiten_id": 1,
+  "ja_id": 1,
+  "hanbaiten_code": "H001",
+  "hanbaiten_name": "山田新聞販売店",
+  "todofuken_code": "13",
+  "yubin_no": "1000001",
+  "address": "東京都千代田区千代田1-1",
+  "tel": "0312345678",
+  "fax": "0312345679",
+  "shocho_name": "山田太郎",
+  "itaku_kubun": 1,
+  "haitatsuryo_shiharai_cycle": 1,
+  "furikomi_tesuryo_futan_kubun": 1,
+  "furikomi_tesuryo": 500,
+  "haiten_flg": false
+}</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="10" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="10" t="n"/>
+      <c r="M85" s="10" t="n"/>
+      <c r="N85" s="10" t="n"/>
+      <c r="O85" s="10" t="n"/>
+      <c r="P85" s="10" t="n"/>
+      <c r="Q85" s="10" t="n"/>
+      <c r="R85" s="10" t="n"/>
+      <c r="S85" s="10" t="n"/>
+      <c r="T85" s="10" t="n"/>
+      <c r="U85" s="10" t="n"/>
+      <c r="V85" s="10" t="n"/>
+      <c r="W85" s="10" t="n"/>
+      <c r="X85" s="10" t="n"/>
+      <c r="Y85" s="10" t="n"/>
+      <c r="Z85" s="10" t="n"/>
+      <c r="AA85" s="10" t="n"/>
+      <c r="AB85" s="10" t="n"/>
+      <c r="AC85" s="10" t="n"/>
+      <c r="AD85" s="10" t="n"/>
+      <c r="AE85" s="10" t="n"/>
+      <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>4.7 レスポンス生成</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="18" customHeight="1">
-      <c r="C86" s="41" t="inlineStr">
+    <row r="87" ht="18" customHeight="1">
+      <c r="C87" s="41" t="inlineStr">
         <is>
           <t>削除成功メッセージを返却する。HTTP 200。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="18" customHeight="1">
-      <c r="B87" s="27" t="inlineStr">
+    <row r="88" ht="18" customHeight="1">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>4.8 例外処理</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="C88" s="41" t="inlineStr">
-        <is>
-          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="C89" s="41" t="inlineStr">
         <is>
+          <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="C90" s="41" t="inlineStr">
+        <is>
           <t>エラー発生時も操作ログを記録する（`log_type = 3`）。</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="216" customHeight="1">
-      <c r="C90" s="42" t="inlineStr">
+    <row r="91" ht="216" customHeight="1">
+      <c r="C91" s="42" t="inlineStr">
         <is>
           <t>INSERT INTO t_log (log_type, log_datetime, account_id, ja_id,
                    gamen_name, operation, result_status,
@@ -9158,43 +9646,43 @@
         :ip_address, :user_agent)</t>
         </is>
       </c>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="10" t="n"/>
-      <c r="M90" s="10" t="n"/>
-      <c r="N90" s="10" t="n"/>
-      <c r="O90" s="10" t="n"/>
-      <c r="P90" s="10" t="n"/>
-      <c r="Q90" s="10" t="n"/>
-      <c r="R90" s="10" t="n"/>
-      <c r="S90" s="10" t="n"/>
-      <c r="T90" s="10" t="n"/>
-      <c r="U90" s="10" t="n"/>
-      <c r="V90" s="10" t="n"/>
-      <c r="W90" s="10" t="n"/>
-      <c r="X90" s="10" t="n"/>
-      <c r="Y90" s="10" t="n"/>
-      <c r="Z90" s="10" t="n"/>
-      <c r="AA90" s="10" t="n"/>
-      <c r="AB90" s="10" t="n"/>
-      <c r="AC90" s="10" t="n"/>
-      <c r="AD90" s="10" t="n"/>
-      <c r="AE90" s="10" t="n"/>
-      <c r="AF90" s="10" t="n"/>
-      <c r="AG90" s="10" t="n"/>
-      <c r="AH90" s="10" t="n"/>
-      <c r="AI90" s="10" t="n"/>
-      <c r="AJ90" s="10" t="n"/>
-      <c r="AK90" s="11" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="10" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="10" t="n"/>
+      <c r="M91" s="10" t="n"/>
+      <c r="N91" s="10" t="n"/>
+      <c r="O91" s="10" t="n"/>
+      <c r="P91" s="10" t="n"/>
+      <c r="Q91" s="10" t="n"/>
+      <c r="R91" s="10" t="n"/>
+      <c r="S91" s="10" t="n"/>
+      <c r="T91" s="10" t="n"/>
+      <c r="U91" s="10" t="n"/>
+      <c r="V91" s="10" t="n"/>
+      <c r="W91" s="10" t="n"/>
+      <c r="X91" s="10" t="n"/>
+      <c r="Y91" s="10" t="n"/>
+      <c r="Z91" s="10" t="n"/>
+      <c r="AA91" s="10" t="n"/>
+      <c r="AB91" s="10" t="n"/>
+      <c r="AC91" s="10" t="n"/>
+      <c r="AD91" s="10" t="n"/>
+      <c r="AE91" s="10" t="n"/>
+      <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="11" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="121">
+  <mergeCells count="122">
     <mergeCell ref="J11:AK11"/>
     <mergeCell ref="Q29:S29"/>
     <mergeCell ref="A26:AK26"/>
@@ -9208,15 +9696,14 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="J18:M18"/>
     <mergeCell ref="M23:P23"/>
-    <mergeCell ref="C86:AK86"/>
     <mergeCell ref="J12:AK12"/>
     <mergeCell ref="N17:AK17"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="AF23:AK23"/>
-    <mergeCell ref="B87:AK87"/>
     <mergeCell ref="B8:I8"/>
     <mergeCell ref="N19:AK19"/>
     <mergeCell ref="J19:M19"/>
+    <mergeCell ref="C85:AK85"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
     <mergeCell ref="Y24:AB24"/>
@@ -9226,7 +9713,6 @@
     <mergeCell ref="C75:AK75"/>
     <mergeCell ref="C84:AK84"/>
     <mergeCell ref="B10:I10"/>
-    <mergeCell ref="C80:AK80"/>
     <mergeCell ref="J2:P3"/>
     <mergeCell ref="B63:AK63"/>
     <mergeCell ref="B9:I9"/>
@@ -9235,16 +9721,17 @@
     <mergeCell ref="C38:AK38"/>
     <mergeCell ref="A21:AK21"/>
     <mergeCell ref="T29:X29"/>
+    <mergeCell ref="B86:AK86"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="D62:AK62"/>
     <mergeCell ref="N14:AK14"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="C88:AK88"/>
     <mergeCell ref="C35:AK35"/>
     <mergeCell ref="Z2:AC3"/>
     <mergeCell ref="C24:L24"/>
+    <mergeCell ref="D79:AK79"/>
     <mergeCell ref="AD2:AG3"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="J13:AK13"/>
@@ -9252,22 +9739,21 @@
     <mergeCell ref="Y29:AE29"/>
     <mergeCell ref="C59:AK59"/>
     <mergeCell ref="A2:I3"/>
-    <mergeCell ref="B79:AK79"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="Q24:S24"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="C61:AK61"/>
-    <mergeCell ref="B81:AK81"/>
     <mergeCell ref="D66:AK66"/>
     <mergeCell ref="Y28:AE28"/>
     <mergeCell ref="C72:AK72"/>
     <mergeCell ref="C32:AK32"/>
+    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="B58:AK58"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="C78:AK78"/>
+    <mergeCell ref="C87:AK87"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="C28:L28"/>
-    <mergeCell ref="C82:AK82"/>
     <mergeCell ref="B57:AK57"/>
     <mergeCell ref="B11:I11"/>
     <mergeCell ref="C89:AK89"/>
@@ -9281,6 +9767,7 @@
     <mergeCell ref="N15:AK15"/>
     <mergeCell ref="V1:Y1"/>
     <mergeCell ref="T23:X23"/>
+    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="J9:AK9"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="AH1:AK1"/>
@@ -9297,6 +9784,8 @@
     <mergeCell ref="Y23:AB23"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="B52:I52"/>
+    <mergeCell ref="B88:AK88"/>
+    <mergeCell ref="B82:AK82"/>
     <mergeCell ref="D67:AK67"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="C47:AK47"/>
@@ -9310,10 +9799,10 @@
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="C90:AK90"/>
-    <mergeCell ref="B85:AK85"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="C71:AK71"/>
     <mergeCell ref="C76:AK76"/>
+    <mergeCell ref="C91:AK91"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="AF29:AK29"/>
   </mergeCells>

--- a/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
+++ b/docs/design/ACSMS-SCR-018/【日本農業新聞様】VTIジャパン_クラウド版購読者管理システム_API設計書_販売店明細検索画面_V1.0.xlsx
@@ -1832,7 +1832,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -2303,7 +2303,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3118,7 +3118,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -3392,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AK139"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="4.25" customWidth="1" min="1" max="1"/>
@@ -3553,7 +3553,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
@@ -4559,11 +4559,11 @@
     </row>
     <row r="28" ht="54" customHeight="1">
       <c r="B28" s="31" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>haiten_flg</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="D28" s="10" t="n"/>
@@ -4577,7 +4577,7 @@
       <c r="L28" s="11" t="n"/>
       <c r="M28" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N28" s="10" t="n"/>
@@ -4608,7 +4608,7 @@
       <c r="AE28" s="11" t="n"/>
       <c r="AF28" s="19" t="inlineStr">
         <is>
-          <t>廃店フラグ（true:廃店も含む, false:廃店を除外）。**省略時は false（廃店フラグが立っているレコードは一覧に表示しない）**。画面設計書 v1.2 §1.1 / §2.1 参照</t>
+          <t>JA絞り込み（NICHINO_STAFF 代行入力 専用）。セッションが JA スコープ役（CHUOKAI/JA_HONTEN/JA_KANRI_SHITEN）の場合は無視され session.ja_id が優先される。1以上の整数。</t>
         </is>
       </c>
       <c r="AG28" s="10" t="n"/>
@@ -4617,13 +4617,13 @@
       <c r="AJ28" s="10" t="n"/>
       <c r="AK28" s="11" t="n"/>
     </row>
-    <row r="29" ht="126" customHeight="1">
+    <row r="29" ht="90" customHeight="1">
       <c r="B29" s="31" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="C29" s="19" t="inlineStr">
         <is>
-          <t>active_tanka_flg</t>
+          <t>haiten_flg</t>
         </is>
       </c>
       <c r="D29" s="10" t="n"/>
@@ -4668,7 +4668,7 @@
       <c r="AE29" s="11" t="n"/>
       <c r="AF29" s="19" t="inlineStr">
         <is>
-          <t>有効単価フラグ（SCR-021 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する販売店のみ、`false`=失効単価(active_flg=FALSE)を参照する販売店のみ、省略=両方。参照する配達手数料単価は m_hanbaiten.haitatsuryo_tanka_id → m_tanka.tanka_type=2。配達手数料出力(SCR-021)の失効単価エラーからは `false`(無効)で初期選択される</t>
+          <t>廃店フラグ（完全一致：`true`=廃店のレコードのみ表示、`false`=営業中のレコードのみ表示）。**省略時は false（営業中のみ表示、廃店フラグが立っているレコードは一覧に表示しない）**。`true`は「廃店も含む」ではなく「廃店のみに絞り込む」（顧客要件2026-05-26：ラベル「廃店を含む」→「廃店フラグ」）。画面設計書 v1.2 §1.1 / §2.1 参照</t>
         </is>
       </c>
       <c r="AG29" s="10" t="n"/>
@@ -4677,13 +4677,13 @@
       <c r="AJ29" s="10" t="n"/>
       <c r="AK29" s="11" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
+    <row r="30" ht="126" customHeight="1">
       <c r="B30" s="31" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="C30" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>active_tanka_flg</t>
         </is>
       </c>
       <c r="D30" s="10" t="n"/>
@@ -4697,7 +4697,7 @@
       <c r="L30" s="11" t="n"/>
       <c r="M30" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N30" s="10" t="n"/>
@@ -4728,7 +4728,7 @@
       <c r="AE30" s="11" t="n"/>
       <c r="AF30" s="19" t="inlineStr">
         <is>
-          <t>ページ番号（1始まり）。デフォルト: 1</t>
+          <t>有効単価フラグ（SCR-021 error gate 連携・顧客要件2026-07 改訂）。単価一覧(SCR-006)と同一のトライステート: `true`=有効単価(active_flg=TRUE)を参照する販売店のみ、`false`=失効単価(active_flg=FALSE)を参照する販売店のみ、省略=両方。参照する配達手数料単価は m_hanbaiten.haitatsuryo_tanka_id → m_tanka.tanka_type=2。配達手数料出力(SCR-021)の失効単価エラーからは `false`(無効)で初期選択される</t>
         </is>
       </c>
       <c r="AG30" s="10" t="n"/>
@@ -4739,11 +4739,11 @@
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31" s="19" t="inlineStr">
         <is>
-          <t>per_page</t>
+          <t>page</t>
         </is>
       </c>
       <c r="D31" s="10" t="n"/>
@@ -4788,7 +4788,7 @@
       <c r="AE31" s="11" t="n"/>
       <c r="AF31" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
+          <t>ページ番号（1始まり）。デフォルト: 1</t>
         </is>
       </c>
       <c r="AG31" s="10" t="n"/>
@@ -4797,13 +4797,13 @@
       <c r="AJ31" s="10" t="n"/>
       <c r="AK31" s="11" t="n"/>
     </row>
-    <row r="32" ht="54" customHeight="1">
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>sort_by</t>
+          <t>per_page</t>
         </is>
       </c>
       <c r="D32" s="10" t="n"/>
@@ -4817,7 +4817,7 @@
       <c r="L32" s="11" t="n"/>
       <c r="M32" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N32" s="10" t="n"/>
@@ -4848,7 +4848,7 @@
       <c r="AE32" s="11" t="n"/>
       <c r="AF32" s="19" t="inlineStr">
         <is>
-          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name, updated_at）。デフォルト: updated_at（最終更新が新しい順）。updated_at は画面のソートヘッダではなく既定の並び順（新規作成・取込・更新直後の行を先頭に表示）</t>
+          <t>1ページあたりの件数（1〜100）。デフォルト: 20</t>
         </is>
       </c>
       <c r="AG32" s="10" t="n"/>
@@ -4857,13 +4857,13 @@
       <c r="AJ32" s="10" t="n"/>
       <c r="AK32" s="11" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1">
+    <row r="33" ht="54" customHeight="1">
       <c r="B33" s="31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>sort_by</t>
         </is>
       </c>
       <c r="D33" s="10" t="n"/>
@@ -4908,7 +4908,7 @@
       <c r="AE33" s="11" t="n"/>
       <c r="AF33" s="19" t="inlineStr">
         <is>
-          <t>ソート順（asc, desc）。デフォルト: desc（最終更新が新しい順）</t>
+          <t>ソート対象カラム（hanbaiten_code, hanbaiten_name, updated_at）。デフォルト: updated_at（最終更新が新しい順）。updated_at は画面のソートヘッダではなく既定の並び順（新規作成・取込・更新直後の行を先頭に表示）</t>
         </is>
       </c>
       <c r="AG33" s="10" t="n"/>
@@ -4917,88 +4917,84 @@
       <c r="AJ33" s="10" t="n"/>
       <c r="AK33" s="11" t="n"/>
     </row>
-    <row r="34" ht="19.5" customHeight="1"/>
-    <row r="35" ht="19.5" customHeight="1">
-      <c r="A35" s="27" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="B34" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="10" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="17" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="11" t="n"/>
+      <c r="T34" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="11" t="n"/>
+      <c r="Y34" s="17" t="inlineStr"/>
+      <c r="Z34" s="10" t="n"/>
+      <c r="AA34" s="10" t="n"/>
+      <c r="AB34" s="11" t="n"/>
+      <c r="AC34" s="17" t="inlineStr"/>
+      <c r="AD34" s="10" t="n"/>
+      <c r="AE34" s="11" t="n"/>
+      <c r="AF34" s="19" t="inlineStr">
+        <is>
+          <t>ソート順（asc, desc）。デフォルト: desc（最終更新が新しい順）</t>
+        </is>
+      </c>
+      <c r="AG34" s="10" t="n"/>
+      <c r="AH34" s="10" t="n"/>
+      <c r="AI34" s="10" t="n"/>
+      <c r="AJ34" s="10" t="n"/>
+      <c r="AK34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="19.5" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t>3.レスポンスデータ</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19.5" customHeight="1"/>
-    <row r="37" ht="19.5" customHeight="1">
-      <c r="B37" s="30" t="inlineStr">
+    <row r="37" ht="19.5" customHeight="1"/>
+    <row r="38" ht="19.5" customHeight="1">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>項目ID</t>
-        </is>
-      </c>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-      <c r="I37" s="10" t="n"/>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="16" t="inlineStr">
-        <is>
-          <t>タイプ</t>
-        </is>
-      </c>
-      <c r="N37" s="10" t="n"/>
-      <c r="O37" s="10" t="n"/>
-      <c r="P37" s="11" t="n"/>
-      <c r="Q37" s="16" t="inlineStr">
-        <is>
-          <t>繰り返し</t>
-        </is>
-      </c>
-      <c r="R37" s="10" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="16" t="inlineStr">
-        <is>
-          <t>フォーマット</t>
-        </is>
-      </c>
-      <c r="U37" s="10" t="n"/>
-      <c r="V37" s="10" t="n"/>
-      <c r="W37" s="10" t="n"/>
-      <c r="X37" s="11" t="n"/>
-      <c r="Y37" s="16" t="inlineStr">
-        <is>
-          <t>Nullable</t>
-        </is>
-      </c>
-      <c r="Z37" s="10" t="n"/>
-      <c r="AA37" s="10" t="n"/>
-      <c r="AB37" s="10" t="n"/>
-      <c r="AC37" s="10" t="n"/>
-      <c r="AD37" s="10" t="n"/>
-      <c r="AE37" s="11" t="n"/>
-      <c r="AF37" s="16" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="AG37" s="10" t="n"/>
-      <c r="AH37" s="10" t="n"/>
-      <c r="AI37" s="10" t="n"/>
-      <c r="AJ37" s="10" t="n"/>
-      <c r="AK37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="19" t="inlineStr">
-        <is>
-          <t>data</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -5010,29 +5006,33 @@
       <c r="J38" s="10" t="n"/>
       <c r="K38" s="10" t="n"/>
       <c r="L38" s="11" t="n"/>
-      <c r="M38" s="17" t="inlineStr">
-        <is>
-          <t>Array</t>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>タイプ</t>
         </is>
       </c>
       <c r="N38" s="10" t="n"/>
       <c r="O38" s="10" t="n"/>
       <c r="P38" s="11" t="n"/>
-      <c r="Q38" s="17" t="inlineStr">
-        <is>
-          <t>〇</t>
+      <c r="Q38" s="16" t="inlineStr">
+        <is>
+          <t>繰り返し</t>
         </is>
       </c>
       <c r="R38" s="10" t="n"/>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="17" t="inlineStr"/>
+      <c r="T38" s="16" t="inlineStr">
+        <is>
+          <t>フォーマット</t>
+        </is>
+      </c>
       <c r="U38" s="10" t="n"/>
       <c r="V38" s="10" t="n"/>
       <c r="W38" s="10" t="n"/>
       <c r="X38" s="11" t="n"/>
-      <c r="Y38" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="Y38" s="16" t="inlineStr">
+        <is>
+          <t>Nullable</t>
         </is>
       </c>
       <c r="Z38" s="10" t="n"/>
@@ -5041,9 +5041,9 @@
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
       <c r="AE38" s="11" t="n"/>
-      <c r="AF38" s="19" t="inlineStr">
-        <is>
-          <t>販売店データの配列</t>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>説明</t>
         </is>
       </c>
       <c r="AG38" s="10" t="n"/>
@@ -5054,14 +5054,14 @@
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="37" t="n"/>
-      <c r="D39" s="19" t="inlineStr">
-        <is>
-          <t>hanbaiten_id</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C39" s="19" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="n"/>
       <c r="E39" s="10" t="n"/>
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
@@ -5072,7 +5072,7 @@
       <c r="L39" s="11" t="n"/>
       <c r="M39" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Array</t>
         </is>
       </c>
       <c r="N39" s="10" t="n"/>
@@ -5080,7 +5080,7 @@
       <c r="P39" s="11" t="n"/>
       <c r="Q39" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="R39" s="10" t="n"/>
@@ -5103,7 +5103,7 @@
       <c r="AE39" s="11" t="n"/>
       <c r="AF39" s="19" t="inlineStr">
         <is>
-          <t>販売店ID</t>
+          <t>販売店データの配列</t>
         </is>
       </c>
       <c r="AG39" s="10" t="n"/>
@@ -5114,12 +5114,12 @@
     </row>
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="31" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" s="38" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="C40" s="37" t="n"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
-          <t>ja_id</t>
+          <t>hanbaiten_id</t>
         </is>
       </c>
       <c r="E40" s="10" t="n"/>
@@ -5163,7 +5163,7 @@
       <c r="AE40" s="11" t="n"/>
       <c r="AF40" s="19" t="inlineStr">
         <is>
-          <t>JA ID</t>
+          <t>販売店ID</t>
         </is>
       </c>
       <c r="AG40" s="10" t="n"/>
@@ -5174,12 +5174,12 @@
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_code</t>
+          <t>ja_id</t>
         </is>
       </c>
       <c r="E41" s="10" t="n"/>
@@ -5192,7 +5192,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N41" s="10" t="n"/>
@@ -5223,7 +5223,7 @@
       <c r="AE41" s="11" t="n"/>
       <c r="AF41" s="19" t="inlineStr">
         <is>
-          <t>販売店コード</t>
+          <t>JA ID</t>
         </is>
       </c>
       <c r="AG41" s="10" t="n"/>
@@ -5232,14 +5232,14 @@
       <c r="AJ41" s="10" t="n"/>
       <c r="AK41" s="11" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="B42" s="31" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>hanbaiten_name</t>
+          <t>ja_code</t>
         </is>
       </c>
       <c r="E42" s="10" t="n"/>
@@ -5283,7 +5283,7 @@
       <c r="AE42" s="11" t="n"/>
       <c r="AF42" s="19" t="inlineStr">
         <is>
-          <t>販売店名</t>
+          <t>JAコード（m_ja からの一括ルックアップ。存在しない場合は空文字列）</t>
         </is>
       </c>
       <c r="AG42" s="10" t="n"/>
@@ -5294,12 +5294,12 @@
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="B43" s="31" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>todofuken_code</t>
+          <t>ja_name</t>
         </is>
       </c>
       <c r="E43" s="10" t="n"/>
@@ -5343,7 +5343,7 @@
       <c r="AE43" s="11" t="n"/>
       <c r="AF43" s="19" t="inlineStr">
         <is>
-          <t>都道府県コード（m_hanbaiten.todofuken_code、2桁）</t>
+          <t>JA名（m_ja からの一括ルックアップ。存在しない場合は空文字列）</t>
         </is>
       </c>
       <c r="AG43" s="10" t="n"/>
@@ -5352,14 +5352,14 @@
       <c r="AJ43" s="10" t="n"/>
       <c r="AK43" s="11" t="n"/>
     </row>
-    <row r="44" ht="36" customHeight="1">
+    <row r="44" ht="18" customHeight="1">
       <c r="B44" s="31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="19" t="inlineStr">
         <is>
-          <t>todofuken_name</t>
+          <t>hanbaiten_code</t>
         </is>
       </c>
       <c r="E44" s="10" t="n"/>
@@ -5403,7 +5403,7 @@
       <c r="AE44" s="11" t="n"/>
       <c r="AF44" s="19" t="inlineStr">
         <is>
-          <t>都道府県名（m_todofuken JOIN による表示用。一覧では本項目を「都道府県」列に表示する）</t>
+          <t>販売店コード</t>
         </is>
       </c>
       <c r="AG44" s="10" t="n"/>
@@ -5414,12 +5414,12 @@
     </row>
     <row r="45" ht="18" customHeight="1">
       <c r="B45" s="31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="19" t="inlineStr">
         <is>
-          <t>yubin_no</t>
+          <t>hanbaiten_name</t>
         </is>
       </c>
       <c r="E45" s="10" t="n"/>
@@ -5463,7 +5463,7 @@
       <c r="AE45" s="11" t="n"/>
       <c r="AF45" s="19" t="inlineStr">
         <is>
-          <t>郵便番号</t>
+          <t>販売店名</t>
         </is>
       </c>
       <c r="AG45" s="10" t="n"/>
@@ -5472,14 +5472,14 @@
       <c r="AJ45" s="10" t="n"/>
       <c r="AK45" s="11" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="B46" s="31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="19" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>todofuken_code</t>
         </is>
       </c>
       <c r="E46" s="10" t="n"/>
@@ -5523,7 +5523,7 @@
       <c r="AE46" s="11" t="n"/>
       <c r="AF46" s="19" t="inlineStr">
         <is>
-          <t>住所</t>
+          <t>都道府県コード（m_hanbaiten.todofuken_code、2桁）</t>
         </is>
       </c>
       <c r="AG46" s="10" t="n"/>
@@ -5532,14 +5532,14 @@
       <c r="AJ46" s="10" t="n"/>
       <c r="AK46" s="11" t="n"/>
     </row>
-    <row r="47" ht="18" customHeight="1">
+    <row r="47" ht="36" customHeight="1">
       <c r="B47" s="31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C47" s="38" t="n"/>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>tel</t>
+          <t>todofuken_name</t>
         </is>
       </c>
       <c r="E47" s="10" t="n"/>
@@ -5583,7 +5583,7 @@
       <c r="AE47" s="11" t="n"/>
       <c r="AF47" s="19" t="inlineStr">
         <is>
-          <t>電話番号</t>
+          <t>都道府県名（m_todofuken JOIN による表示用。一覧では本項目を「都道府県」列に表示する）</t>
         </is>
       </c>
       <c r="AG47" s="10" t="n"/>
@@ -5594,12 +5594,12 @@
     </row>
     <row r="48" ht="18" customHeight="1">
       <c r="B48" s="31" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C48" s="38" t="n"/>
       <c r="D48" s="19" t="inlineStr">
         <is>
-          <t>fax</t>
+          <t>yubin_no</t>
         </is>
       </c>
       <c r="E48" s="10" t="n"/>
@@ -5643,7 +5643,7 @@
       <c r="AE48" s="11" t="n"/>
       <c r="AF48" s="19" t="inlineStr">
         <is>
-          <t>FAX番号</t>
+          <t>郵便番号</t>
         </is>
       </c>
       <c r="AG48" s="10" t="n"/>
@@ -5654,12 +5654,12 @@
     </row>
     <row r="49" ht="18" customHeight="1">
       <c r="B49" s="31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="38" t="n"/>
       <c r="D49" s="19" t="inlineStr">
         <is>
-          <t>shocho_name</t>
+          <t>address</t>
         </is>
       </c>
       <c r="E49" s="10" t="n"/>
@@ -5703,7 +5703,7 @@
       <c r="AE49" s="11" t="n"/>
       <c r="AF49" s="19" t="inlineStr">
         <is>
-          <t>所長名</t>
+          <t>住所</t>
         </is>
       </c>
       <c r="AG49" s="10" t="n"/>
@@ -5712,14 +5712,14 @@
       <c r="AJ49" s="10" t="n"/>
       <c r="AK49" s="11" t="n"/>
     </row>
-    <row r="50" ht="54" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="B50" s="31" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C50" s="38" t="n"/>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>itaku_kubun</t>
+          <t>tel</t>
         </is>
       </c>
       <c r="E50" s="10" t="n"/>
@@ -5732,7 +5732,7 @@
       <c r="L50" s="11" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N50" s="10" t="n"/>
@@ -5752,7 +5752,7 @@
       <c r="X50" s="11" t="n"/>
       <c r="Y50" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z50" s="10" t="n"/>
@@ -5763,7 +5763,7 @@
       <c r="AE50" s="11" t="n"/>
       <c r="AF50" s="19" t="inlineStr">
         <is>
-          <t>委託区分（※m_code.code_category='ITAKU_KUBUN'を参照、1:振込, 2:日農委託, 9:その他）</t>
+          <t>電話番号</t>
         </is>
       </c>
       <c r="AG50" s="10" t="n"/>
@@ -5772,14 +5772,14 @@
       <c r="AJ50" s="10" t="n"/>
       <c r="AK50" s="11" t="n"/>
     </row>
-    <row r="51" ht="36" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="B51" s="31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C51" s="38" t="n"/>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>haitatsuryo_shiharai_cycle</t>
+          <t>fax</t>
         </is>
       </c>
       <c r="E51" s="10" t="n"/>
@@ -5792,7 +5792,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N51" s="10" t="n"/>
@@ -5812,7 +5812,7 @@
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z51" s="10" t="n"/>
@@ -5823,7 +5823,7 @@
       <c r="AE51" s="11" t="n"/>
       <c r="AF51" s="19" t="inlineStr">
         <is>
-          <t>配達手数料支払サイクル（月数）。一覧では「配達手数料支払サイクル」列に表示する</t>
+          <t>FAX番号</t>
         </is>
       </c>
       <c r="AG51" s="10" t="n"/>
@@ -5832,14 +5832,14 @@
       <c r="AJ51" s="10" t="n"/>
       <c r="AK51" s="11" t="n"/>
     </row>
-    <row r="52" ht="54" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="B52" s="31" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C52" s="38" t="n"/>
       <c r="D52" s="19" t="inlineStr">
         <is>
-          <t>furikomi_tesuryo_futan_kubun</t>
+          <t>shocho_name</t>
         </is>
       </c>
       <c r="E52" s="10" t="n"/>
@@ -5852,7 +5852,7 @@
       <c r="L52" s="11" t="n"/>
       <c r="M52" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N52" s="10" t="n"/>
@@ -5872,7 +5872,7 @@
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>〇</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Z52" s="10" t="n"/>
@@ -5883,7 +5883,7 @@
       <c r="AE52" s="11" t="n"/>
       <c r="AF52" s="19" t="inlineStr">
         <is>
-          <t>振込手数料負担区分（※m_code.code_category='TESURYO_KUBUN'を参照、1:JA, 2:販売店）。一覧では「振込手数料負担区分」列に表示する</t>
+          <t>所長名</t>
         </is>
       </c>
       <c r="AG52" s="10" t="n"/>
@@ -5892,14 +5892,14 @@
       <c r="AJ52" s="10" t="n"/>
       <c r="AK52" s="11" t="n"/>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="54" customHeight="1">
       <c r="B53" s="31" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C53" s="38" t="n"/>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>furikomi_tesuryo</t>
+          <t>itaku_kubun</t>
         </is>
       </c>
       <c r="E53" s="10" t="n"/>
@@ -5943,7 +5943,7 @@
       <c r="AE53" s="11" t="n"/>
       <c r="AF53" s="19" t="inlineStr">
         <is>
-          <t>振込手数料</t>
+          <t>委託区分（※m_code.code_category='ITAKU_KUBUN'を参照、1:振込, 2:日農委託, 9:その他）</t>
         </is>
       </c>
       <c r="AG53" s="10" t="n"/>
@@ -5952,14 +5952,14 @@
       <c r="AJ53" s="10" t="n"/>
       <c r="AK53" s="11" t="n"/>
     </row>
-    <row r="54" ht="18" customHeight="1">
+    <row r="54" ht="36" customHeight="1">
       <c r="B54" s="31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C54" s="38" t="n"/>
       <c r="D54" s="19" t="inlineStr">
         <is>
-          <t>haiten_flg</t>
+          <t>haitatsuryo_shiharai_cycle</t>
         </is>
       </c>
       <c r="E54" s="10" t="n"/>
@@ -5972,7 +5972,7 @@
       <c r="L54" s="11" t="n"/>
       <c r="M54" s="17" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N54" s="10" t="n"/>
@@ -5992,7 +5992,7 @@
       <c r="X54" s="11" t="n"/>
       <c r="Y54" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z54" s="10" t="n"/>
@@ -6003,7 +6003,7 @@
       <c r="AE54" s="11" t="n"/>
       <c r="AF54" s="19" t="inlineStr">
         <is>
-          <t>廃店フラグ（true:廃店, false:営業中）</t>
+          <t>配達手数料支払サイクル（月数）。一覧では「配達手数料支払サイクル」列に表示する</t>
         </is>
       </c>
       <c r="AG54" s="10" t="n"/>
@@ -6012,14 +6012,14 @@
       <c r="AJ54" s="10" t="n"/>
       <c r="AK54" s="11" t="n"/>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="54" customHeight="1">
       <c r="B55" s="31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C55" s="38" t="n"/>
       <c r="D55" s="19" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>furikomi_tesuryo_futan_kubun</t>
         </is>
       </c>
       <c r="E55" s="10" t="n"/>
@@ -6032,7 +6032,7 @@
       <c r="L55" s="11" t="n"/>
       <c r="M55" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N55" s="10" t="n"/>
@@ -6045,18 +6045,14 @@
       </c>
       <c r="R55" s="10" t="n"/>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T55" s="17" t="inlineStr"/>
       <c r="U55" s="10" t="n"/>
       <c r="V55" s="10" t="n"/>
       <c r="W55" s="10" t="n"/>
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z55" s="10" t="n"/>
@@ -6067,7 +6063,7 @@
       <c r="AE55" s="11" t="n"/>
       <c r="AF55" s="19" t="inlineStr">
         <is>
-          <t>作成日時</t>
+          <t>振込手数料負担区分（※m_code.code_category='TESURYO_KUBUN'を参照、1:JA, 2:販売店）。一覧では「振込手数料負担区分」列に表示する</t>
         </is>
       </c>
       <c r="AG55" s="10" t="n"/>
@@ -6078,12 +6074,12 @@
     </row>
     <row r="56" ht="18" customHeight="1">
       <c r="B56" s="31" t="n">
-        <v>19</v>
-      </c>
-      <c r="C56" s="39" t="n"/>
+        <v>16</v>
+      </c>
+      <c r="C56" s="38" t="n"/>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>furikomi_tesuryo</t>
         </is>
       </c>
       <c r="E56" s="10" t="n"/>
@@ -6096,7 +6092,7 @@
       <c r="L56" s="11" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="N56" s="10" t="n"/>
@@ -6109,18 +6105,14 @@
       </c>
       <c r="R56" s="10" t="n"/>
       <c r="S56" s="11" t="n"/>
-      <c r="T56" s="17" t="inlineStr">
-        <is>
-          <t>ISO8601</t>
-        </is>
-      </c>
+      <c r="T56" s="17" t="inlineStr"/>
       <c r="U56" s="10" t="n"/>
       <c r="V56" s="10" t="n"/>
       <c r="W56" s="10" t="n"/>
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z56" s="10" t="n"/>
@@ -6131,7 +6123,7 @@
       <c r="AE56" s="11" t="n"/>
       <c r="AF56" s="19" t="inlineStr">
         <is>
-          <t>更新日時</t>
+          <t>振込手数料</t>
         </is>
       </c>
       <c r="AG56" s="10" t="n"/>
@@ -6142,14 +6134,14 @@
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="B57" s="31" t="n">
-        <v>20</v>
-      </c>
-      <c r="C57" s="19" t="inlineStr">
-        <is>
-          <t>meta</t>
-        </is>
-      </c>
-      <c r="D57" s="10" t="n"/>
+        <v>17</v>
+      </c>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="19" t="inlineStr">
+        <is>
+          <t>haiten_flg</t>
+        </is>
+      </c>
       <c r="E57" s="10" t="n"/>
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
@@ -6160,7 +6152,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="17" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="N57" s="10" t="n"/>
@@ -6191,7 +6183,7 @@
       <c r="AE57" s="11" t="n"/>
       <c r="AF57" s="19" t="inlineStr">
         <is>
-          <t>ページネーション情報</t>
+          <t>廃店フラグ（true:廃店, false:営業中）</t>
         </is>
       </c>
       <c r="AG57" s="10" t="n"/>
@@ -6202,12 +6194,12 @@
     </row>
     <row r="58" ht="18" customHeight="1">
       <c r="B58" s="31" t="n">
-        <v>21</v>
-      </c>
-      <c r="C58" s="37" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="C58" s="38" t="n"/>
       <c r="D58" s="19" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E58" s="10" t="n"/>
@@ -6220,7 +6212,7 @@
       <c r="L58" s="11" t="n"/>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N58" s="10" t="n"/>
@@ -6233,7 +6225,11 @@
       </c>
       <c r="R58" s="10" t="n"/>
       <c r="S58" s="11" t="n"/>
-      <c r="T58" s="17" t="inlineStr"/>
+      <c r="T58" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U58" s="10" t="n"/>
       <c r="V58" s="10" t="n"/>
       <c r="W58" s="10" t="n"/>
@@ -6251,7 +6247,7 @@
       <c r="AE58" s="11" t="n"/>
       <c r="AF58" s="19" t="inlineStr">
         <is>
-          <t>総件数</t>
+          <t>作成日時</t>
         </is>
       </c>
       <c r="AG58" s="10" t="n"/>
@@ -6262,12 +6258,12 @@
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="B59" s="31" t="n">
-        <v>22</v>
-      </c>
-      <c r="C59" s="38" t="n"/>
+        <v>19</v>
+      </c>
+      <c r="C59" s="39" t="n"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="E59" s="10" t="n"/>
@@ -6280,7 +6276,7 @@
       <c r="L59" s="11" t="n"/>
       <c r="M59" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>String</t>
         </is>
       </c>
       <c r="N59" s="10" t="n"/>
@@ -6293,14 +6289,18 @@
       </c>
       <c r="R59" s="10" t="n"/>
       <c r="S59" s="11" t="n"/>
-      <c r="T59" s="17" t="inlineStr"/>
+      <c r="T59" s="17" t="inlineStr">
+        <is>
+          <t>ISO8601</t>
+        </is>
+      </c>
       <c r="U59" s="10" t="n"/>
       <c r="V59" s="10" t="n"/>
       <c r="W59" s="10" t="n"/>
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>〇</t>
         </is>
       </c>
       <c r="Z59" s="10" t="n"/>
@@ -6311,7 +6311,7 @@
       <c r="AE59" s="11" t="n"/>
       <c r="AF59" s="19" t="inlineStr">
         <is>
-          <t>現在のページ番号</t>
+          <t>更新日時</t>
         </is>
       </c>
       <c r="AG59" s="10" t="n"/>
@@ -6322,14 +6322,14 @@
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="B60" s="31" t="n">
-        <v>23</v>
-      </c>
-      <c r="C60" s="38" t="n"/>
-      <c r="D60" s="19" t="inlineStr">
-        <is>
-          <t>per_page</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C60" s="19" t="inlineStr">
+        <is>
+          <t>meta</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="n"/>
       <c r="E60" s="10" t="n"/>
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
@@ -6340,7 +6340,7 @@
       <c r="L60" s="11" t="n"/>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="N60" s="10" t="n"/>
@@ -6371,7 +6371,7 @@
       <c r="AE60" s="11" t="n"/>
       <c r="AF60" s="19" t="inlineStr">
         <is>
-          <t>1ページあたりの件数</t>
+          <t>ページネーション情報</t>
         </is>
       </c>
       <c r="AG60" s="10" t="n"/>
@@ -6382,12 +6382,12 @@
     </row>
     <row r="61" ht="18" customHeight="1">
       <c r="B61" s="31" t="n">
-        <v>24</v>
-      </c>
-      <c r="C61" s="39" t="n"/>
+        <v>21</v>
+      </c>
+      <c r="C61" s="37" t="n"/>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>total_pages</t>
+          <t>total</t>
         </is>
       </c>
       <c r="E61" s="10" t="n"/>
@@ -6431,7 +6431,7 @@
       <c r="AE61" s="11" t="n"/>
       <c r="AF61" s="19" t="inlineStr">
         <is>
-          <t>総ページ数</t>
+          <t>総件数</t>
         </is>
       </c>
       <c r="AG61" s="10" t="n"/>
@@ -6440,21 +6440,136 @@
       <c r="AJ61" s="10" t="n"/>
       <c r="AK61" s="11" t="n"/>
     </row>
-    <row r="62" ht="19.5" customHeight="1"/>
-    <row r="63" ht="19.5" customHeight="1">
-      <c r="B63" s="40" t="inlineStr">
-        <is>
-          <t>リクエスト</t>
-        </is>
-      </c>
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="31" t="n">
+        <v>22</v>
+      </c>
+      <c r="C62" s="38" t="n"/>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="10" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="11" t="n"/>
+      <c r="M62" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N62" s="10" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="11" t="n"/>
+      <c r="Q62" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="10" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="17" t="inlineStr"/>
+      <c r="U62" s="10" t="n"/>
+      <c r="V62" s="10" t="n"/>
+      <c r="W62" s="10" t="n"/>
+      <c r="X62" s="11" t="n"/>
+      <c r="Y62" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z62" s="10" t="n"/>
+      <c r="AA62" s="10" t="n"/>
+      <c r="AB62" s="10" t="n"/>
+      <c r="AC62" s="10" t="n"/>
+      <c r="AD62" s="10" t="n"/>
+      <c r="AE62" s="11" t="n"/>
+      <c r="AF62" s="19" t="inlineStr">
+        <is>
+          <t>現在のページ番号</t>
+        </is>
+      </c>
+      <c r="AG62" s="10" t="n"/>
+      <c r="AH62" s="10" t="n"/>
+      <c r="AI62" s="10" t="n"/>
+      <c r="AJ62" s="10" t="n"/>
+      <c r="AK62" s="11" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="31" t="n">
+        <v>23</v>
+      </c>
+      <c r="C63" s="38" t="n"/>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>per_page</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="10" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="n"/>
+      <c r="O63" s="10" t="n"/>
+      <c r="P63" s="11" t="n"/>
+      <c r="Q63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="10" t="n"/>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="17" t="inlineStr"/>
+      <c r="U63" s="10" t="n"/>
+      <c r="V63" s="10" t="n"/>
+      <c r="W63" s="10" t="n"/>
+      <c r="X63" s="11" t="n"/>
+      <c r="Y63" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z63" s="10" t="n"/>
+      <c r="AA63" s="10" t="n"/>
+      <c r="AB63" s="10" t="n"/>
+      <c r="AC63" s="10" t="n"/>
+      <c r="AD63" s="10" t="n"/>
+      <c r="AE63" s="11" t="n"/>
+      <c r="AF63" s="19" t="inlineStr">
+        <is>
+          <t>1ページあたりの件数</t>
+        </is>
+      </c>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="11" t="n"/>
     </row>
     <row r="64" ht="18" customHeight="1">
-      <c r="C64" s="19" t="inlineStr">
-        <is>
-          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;haiten_flg=false&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="n"/>
+      <c r="B64" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="C64" s="39" t="n"/>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>total_pages</t>
+        </is>
+      </c>
       <c r="E64" s="10" t="n"/>
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
@@ -6462,93 +6577,61 @@
       <c r="I64" s="10" t="n"/>
       <c r="J64" s="10" t="n"/>
       <c r="K64" s="10" t="n"/>
-      <c r="L64" s="10" t="n"/>
-      <c r="M64" s="10" t="n"/>
+      <c r="L64" s="11" t="n"/>
+      <c r="M64" s="17" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
       <c r="N64" s="10" t="n"/>
       <c r="O64" s="10" t="n"/>
-      <c r="P64" s="10" t="n"/>
-      <c r="Q64" s="10" t="n"/>
+      <c r="P64" s="11" t="n"/>
+      <c r="Q64" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R64" s="10" t="n"/>
-      <c r="S64" s="10" t="n"/>
-      <c r="T64" s="10" t="n"/>
+      <c r="S64" s="11" t="n"/>
+      <c r="T64" s="17" t="inlineStr"/>
       <c r="U64" s="10" t="n"/>
       <c r="V64" s="10" t="n"/>
       <c r="W64" s="10" t="n"/>
-      <c r="X64" s="10" t="n"/>
-      <c r="Y64" s="10" t="n"/>
+      <c r="X64" s="11" t="n"/>
+      <c r="Y64" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="Z64" s="10" t="n"/>
       <c r="AA64" s="10" t="n"/>
       <c r="AB64" s="10" t="n"/>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
-      <c r="AE64" s="10" t="n"/>
-      <c r="AF64" s="10" t="n"/>
+      <c r="AE64" s="11" t="n"/>
+      <c r="AF64" s="19" t="inlineStr">
+        <is>
+          <t>総ページ数</t>
+        </is>
+      </c>
       <c r="AG64" s="10" t="n"/>
       <c r="AH64" s="10" t="n"/>
       <c r="AI64" s="10" t="n"/>
       <c r="AJ64" s="10" t="n"/>
       <c r="AK64" s="11" t="n"/>
     </row>
+    <row r="65" ht="19.5" customHeight="1"/>
     <row r="66" ht="19.5" customHeight="1">
       <c r="B66" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（成功）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="409" customHeight="1">
+          <t>リクエスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
       <c r="C67" s="19" t="inlineStr">
         <is>
-          <t>{
-  "data": [
-    {
-      "hanbaiten_id": 1,
-      "ja_id": 1,
-      "hanbaiten_code": "H001",
-      "hanbaiten_name": "山田新聞販売店",
-      "todofuken_code": "13",
-      "todofuken_name": "東京都",
-      "yubin_no": "1000001",
-      "address": "東京都千代田区千代田1-1",
-      "tel": "0312345678",
-      "fax": "0312345679",
-      "shocho_name": "山田太郎",
-      "itaku_kubun": 1,
-      "haitatsuryo_shiharai_cycle": 1,
-      "furikomi_tesuryo_futan_kubun": 1,
-      "furikomi_tesuryo": 500,
-      "haiten_flg": false,
-      "created_at": "2026-01-15T10:00:00Z",
-      "updated_at": "2026-03-10T14:30:00Z"
-    },
-    {
-      "hanbaiten_id": 2,
-      "ja_id": 1,
-      "hanbaiten_code": "H002",
-      "hanbaiten_name": "山田書店",
-      "todofuken_code": "14",
-      "todofuken_name": "神奈川県",
-      "yubin_no": "1500001",
-      "address": "神奈川県横浜市西区1-2-3",
-      "tel": "0398765432",
-      "fax": "0398765433",
-      "shocho_name": "山田花子",
-      "itaku_kubun": 2,
-      "haitatsuryo_shiharai_cycle": 3,
-      "furikomi_tesuryo_futan_kubun": 2,
-      "furikomi_tesuryo": 300,
-      "haiten_flg": false,
-      "created_at": "2026-02-01T09:00:00Z",
-      "updated_at": null
-    }
-  ],
-  "meta": {
-    "total": 25,
-    "page": 1,
-    "per_page": 20,
-    "total_pages": 2
-  }
-}</t>
+          <t>GET /api/v1/hanbaiten?hanbaiten_name=山田&amp;tel=03&amp;haiten_flg=false&amp;page=1&amp;per_page=20&amp;sort_by=hanbaiten_code&amp;sort_order=asc</t>
         </is>
       </c>
       <c r="D67" s="10" t="n"/>
@@ -6589,16 +6672,66 @@
     <row r="69" ht="19.5" customHeight="1">
       <c r="B69" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 401 Unauthorized）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="72" customHeight="1">
+          <t>レスポンス（成功）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="409" customHeight="1">
       <c r="C70" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "UNAUTHORIZED",
-  "message": "セッションが切れました。再度ログインしてください"
+  "data": [
+    {
+      "hanbaiten_id": 1,
+      "ja_id": 1,
+      "ja_code": "JA01001",
+      "ja_name": "JA東京",
+      "hanbaiten_code": "H001",
+      "hanbaiten_name": "山田新聞販売店",
+      "todofuken_code": "13",
+      "todofuken_name": "東京都",
+      "yubin_no": "1000001",
+      "address": "東京都千代田区千代田1-1",
+      "tel": "0312345678",
+      "fax": "0312345679",
+      "shocho_name": "山田太郎",
+      "itaku_kubun": 1,
+      "haitatsuryo_shiharai_cycle": 1,
+      "furikomi_tesuryo_futan_kubun": 1,
+      "furikomi_tesuryo": 500,
+      "haiten_flg": false,
+      "created_at": "2026-01-15T10:00:00Z",
+      "updated_at": "2026-03-10T14:30:00Z"
+    },
+    {
+      "hanbaiten_id": 2,
+      "ja_id": 1,
+      "ja_code": "JA01001",
+      "ja_name": "JA東京",
+      "hanbaiten_code": "H002",
+      "hanbaiten_name": "山田書店",
+      "todofuken_code": "14",
+      "todofuken_name": "神奈川県",
+      "yubin_no": "1500001",
+      "address": "神奈川県横浜市西区1-2-3",
+      "tel": "0398765432",
+      "fax": "0398765433",
+      "shocho_name": "山田花子",
+      "itaku_kubun": 2,
+      "haitatsuryo_shiharai_cycle": 3,
+      "furikomi_tesuryo_futan_kubun": 2,
+      "furikomi_tesuryo": 300,
+      "haiten_flg": false,
+      "created_at": "2026-02-01T09:00:00Z",
+      "updated_at": null
+    }
+  ],
+  "meta": {
+    "total": 25,
+    "page": 1,
+    "per_page": 20,
+    "total_pages": 2
+  }
 }</t>
         </is>
       </c>
@@ -6640,7 +6773,7 @@
     <row r="72" ht="19.5" customHeight="1">
       <c r="B72" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 403 Forbidden）</t>
+          <t>レスポンス（失敗 401 Unauthorized）</t>
         </is>
       </c>
     </row>
@@ -6648,8 +6781,8 @@
       <c r="C73" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "FORBIDDEN",
-  "message": "この画面へのアクセス権限がありません"
+  "error_code": "UNAUTHORIZED",
+  "message": "セッションが切れました。再度ログインしてください"
 }</t>
         </is>
       </c>
@@ -6691,7 +6824,7 @@
     <row r="75" ht="19.5" customHeight="1">
       <c r="B75" s="40" t="inlineStr">
         <is>
-          <t>レスポンス（失敗 500 Internal Server Error）</t>
+          <t>レスポンス（失敗 403 Forbidden）</t>
         </is>
       </c>
     </row>
@@ -6699,8 +6832,8 @@
       <c r="C76" s="19" t="inlineStr">
         <is>
           <t>{
-  "error_code": "INTERNAL_SERVER_ERROR",
-  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+  "error_code": "FORBIDDEN",
+  "message": "この画面へのアクセス権限がありません"
 }</t>
         </is>
       </c>
@@ -6739,275 +6872,347 @@
       <c r="AJ76" s="10" t="n"/>
       <c r="AK76" s="11" t="n"/>
     </row>
-    <row r="78" ht="19.5" customHeight="1"/>
-    <row r="79" ht="19.5" customHeight="1">
-      <c r="A79" s="27" t="inlineStr">
+    <row r="78" ht="19.5" customHeight="1">
+      <c r="B78" s="40" t="inlineStr">
+        <is>
+          <t>レスポンス（失敗 500 Internal Server Error）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="72" customHeight="1">
+      <c r="C79" s="19" t="inlineStr">
+        <is>
+          <t>{
+  "error_code": "INTERNAL_SERVER_ERROR",
+  "message": "システムエラーが発生しました。しばらくしてから再度お試しください"
+}</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="10" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="10" t="n"/>
+      <c r="M79" s="10" t="n"/>
+      <c r="N79" s="10" t="n"/>
+      <c r="O79" s="10" t="n"/>
+      <c r="P79" s="10" t="n"/>
+      <c r="Q79" s="10" t="n"/>
+      <c r="R79" s="10" t="n"/>
+      <c r="S79" s="10" t="n"/>
+      <c r="T79" s="10" t="n"/>
+      <c r="U79" s="10" t="n"/>
+      <c r="V79" s="10" t="n"/>
+      <c r="W79" s="10" t="n"/>
+      <c r="X79" s="10" t="n"/>
+      <c r="Y79" s="10" t="n"/>
+      <c r="Z79" s="10" t="n"/>
+      <c r="AA79" s="10" t="n"/>
+      <c r="AB79" s="10" t="n"/>
+      <c r="AC79" s="10" t="n"/>
+      <c r="AD79" s="10" t="n"/>
+      <c r="AE79" s="10" t="n"/>
+      <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="11" t="n"/>
+    </row>
+    <row r="81" ht="19.5" customHeight="1"/>
+    <row r="82" ht="19.5" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>4. 処理手順</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="18" customHeight="1">
-      <c r="B80" s="27" t="inlineStr">
+    <row r="83" ht="18" customHeight="1">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>4.1 リクエストのバリデーション</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="C81" s="41" t="inlineStr">
+    <row r="84" ht="18" customHeight="1">
+      <c r="C84" s="41" t="inlineStr">
         <is>
           <t>クエリパラメータの検証：</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="D82" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_code：最大10桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="D83" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name：最大100桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="18" customHeight="1">
-      <c r="D84" s="41" t="inlineStr">
-        <is>
-          <t>tel：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="85" ht="18" customHeight="1">
       <c r="D85" s="41" t="inlineStr">
         <is>
-          <t>fax：最大15桁</t>
+          <t>hanbaiten_code：最大10桁</t>
         </is>
       </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="D86" s="41" t="inlineStr">
         <is>
-          <t>address：最大200桁</t>
+          <t>hanbaiten_name：最大100桁</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
       <c r="D87" s="41" t="inlineStr">
         <is>
-          <t>shocho_name：最大50桁</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="36" customHeight="1">
+          <t>tel：最大15桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
       <c r="D88" s="41" t="inlineStr">
         <is>
-          <t>haiten_flg：Boolean型チェック。省略時は false（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）</t>
+          <t>fax：最大15桁</t>
         </is>
       </c>
     </row>
     <row r="89" ht="18" customHeight="1">
       <c r="D89" s="41" t="inlineStr">
         <is>
-          <t>page：正の整数。デフォルト: 1</t>
+          <t>address：最大200桁</t>
         </is>
       </c>
     </row>
     <row r="90" ht="18" customHeight="1">
       <c r="D90" s="41" t="inlineStr">
         <is>
-          <t>per_page：1〜100の整数。デフォルト: 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="108" customHeight="1">
+          <t>shocho_name：最大50桁</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="36" customHeight="1">
       <c r="D91" s="41" t="inlineStr">
         <is>
-          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, updated_at）のみ。画面のソートヘッダは hanbaiten_code / hanbaiten_name（画面設計書 v1.2 §8.1）、updated_at は既定の並び順専用。デフォルト: updated_at（最終更新が新しい順）。updated_at は新規作成・更新・取込のいずれの書き込みでも更新されるため、直近に操作した行が先頭に並ぶ。並び順には常に二次キー hanbaiten_id DESC を付与し、同一 updated_at（取込バッチ等）でも安定した順序となる</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="18" customHeight="1">
+          <t>ja_id：1以上の整数（NICHINO_STAFF 代行入力 専用の絞り込み。JAスコープ役では無視される）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="54" customHeight="1">
       <c r="D92" s="41" t="inlineStr">
         <is>
-          <t>sort_order：asc または desc のみ。デフォルト: desc（最終更新が新しい順）</t>
+          <t>haiten_flg：Boolean型チェック（完全一致）。省略時は false（営業中のレコードのみ表示。廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）</t>
         </is>
       </c>
     </row>
     <row r="93" ht="18" customHeight="1">
-      <c r="C93" s="41" t="inlineStr">
-        <is>
-          <t>不正なパラメータが存在する場合：</t>
+      <c r="D93" s="41" t="inlineStr">
+        <is>
+          <t>active_tanka_flg：Boolean型チェック。省略時は絞り込まない（両方表示）</t>
         </is>
       </c>
     </row>
     <row r="94" ht="18" customHeight="1">
       <c r="D94" s="41" t="inlineStr">
         <is>
-          <t>HTTP 400 Bad Request を返却する。</t>
+          <t>page：正の整数。デフォルト: 1</t>
         </is>
       </c>
     </row>
     <row r="95" ht="18" customHeight="1">
-      <c r="B95" s="27" t="inlineStr">
-        <is>
-          <t>4.2 認証・認可チェック</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="18" customHeight="1">
-      <c r="C96" s="41" t="inlineStr">
-        <is>
-          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
+      <c r="D95" s="41" t="inlineStr">
+        <is>
+          <t>per_page：1〜100の整数。デフォルト: 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="108" customHeight="1">
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>sort_by：許可カラム（hanbaiten_code, hanbaiten_name, updated_at）のみ。画面のソートヘッダは hanbaiten_code / hanbaiten_name（画面設計書 v1.2 §8.1）、updated_at は既定の並び順専用。デフォルト: updated_at（最終更新が新しい順）。updated_at は新規作成・更新・取込のいずれの書き込みでも更新されるため、直近に操作した行が先頭に並ぶ。並び順には常に二次キー hanbaiten_id DESC を付与し、同一 updated_at（取込バッチ等）でも安定した順序となる</t>
         </is>
       </c>
     </row>
     <row r="97" ht="18" customHeight="1">
-      <c r="C97" s="41" t="inlineStr">
-        <is>
-          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+      <c r="D97" s="41" t="inlineStr">
+        <is>
+          <t>sort_order：asc または desc のみ。デフォルト: desc（最終更新が新しい順）</t>
         </is>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1">
       <c r="C98" s="41" t="inlineStr">
         <is>
-          <t>権限チェック：`hanbaiten.view` を保持しているか確認する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="36" customHeight="1">
+          <t>不正なパラメータが存在する場合：</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
       <c r="D99" s="41" t="inlineStr">
         <is>
-          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+          <t>HTTP 400 Bad Request を返却する。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="18" customHeight="1">
-      <c r="C100" s="41" t="inlineStr">
-        <is>
-          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>4.2 認証・認可チェック</t>
         </is>
       </c>
     </row>
     <row r="101" ht="18" customHeight="1">
-      <c r="B101" s="27" t="inlineStr">
-        <is>
-          <t>4.3 データ取得条件の設定</t>
+      <c r="C101" s="41" t="inlineStr">
+        <is>
+          <t>認証情報を検証する（HTTP-only Cookieセッション）。</t>
         </is>
       </c>
     </row>
     <row r="102" ht="18" customHeight="1">
       <c r="C102" s="41" t="inlineStr">
         <is>
-          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="18" customHeight="1">
+          <t>認証失敗の場合：HTTP 401 Unauthorized (`UNAUTHORIZED`)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
       <c r="C103" s="41" t="inlineStr">
         <is>
-          <t>DataScope条件を構築する：</t>
+          <t>権限チェック：`hanbaiten.view` または `hanbaiten.daiko_input` のいずれかを保持しているか確認する（OR条件）。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="36" customHeight="1">
       <c r="D104" s="41" t="inlineStr">
         <is>
-          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能。販売店代行入力時は明示的に対象 ja_id を指定する）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="36" customHeight="1">
-      <c r="D105" s="41" t="inlineStr">
-        <is>
-          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ）</t>
+          <t>対象ロール：NICHINO_STAFF（日農担当者）, CHUOKAI（中央会）, JA_HONTEN（JA本店）, JA_KANRI_SHITEN（JA管理支店）</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="C105" s="41" t="inlineStr">
+        <is>
+          <t>権限がない場合：HTTP 403 Forbidden (`FORBIDDEN`)</t>
         </is>
       </c>
     </row>
     <row r="106" ht="18" customHeight="1">
-      <c r="C106" s="41" t="inlineStr">
-        <is>
-          <t>基本条件：</t>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>4.3 データ取得条件の設定</t>
         </is>
       </c>
     </row>
     <row r="107" ht="18" customHeight="1">
-      <c r="D107" s="41" t="inlineStr">
-        <is>
-          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="36" customHeight="1">
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>**`haiten_flg = false`（廃店フラグが立っているレコードは一覧に表示しない、画面設計書 v1.2 §1.1 / §2.1 参照）**</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="18" customHeight="1">
-      <c r="C109" s="41" t="inlineStr">
-        <is>
-          <t>検索条件（指定時のみ追加）：</t>
+      <c r="C107" s="41" t="inlineStr">
+        <is>
+          <t>ログインユーザーのスコープを取得する（role_code, ja_id）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="C108" s="41" t="inlineStr">
+        <is>
+          <t>DataScope条件を構築する：</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="D109" s="41" t="inlineStr">
+        <is>
+          <t>NICHINO_STAFF：ja_id フィルタなし（全JAの販売店にアクセス可能。販売店代行入力時はクエリパラメータ `ja_id` を指定して対象 JA を1つに絞り込める）</t>
         </is>
       </c>
     </row>
     <row r="110" ht="36" customHeight="1">
       <c r="D110" s="41" t="inlineStr">
         <is>
-          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="36" customHeight="1">
-      <c r="D111" s="41" t="inlineStr">
-        <is>
-          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+          <t>CHUOKAI, JA_HONTEN, JA_KANRI_SHITEN：`ja_id = :ja_id`（自JAのみ。クエリパラメータ `ja_id` が指定されても無視される）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="C111" s="41" t="inlineStr">
+        <is>
+          <t>基本条件：</t>
         </is>
       </c>
     </row>
     <row r="112" ht="18" customHeight="1">
       <c r="D112" s="41" t="inlineStr">
         <is>
-          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="18" customHeight="1">
+          <t>`deleted_at IS NULL`（論理削除除外：必須条件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="54" customHeight="1">
       <c r="D113" s="41" t="inlineStr">
         <is>
-          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+          <t>**`haiten_flg = :haiten_flg`（完全一致。省略時は `false` を設定し営業中のレコードのみ表示、`haiten_flg=true` 明示指定時は廃店のレコードのみ表示、画面設計書 v1.2 §1.1 / §2.1 参照）**</t>
         </is>
       </c>
     </row>
     <row r="114" ht="18" customHeight="1">
-      <c r="D114" s="41" t="inlineStr">
-        <is>
-          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
+      <c r="C114" s="41" t="inlineStr">
+        <is>
+          <t>検索条件（指定時のみ追加）：</t>
         </is>
       </c>
     </row>
     <row r="115" ht="36" customHeight="1">
       <c r="D115" s="41" t="inlineStr">
         <is>
+          <t>ja_id 指定時（NICHINO_STAFF 代行入力専用。JAスコープ役では無視される）：`ja_id = :ja_id`</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="36" customHeight="1">
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_code 指定時：`hanbaiten_code ILIKE '%' || :hanbaiten_code || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="D117" s="41" t="inlineStr">
+        <is>
+          <t>hanbaiten_name 指定時：`hanbaiten_name ILIKE '%' || :hanbaiten_name || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="D118" s="41" t="inlineStr">
+        <is>
+          <t>tel 指定時：`tel ILIKE '%' || :tel || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="D119" s="41" t="inlineStr">
+        <is>
+          <t>fax 指定時：`fax ILIKE '%' || :fax || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="D120" s="41" t="inlineStr">
+        <is>
+          <t>address 指定時：`address ILIKE '%' || :address || '%'`</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="D121" s="41" t="inlineStr">
+        <is>
           <t>shocho_name 指定時：`shocho_name ILIKE '%' || :shocho_name || '%'`</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="108" customHeight="1">
-      <c r="D116" s="41" t="inlineStr">
+    <row r="122" ht="108" customHeight="1">
+      <c r="D122" s="41" t="inlineStr">
         <is>
           <t>active_tanka_flg 指定時：`true`=参照する配達手数料単価が有効(active_flg=TRUE)の販売店のみ、`false`=失効(active_flg=FALSE)の販売店のみ抽出（省略時は絞り込まない）。非相関サブクエリ IN で判定する（getManyAndCount のページング経路を壊さず、pg-mem でも動作）。active_flg はパラメータ（`:activeTankaFlg`）でバインドする。`haitatsuryo_tanka_id` が NULL の販売店は `NULL IN (...)` が真にならず除外される。</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="108" customHeight="1">
-      <c r="C117" s="42" t="inlineStr">
+    <row r="123" ht="108" customHeight="1">
+      <c r="C123" s="42" t="inlineStr">
         <is>
           <t xml:space="preserve">    AND m.haitatsuryo_tanka_id IN (
       SELECT mti.tanka_id FROM m_tanka mti
@@ -7017,115 +7222,121 @@
     )</t>
         </is>
       </c>
-      <c r="D117" s="10" t="n"/>
-      <c r="E117" s="10" t="n"/>
-      <c r="F117" s="10" t="n"/>
-      <c r="G117" s="10" t="n"/>
-      <c r="H117" s="10" t="n"/>
-      <c r="I117" s="10" t="n"/>
-      <c r="J117" s="10" t="n"/>
-      <c r="K117" s="10" t="n"/>
-      <c r="L117" s="10" t="n"/>
-      <c r="M117" s="10" t="n"/>
-      <c r="N117" s="10" t="n"/>
-      <c r="O117" s="10" t="n"/>
-      <c r="P117" s="10" t="n"/>
-      <c r="Q117" s="10" t="n"/>
-      <c r="R117" s="10" t="n"/>
-      <c r="S117" s="10" t="n"/>
-      <c r="T117" s="10" t="n"/>
-      <c r="U117" s="10" t="n"/>
-      <c r="V117" s="10" t="n"/>
-      <c r="W117" s="10" t="n"/>
-      <c r="X117" s="10" t="n"/>
-      <c r="Y117" s="10" t="n"/>
-      <c r="Z117" s="10" t="n"/>
-      <c r="AA117" s="10" t="n"/>
-      <c r="AB117" s="10" t="n"/>
-      <c r="AC117" s="10" t="n"/>
-      <c r="AD117" s="10" t="n"/>
-      <c r="AE117" s="10" t="n"/>
-      <c r="AF117" s="10" t="n"/>
-      <c r="AG117" s="10" t="n"/>
-      <c r="AH117" s="10" t="n"/>
-      <c r="AI117" s="10" t="n"/>
-      <c r="AJ117" s="10" t="n"/>
-      <c r="AK117" s="11" t="n"/>
-    </row>
-    <row r="118" ht="54" customHeight="1">
-      <c r="C118" s="41" t="inlineStr">
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="10" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
+      <c r="H123" s="10" t="n"/>
+      <c r="I123" s="10" t="n"/>
+      <c r="J123" s="10" t="n"/>
+      <c r="K123" s="10" t="n"/>
+      <c r="L123" s="10" t="n"/>
+      <c r="M123" s="10" t="n"/>
+      <c r="N123" s="10" t="n"/>
+      <c r="O123" s="10" t="n"/>
+      <c r="P123" s="10" t="n"/>
+      <c r="Q123" s="10" t="n"/>
+      <c r="R123" s="10" t="n"/>
+      <c r="S123" s="10" t="n"/>
+      <c r="T123" s="10" t="n"/>
+      <c r="U123" s="10" t="n"/>
+      <c r="V123" s="10" t="n"/>
+      <c r="W123" s="10" t="n"/>
+      <c r="X123" s="10" t="n"/>
+      <c r="Y123" s="10" t="n"/>
+      <c r="Z123" s="10" t="n"/>
+      <c r="AA123" s="10" t="n"/>
+      <c r="AB123" s="10" t="n"/>
+      <c r="AC123" s="10" t="n"/>
+      <c r="AD123" s="10" t="n"/>
+      <c r="AE123" s="10" t="n"/>
+      <c r="AF123" s="10" t="n"/>
+      <c r="AG123" s="10" t="n"/>
+      <c r="AH123" s="10" t="n"/>
+      <c r="AI123" s="10" t="n"/>
+      <c r="AJ123" s="10" t="n"/>
+      <c r="AK123" s="11" t="n"/>
+    </row>
+    <row r="124" ht="54" customHeight="1">
+      <c r="C124" s="41" t="inlineStr">
         <is>
           <t>都道府県表示：`m_todofuken` を `LEFT JOIN`（`m_hanbaiten.todofuken_code = m_todofuken.todofuken_code`）し、`todofuken_name` を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="18" customHeight="1">
-      <c r="B119" s="27" t="inlineStr">
+    <row r="125" ht="18" customHeight="1">
+      <c r="B125" s="27" t="inlineStr">
         <is>
           <t>4.4 データ件数の取得</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="198" customHeight="1">
-      <c r="C120" s="42" t="inlineStr">
+    <row r="126" ht="306" customHeight="1">
+      <c r="C126" s="42" t="inlineStr">
         <is>
           <t>SELECT COUNT(*) AS total
 FROM m_hanbaiten h
 WHERE h.deleted_at IS NULL
-  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND h.haiten_flg = :haiten_flg
   AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
   AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
   AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
   AND (:tel IS NULL OR h.tel ILIKE '%' || :tel || '%')
   AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
   AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
-  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')</t>
-        </is>
-      </c>
-      <c r="D120" s="10" t="n"/>
-      <c r="E120" s="10" t="n"/>
-      <c r="F120" s="10" t="n"/>
-      <c r="G120" s="10" t="n"/>
-      <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="10" t="n"/>
-      <c r="K120" s="10" t="n"/>
-      <c r="L120" s="10" t="n"/>
-      <c r="M120" s="10" t="n"/>
-      <c r="N120" s="10" t="n"/>
-      <c r="O120" s="10" t="n"/>
-      <c r="P120" s="10" t="n"/>
-      <c r="Q120" s="10" t="n"/>
-      <c r="R120" s="10" t="n"/>
-      <c r="S120" s="10" t="n"/>
-      <c r="T120" s="10" t="n"/>
-      <c r="U120" s="10" t="n"/>
-      <c r="V120" s="10" t="n"/>
-      <c r="W120" s="10" t="n"/>
-      <c r="X120" s="10" t="n"/>
-      <c r="Y120" s="10" t="n"/>
-      <c r="Z120" s="10" t="n"/>
-      <c r="AA120" s="10" t="n"/>
-      <c r="AB120" s="10" t="n"/>
-      <c r="AC120" s="10" t="n"/>
-      <c r="AD120" s="10" t="n"/>
-      <c r="AE120" s="10" t="n"/>
-      <c r="AF120" s="10" t="n"/>
-      <c r="AG120" s="10" t="n"/>
-      <c r="AH120" s="10" t="n"/>
-      <c r="AI120" s="10" t="n"/>
-      <c r="AJ120" s="10" t="n"/>
-      <c r="AK120" s="11" t="n"/>
-    </row>
-    <row r="121" ht="18" customHeight="1">
-      <c r="B121" s="27" t="inlineStr">
+  AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')
+  AND (:active_tanka_flg IS NULL OR h.haitatsuryo_tanka_id IN (
+        SELECT mti.tanka_id FROM m_tanka mti
+         WHERE mti.tanka_type = 2
+           AND mti.deleted_at IS NULL
+           AND mti.active_flg = :active_tanka_flg
+      ))</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="10" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="10" t="n"/>
+      <c r="K126" s="10" t="n"/>
+      <c r="L126" s="10" t="n"/>
+      <c r="M126" s="10" t="n"/>
+      <c r="N126" s="10" t="n"/>
+      <c r="O126" s="10" t="n"/>
+      <c r="P126" s="10" t="n"/>
+      <c r="Q126" s="10" t="n"/>
+      <c r="R126" s="10" t="n"/>
+      <c r="S126" s="10" t="n"/>
+      <c r="T126" s="10" t="n"/>
+      <c r="U126" s="10" t="n"/>
+      <c r="V126" s="10" t="n"/>
+      <c r="W126" s="10" t="n"/>
+      <c r="X126" s="10" t="n"/>
+      <c r="Y126" s="10" t="n"/>
+      <c r="Z126" s="10" t="n"/>
+      <c r="AA126" s="10" t="n"/>
+      <c r="AB126" s="10" t="n"/>
+      <c r="AC126" s="10" t="n"/>
+      <c r="AD126" s="10" t="n"/>
+      <c r="AE126" s="10" t="n"/>
+      <c r="AF126" s="10" t="n"/>
+      <c r="AG126" s="10" t="n"/>
+      <c r="AH126" s="10" t="n"/>
+      <c r="AI126" s="10" t="n"/>
+      <c r="AJ126" s="10" t="n"/>
+      <c r="AK126" s="11" t="n"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="B127" s="27" t="inlineStr">
         <is>
           <t>4.5 データ取得</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="360" customHeight="1">
-      <c r="C122" s="42" t="inlineStr">
+    <row r="128" ht="409" customHeight="1">
+      <c r="C128" s="42" t="inlineStr">
         <is>
           <t>SELECT h.hanbaiten_id, h.ja_id, h.hanbaiten_code, h.hanbaiten_name,
        h.todofuken_code, t.todofuken_name,
@@ -7136,7 +7347,7 @@
 FROM m_hanbaiten h
 LEFT JOIN m_todofuken t ON h.todofuken_code = t.todofuken_code
 WHERE h.deleted_at IS NULL
-  AND (:include_haiten = true OR h.haiten_flg = false)
+  AND h.haiten_flg = :haiten_flg
   AND (:role_code = 'NICHINO_STAFF' OR h.ja_id = :ja_id)
   AND (:hanbaiten_code IS NULL OR h.hanbaiten_code ILIKE '%' || :hanbaiten_code || '%')
   AND (:hanbaiten_name IS NULL OR h.hanbaiten_name ILIKE '%' || :hanbaiten_name || '%')
@@ -7144,175 +7355,179 @@
   AND (:fax IS NULL OR h.fax ILIKE '%' || :fax || '%')
   AND (:address IS NULL OR h.address ILIKE '%' || :address || '%')
   AND (:shocho_name IS NULL OR h.shocho_name ILIKE '%' || :shocho_name || '%')
+  AND (:active_tanka_flg IS NULL OR h.haitatsuryo_tanka_id IN (
+        SELECT mti.tanka_id FROM m_tanka mti
+         WHERE mti.tanka_type = 2
+           AND mti.deleted_at IS NULL
+           AND mti.active_flg = :active_tanka_flg
+      ))
 ORDER BY :sort_by :sort_order, h.hanbaiten_id DESC
 LIMIT :per_page
 OFFSET (:page - 1) * :per_page</t>
         </is>
       </c>
-      <c r="D122" s="10" t="n"/>
-      <c r="E122" s="10" t="n"/>
-      <c r="F122" s="10" t="n"/>
-      <c r="G122" s="10" t="n"/>
-      <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="n"/>
-      <c r="J122" s="10" t="n"/>
-      <c r="K122" s="10" t="n"/>
-      <c r="L122" s="10" t="n"/>
-      <c r="M122" s="10" t="n"/>
-      <c r="N122" s="10" t="n"/>
-      <c r="O122" s="10" t="n"/>
-      <c r="P122" s="10" t="n"/>
-      <c r="Q122" s="10" t="n"/>
-      <c r="R122" s="10" t="n"/>
-      <c r="S122" s="10" t="n"/>
-      <c r="T122" s="10" t="n"/>
-      <c r="U122" s="10" t="n"/>
-      <c r="V122" s="10" t="n"/>
-      <c r="W122" s="10" t="n"/>
-      <c r="X122" s="10" t="n"/>
-      <c r="Y122" s="10" t="n"/>
-      <c r="Z122" s="10" t="n"/>
-      <c r="AA122" s="10" t="n"/>
-      <c r="AB122" s="10" t="n"/>
-      <c r="AC122" s="10" t="n"/>
-      <c r="AD122" s="10" t="n"/>
-      <c r="AE122" s="10" t="n"/>
-      <c r="AF122" s="10" t="n"/>
-      <c r="AG122" s="10" t="n"/>
-      <c r="AH122" s="10" t="n"/>
-      <c r="AI122" s="10" t="n"/>
-      <c r="AJ122" s="10" t="n"/>
-      <c r="AK122" s="11" t="n"/>
-    </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="B123" s="27" t="inlineStr">
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="10" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="n"/>
+      <c r="I128" s="10" t="n"/>
+      <c r="J128" s="10" t="n"/>
+      <c r="K128" s="10" t="n"/>
+      <c r="L128" s="10" t="n"/>
+      <c r="M128" s="10" t="n"/>
+      <c r="N128" s="10" t="n"/>
+      <c r="O128" s="10" t="n"/>
+      <c r="P128" s="10" t="n"/>
+      <c r="Q128" s="10" t="n"/>
+      <c r="R128" s="10" t="n"/>
+      <c r="S128" s="10" t="n"/>
+      <c r="T128" s="10" t="n"/>
+      <c r="U128" s="10" t="n"/>
+      <c r="V128" s="10" t="n"/>
+      <c r="W128" s="10" t="n"/>
+      <c r="X128" s="10" t="n"/>
+      <c r="Y128" s="10" t="n"/>
+      <c r="Z128" s="10" t="n"/>
+      <c r="AA128" s="10" t="n"/>
+      <c r="AB128" s="10" t="n"/>
+      <c r="AC128" s="10" t="n"/>
+      <c r="AD128" s="10" t="n"/>
+      <c r="AE128" s="10" t="n"/>
+      <c r="AF128" s="10" t="n"/>
+      <c r="AG128" s="10" t="n"/>
+      <c r="AH128" s="10" t="n"/>
+      <c r="AI128" s="10" t="n"/>
+      <c r="AJ128" s="10" t="n"/>
+      <c r="AK128" s="11" t="n"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>4.6 レスポンス生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="C124" s="41" t="inlineStr">
-        <is>
-          <t>列ラベルとデータの対応（画面設計書 v1.2 §6 検索結果テーブル）：</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="18" customHeight="1">
-      <c r="D125" s="41" t="inlineStr">
-        <is>
-          <t>「都道府県」列 → `todofuken_name`（m_todofuken JOIN）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="36" customHeight="1">
-      <c r="D126" s="41" t="inlineStr">
-        <is>
-          <t>「委託区分」列 → `itaku_kubun`（FE は `useCodesStore().label('ITAKU_KUBUN', value)` でラベル解決）</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="36" customHeight="1">
-      <c r="D127" s="41" t="inlineStr">
-        <is>
-          <t>「配達手数料支払サイクル」列（旧「支払区分」）→ `haitatsuryo_shiharai_cycle`</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="54" customHeight="1">
-      <c r="D128" s="41" t="inlineStr">
-        <is>
-          <t>「振込手数料負担区分」列（旧「手数料区分」）→ `furikomi_tesuryo_futan_kubun`（FE は `useCodesStore().label('TESURYO_KUBUN', value)` でラベル解決）</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="18" customHeight="1">
-      <c r="C129" s="41" t="inlineStr">
-        <is>
-          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="18" customHeight="1">
       <c r="C130" s="41" t="inlineStr">
         <is>
+          <t>列ラベルとデータの対応（画面設計書 v1.2 §6 検索結果テーブル）：</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="D131" s="41" t="inlineStr">
+        <is>
+          <t>「都道府県」列 → `todofuken_name`（m_todofuken JOIN）</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="D132" s="41" t="inlineStr">
+        <is>
+          <t>「委託区分」列 → `itaku_kubun`（FE は `useCodesStore().label('ITAKU_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="D133" s="41" t="inlineStr">
+        <is>
+          <t>「配達手数料支払サイクル」列（旧「支払区分」）→ `haitatsuryo_shiharai_cycle`</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="54" customHeight="1">
+      <c r="D134" s="41" t="inlineStr">
+        <is>
+          <t>「振込手数料負担区分」列（旧「手数料区分」）→ `furikomi_tesuryo_futan_kubun`（FE は `useCodesStore().label('TESURYO_KUBUN', value)` でラベル解決）</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="C135" s="41" t="inlineStr">
+        <is>
+          <t>data 配列と meta オブジェクトを含むJSONを返却する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="C136" s="41" t="inlineStr">
+        <is>
           <t>total_pages = CEIL(total / per_page)</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="C131" s="41" t="inlineStr">
+    <row r="137" ht="18" customHeight="1">
+      <c r="C137" s="41" t="inlineStr">
         <is>
           <t>検索結果が0件の場合も空配列 `[]` を返却する（HTTP 200）。</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="18" customHeight="1">
-      <c r="B132" s="27" t="inlineStr">
+    <row r="138" ht="18" customHeight="1">
+      <c r="B138" s="27" t="inlineStr">
         <is>
           <t>4.7 例外処理</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="18" customHeight="1">
-      <c r="C133" s="41" t="inlineStr">
+    <row r="139" ht="18" customHeight="1">
+      <c r="C139" s="41" t="inlineStr">
         <is>
           <t>DB接続エラー等の場合：HTTP 500 (`INTERNAL_SERVER_ERROR`)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="348">
+  <mergeCells count="370">
+    <mergeCell ref="D134:AK134"/>
     <mergeCell ref="T24:X24"/>
     <mergeCell ref="Y45:AE45"/>
     <mergeCell ref="D61:L61"/>
     <mergeCell ref="D48:L48"/>
     <mergeCell ref="T53:X53"/>
+    <mergeCell ref="D62:L62"/>
     <mergeCell ref="D56:L56"/>
+    <mergeCell ref="C128:AK128"/>
     <mergeCell ref="T55:X55"/>
     <mergeCell ref="M59:P59"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="C100:AK100"/>
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="AH2:AK3"/>
+    <mergeCell ref="D64:L64"/>
     <mergeCell ref="D51:L51"/>
     <mergeCell ref="B10:I10"/>
     <mergeCell ref="AF22:AK22"/>
-    <mergeCell ref="C129:AK129"/>
     <mergeCell ref="Q25:S25"/>
     <mergeCell ref="M54:P54"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="Q33:S33"/>
+    <mergeCell ref="B138:AK138"/>
     <mergeCell ref="Y40:AE40"/>
-    <mergeCell ref="T37:X37"/>
+    <mergeCell ref="Y34:AB34"/>
     <mergeCell ref="Y25:AB25"/>
-    <mergeCell ref="D126:AK126"/>
-    <mergeCell ref="C131:AK131"/>
     <mergeCell ref="T38:X38"/>
     <mergeCell ref="Z1:AC1"/>
     <mergeCell ref="C38:L38"/>
     <mergeCell ref="Q59:S59"/>
     <mergeCell ref="Q22:S22"/>
     <mergeCell ref="Q46:S46"/>
+    <mergeCell ref="C126:AK126"/>
     <mergeCell ref="Y53:AE53"/>
     <mergeCell ref="AF41:AK41"/>
     <mergeCell ref="Q61:S61"/>
-    <mergeCell ref="D39:L39"/>
     <mergeCell ref="C33:L33"/>
     <mergeCell ref="Q48:S48"/>
     <mergeCell ref="Y55:AE55"/>
-    <mergeCell ref="C117:AK117"/>
+    <mergeCell ref="A82:AK82"/>
     <mergeCell ref="T40:X40"/>
-    <mergeCell ref="B95:AK95"/>
     <mergeCell ref="M27:P27"/>
-    <mergeCell ref="Y37:AE37"/>
-    <mergeCell ref="C81:AK81"/>
     <mergeCell ref="AF25:AK25"/>
-    <mergeCell ref="C58:C61"/>
     <mergeCell ref="T45:X45"/>
     <mergeCell ref="A5:AK5"/>
     <mergeCell ref="Y33:AB33"/>
     <mergeCell ref="AF30:AK30"/>
+    <mergeCell ref="Q34:S34"/>
     <mergeCell ref="C28:L28"/>
     <mergeCell ref="Y41:AE41"/>
     <mergeCell ref="D92:AK92"/>
@@ -7331,12 +7546,13 @@
     <mergeCell ref="AF56:AK56"/>
     <mergeCell ref="AF43:AK43"/>
     <mergeCell ref="AH1:AK1"/>
-    <mergeCell ref="D105:AK105"/>
     <mergeCell ref="M40:P40"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="D120:AK120"/>
     <mergeCell ref="Q54:S54"/>
     <mergeCell ref="J16:M16"/>
     <mergeCell ref="AF57:AK57"/>
-    <mergeCell ref="B121:AK121"/>
+    <mergeCell ref="Q64:S64"/>
     <mergeCell ref="M41:P41"/>
     <mergeCell ref="M24:P24"/>
     <mergeCell ref="Y23:AB23"/>
@@ -7348,21 +7564,22 @@
     <mergeCell ref="T61:X61"/>
     <mergeCell ref="Y51:AE51"/>
     <mergeCell ref="AF39:AK39"/>
-    <mergeCell ref="D108:AK108"/>
     <mergeCell ref="C31:L31"/>
+    <mergeCell ref="D95:AK95"/>
     <mergeCell ref="AC28:AE28"/>
     <mergeCell ref="M30:P30"/>
     <mergeCell ref="Y22:AB22"/>
     <mergeCell ref="Q52:S52"/>
     <mergeCell ref="Q39:S39"/>
     <mergeCell ref="M46:P46"/>
-    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="C60:L60"/>
+    <mergeCell ref="D97:AK97"/>
     <mergeCell ref="AC30:AE30"/>
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="AC23:AE23"/>
     <mergeCell ref="C102:AK102"/>
     <mergeCell ref="AF21:AK21"/>
-    <mergeCell ref="C57:L57"/>
+    <mergeCell ref="D121:AK121"/>
     <mergeCell ref="J17:M17"/>
     <mergeCell ref="M56:P56"/>
     <mergeCell ref="D113:AK113"/>
@@ -7372,40 +7589,43 @@
     <mergeCell ref="D115:AK115"/>
     <mergeCell ref="AF52:AK52"/>
     <mergeCell ref="T22:X22"/>
+    <mergeCell ref="AF34:AK34"/>
     <mergeCell ref="M25:P25"/>
     <mergeCell ref="AF49:AK49"/>
     <mergeCell ref="M33:P33"/>
     <mergeCell ref="Q58:S58"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="AF44:AK44"/>
     <mergeCell ref="Q60:S60"/>
+    <mergeCell ref="M62:P62"/>
     <mergeCell ref="C32:L32"/>
+    <mergeCell ref="D118:AK118"/>
     <mergeCell ref="AC29:AE29"/>
     <mergeCell ref="AF55:AK55"/>
-    <mergeCell ref="B132:AK132"/>
-    <mergeCell ref="B119:AK119"/>
     <mergeCell ref="AC31:AE31"/>
     <mergeCell ref="C103:AK103"/>
-    <mergeCell ref="C118:AK118"/>
+    <mergeCell ref="B127:AK127"/>
+    <mergeCell ref="M64:P64"/>
     <mergeCell ref="M51:P51"/>
+    <mergeCell ref="D131:AK131"/>
     <mergeCell ref="C25:L25"/>
-    <mergeCell ref="AF37:AK37"/>
     <mergeCell ref="AF24:AK24"/>
     <mergeCell ref="M21:P21"/>
     <mergeCell ref="T46:X46"/>
     <mergeCell ref="D116:AK116"/>
     <mergeCell ref="AF53:AK53"/>
+    <mergeCell ref="C40:C59"/>
     <mergeCell ref="D49:L49"/>
     <mergeCell ref="T48:X48"/>
-    <mergeCell ref="C96:AK96"/>
     <mergeCell ref="B66:I66"/>
     <mergeCell ref="C98:AK98"/>
     <mergeCell ref="AF42:AK42"/>
-    <mergeCell ref="C64:AK64"/>
+    <mergeCell ref="M34:P34"/>
     <mergeCell ref="M49:P49"/>
     <mergeCell ref="M39:P39"/>
-    <mergeCell ref="C93:AK93"/>
     <mergeCell ref="B69:I69"/>
     <mergeCell ref="Y30:AB30"/>
+    <mergeCell ref="D119:AK119"/>
     <mergeCell ref="D54:L54"/>
     <mergeCell ref="T41:X41"/>
     <mergeCell ref="V1:Y1"/>
@@ -7417,16 +7637,24 @@
     <mergeCell ref="T43:X43"/>
     <mergeCell ref="Y31:AB31"/>
     <mergeCell ref="Y46:AE46"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="AF63:AK63"/>
+    <mergeCell ref="C111:AK111"/>
     <mergeCell ref="Y61:AE61"/>
     <mergeCell ref="Y48:AE48"/>
-    <mergeCell ref="A35:AK35"/>
     <mergeCell ref="T25:X25"/>
     <mergeCell ref="M58:P58"/>
+    <mergeCell ref="D117:AK117"/>
+    <mergeCell ref="T62:X62"/>
+    <mergeCell ref="D132:AK132"/>
     <mergeCell ref="AC27:AE27"/>
+    <mergeCell ref="C137:AK137"/>
+    <mergeCell ref="T64:X64"/>
+    <mergeCell ref="B83:AK83"/>
     <mergeCell ref="C124:AK124"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D44:L44"/>
-    <mergeCell ref="D60:L60"/>
+    <mergeCell ref="C139:AK139"/>
     <mergeCell ref="Q28:S28"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="C76:AK76"/>
@@ -7443,15 +7671,21 @@
     <mergeCell ref="D87:AK87"/>
     <mergeCell ref="T33:X33"/>
     <mergeCell ref="B72:I72"/>
+    <mergeCell ref="D122:AK122"/>
     <mergeCell ref="Q31:S31"/>
     <mergeCell ref="Y32:AB32"/>
+    <mergeCell ref="C108:AK108"/>
     <mergeCell ref="J12:AK12"/>
-    <mergeCell ref="D82:AK82"/>
-    <mergeCell ref="C109:AK109"/>
-    <mergeCell ref="C133:AK133"/>
+    <mergeCell ref="C34:L34"/>
+    <mergeCell ref="Y62:AE62"/>
+    <mergeCell ref="C84:AK84"/>
     <mergeCell ref="Y54:AE54"/>
     <mergeCell ref="Y21:AB21"/>
+    <mergeCell ref="C114:AK114"/>
+    <mergeCell ref="A36:AK36"/>
+    <mergeCell ref="Y64:AE64"/>
     <mergeCell ref="J2:P3"/>
+    <mergeCell ref="T34:X34"/>
     <mergeCell ref="Q42:S42"/>
     <mergeCell ref="T28:X28"/>
     <mergeCell ref="T30:X30"/>
@@ -7461,9 +7695,7 @@
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="AF59:AK59"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B101:AK101"/>
     <mergeCell ref="Q44:S44"/>
-    <mergeCell ref="C39:C56"/>
     <mergeCell ref="T58:X58"/>
     <mergeCell ref="T54:X54"/>
     <mergeCell ref="D89:AK89"/>
@@ -7476,6 +7708,7 @@
     <mergeCell ref="AC21:AE21"/>
     <mergeCell ref="B13:I13"/>
     <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="B78:I78"/>
     <mergeCell ref="Q32:S32"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="Y39:AE39"/>
@@ -7485,13 +7718,14 @@
     <mergeCell ref="Q47:S47"/>
     <mergeCell ref="T60:X60"/>
     <mergeCell ref="C130:AK130"/>
+    <mergeCell ref="B106:AK106"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="C122:AK122"/>
+    <mergeCell ref="Q63:S63"/>
     <mergeCell ref="Q50:S50"/>
+    <mergeCell ref="C136:AK136"/>
     <mergeCell ref="Y57:AE57"/>
     <mergeCell ref="T42:X42"/>
     <mergeCell ref="AF45:AK45"/>
-    <mergeCell ref="C37:L37"/>
     <mergeCell ref="Q27:S27"/>
     <mergeCell ref="Q2:U3"/>
     <mergeCell ref="T50:X50"/>
@@ -7500,10 +7734,12 @@
     <mergeCell ref="D55:L55"/>
     <mergeCell ref="AF40:AK40"/>
     <mergeCell ref="J10:AK10"/>
+    <mergeCell ref="C105:AK105"/>
+    <mergeCell ref="D96:AK96"/>
     <mergeCell ref="M31:P31"/>
-    <mergeCell ref="C120:AK120"/>
     <mergeCell ref="Y60:AE60"/>
     <mergeCell ref="N16:AK16"/>
+    <mergeCell ref="B125:AK125"/>
     <mergeCell ref="Q55:S55"/>
     <mergeCell ref="B14:I17"/>
     <mergeCell ref="C27:L27"/>
@@ -7513,21 +7749,22 @@
     <mergeCell ref="AC24:AE24"/>
     <mergeCell ref="M26:P26"/>
     <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="D93:AK93"/>
     <mergeCell ref="AC26:AE26"/>
     <mergeCell ref="Y42:AE42"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="AF47:AK47"/>
     <mergeCell ref="M52:P52"/>
     <mergeCell ref="Y58:AE58"/>
+    <mergeCell ref="D109:AK109"/>
     <mergeCell ref="AF46:AK46"/>
-    <mergeCell ref="D84:AK84"/>
     <mergeCell ref="Q53:S53"/>
     <mergeCell ref="J15:M15"/>
     <mergeCell ref="AD1:AG1"/>
     <mergeCell ref="AF61:AK61"/>
-    <mergeCell ref="D111:AK111"/>
     <mergeCell ref="AF48:AK48"/>
     <mergeCell ref="D86:AK86"/>
+    <mergeCell ref="B100:AK100"/>
     <mergeCell ref="D104:AK104"/>
     <mergeCell ref="M28:P28"/>
     <mergeCell ref="M57:P57"/>
@@ -7535,6 +7772,7 @@
     <mergeCell ref="M29:P29"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="N17:AK17"/>
+    <mergeCell ref="T63:X63"/>
     <mergeCell ref="AF29:AK29"/>
     <mergeCell ref="Y24:AB24"/>
     <mergeCell ref="Q41:S41"/>
@@ -7545,28 +7783,27 @@
     <mergeCell ref="Q43:S43"/>
     <mergeCell ref="B9:I9"/>
     <mergeCell ref="T31:X31"/>
-    <mergeCell ref="B123:AK123"/>
     <mergeCell ref="C70:AK70"/>
-    <mergeCell ref="C106:AK106"/>
     <mergeCell ref="M45:P45"/>
     <mergeCell ref="B75:I75"/>
-    <mergeCell ref="D125:AK125"/>
+    <mergeCell ref="AF62:AK62"/>
     <mergeCell ref="D112:AK112"/>
     <mergeCell ref="M47:P47"/>
+    <mergeCell ref="C101:AK101"/>
     <mergeCell ref="N14:AK14"/>
-    <mergeCell ref="D127:AK127"/>
-    <mergeCell ref="D114:AK114"/>
+    <mergeCell ref="AF64:AK64"/>
     <mergeCell ref="AF51:AK51"/>
     <mergeCell ref="AC22:AE22"/>
+    <mergeCell ref="Y63:AE63"/>
     <mergeCell ref="M44:P44"/>
     <mergeCell ref="AF38:AK38"/>
     <mergeCell ref="M60:P60"/>
     <mergeCell ref="A2:I3"/>
+    <mergeCell ref="D63:L63"/>
     <mergeCell ref="Y26:AB26"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="D107:AK107"/>
-    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="B129:AK129"/>
     <mergeCell ref="Q51:S51"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="AC33:AE33"/>
@@ -7574,23 +7811,28 @@
     <mergeCell ref="Y27:AB27"/>
     <mergeCell ref="J7:AK7"/>
     <mergeCell ref="T32:X32"/>
+    <mergeCell ref="M63:P63"/>
     <mergeCell ref="T47:X47"/>
     <mergeCell ref="M53:P53"/>
+    <mergeCell ref="AC34:AE34"/>
     <mergeCell ref="M50:P50"/>
+    <mergeCell ref="C107:AK107"/>
+    <mergeCell ref="D133:AK133"/>
+    <mergeCell ref="C79:AK79"/>
     <mergeCell ref="C73:AK73"/>
     <mergeCell ref="M55:P55"/>
     <mergeCell ref="T21:X21"/>
     <mergeCell ref="M48:P48"/>
+    <mergeCell ref="C61:C64"/>
     <mergeCell ref="N15:AK15"/>
-    <mergeCell ref="D128:AK128"/>
     <mergeCell ref="T23:X23"/>
     <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="B80:AK80"/>
     <mergeCell ref="D46:L46"/>
     <mergeCell ref="T52:X52"/>
     <mergeCell ref="D40:L40"/>
     <mergeCell ref="V2:Y3"/>
     <mergeCell ref="T27:X27"/>
+    <mergeCell ref="C135:AK135"/>
     <mergeCell ref="AF54:AK54"/>
     <mergeCell ref="B7:I7"/>
     <mergeCell ref="Q26:S26"/>
@@ -7599,16 +7841,13 @@
     <mergeCell ref="M38:P38"/>
     <mergeCell ref="AF58:AK58"/>
     <mergeCell ref="D43:L43"/>
-    <mergeCell ref="D83:AK83"/>
-    <mergeCell ref="C97:AK97"/>
     <mergeCell ref="A19:AK19"/>
     <mergeCell ref="Y47:AE47"/>
     <mergeCell ref="AF60:AK60"/>
     <mergeCell ref="D85:AK85"/>
     <mergeCell ref="D110:AK110"/>
     <mergeCell ref="D59:L59"/>
-    <mergeCell ref="A79:AK79"/>
-    <mergeCell ref="Q37:S37"/>
+    <mergeCell ref="C123:AK123"/>
     <mergeCell ref="Y50:AE50"/>
     <mergeCell ref="Y52:AE52"/>
   </mergeCells>
@@ -7783,7 +8022,7 @@
       <c r="AC2" s="22" t="n"/>
       <c r="AD2" s="23" t="inlineStr">
         <is>
-          <t>2026/07/17</t>
+          <t>2026/08/17</t>
         </is>
       </c>
       <c r="AE2" s="21" t="n"/>
